--- a/data/rateBuildUp/File1/RPT_RPT6659694529226EG_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT6659694529226EG_rateBuildUp.xlsx
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="C11" s="369" t="n">
-        <v>46576674.63854356</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="D11" s="368" t="n">
         <v>53430343.59559114</v>
@@ -2970,7 +2970,7 @@
         <v>77027357.5318035</v>
       </c>
       <c r="H11" s="371" t="n">
-        <v>297.2181477908225</v>
+        <v>285.985451492463</v>
       </c>
       <c r="I11" s="372" t="n">
         <v>325.0610632735838</v>
@@ -2985,7 +2985,7 @@
         <v>391.0995684445464</v>
       </c>
       <c r="M11" s="371" t="n">
-        <v>36.83999773386719</v>
+        <v>35.44771227198476</v>
       </c>
       <c r="N11" s="372" t="n">
         <v>41.57241017461948</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="T11" s="374" t="n">
-        <v>46576674.63854356</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="U11" s="375" t="n">
         <v>53430343.59559114</v>
@@ -3020,7 +3020,7 @@
         <v>77027357.5318035</v>
       </c>
       <c r="Y11" s="377" t="n">
-        <v>297.2181477908225</v>
+        <v>285.985451492463</v>
       </c>
       <c r="Z11" s="372" t="n">
         <v>325.0610632735838</v>
@@ -3035,7 +3035,7 @@
         <v>391.0995684445464</v>
       </c>
       <c r="AD11" s="377" t="n">
-        <v>36.83999773386719</v>
+        <v>35.44771227198476</v>
       </c>
       <c r="AE11" s="372" t="n">
         <v>41.57241017461948</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="AK11" s="379" t="n">
-        <v>46576674.63854356</v>
+        <v>44816413.21207619</v>
       </c>
       <c r="AL11" s="368" t="n">
         <v>53430343.59559114</v>
@@ -3070,7 +3070,7 @@
         <v>77027357.5318035</v>
       </c>
       <c r="AP11" s="381" t="n">
-        <v>297.2366573077145</v>
+        <v>286.0032614834901</v>
       </c>
       <c r="AQ11" s="372" t="n">
         <v>325.0851884256385</v>
@@ -3085,7 +3085,7 @@
         <v>391.141430041976</v>
       </c>
       <c r="AU11" s="372" t="n">
-        <v>36.84028208826757</v>
+        <v>35.44798587984546</v>
       </c>
       <c r="AV11" s="372" t="n">
         <v>41.57280474314859</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="BB11" s="383" t="n">
-        <v>48790680.66857278</v>
+        <v>46942406.17078204</v>
       </c>
       <c r="BC11" s="384" t="n">
         <v>57940652.86013988</v>
@@ -3120,7 +3120,7 @@
         <v>90998246.02856024</v>
       </c>
       <c r="BG11" s="386" t="n">
-        <v>311.3656984368213</v>
+        <v>299.5706328213857</v>
       </c>
       <c r="BH11" s="372" t="n">
         <v>352.5271743544865</v>
@@ -3135,7 +3135,7 @@
         <v>462.0849685545384</v>
       </c>
       <c r="BL11" s="388" t="n">
-        <v>38.59147208464195</v>
+        <v>37.12956106579874</v>
       </c>
       <c r="BM11" s="389" t="n">
         <v>45.08216279267779</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>48761832.07662392</v>
+        <v>46918524.2093999</v>
       </c>
       <c r="BT11" s="375" t="n">
         <v>58312864.66497567</v>
@@ -3170,22 +3170,22 @@
         <v>93082485.59376027</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>309.2209694257513</v>
+        <v>297.5317153231276</v>
       </c>
       <c r="BY11" s="372" t="n">
-        <v>350.2537801471804</v>
+        <v>350.2537801471803</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>387.8149181787844</v>
+        <v>387.8149181787843</v>
       </c>
       <c r="CA11" s="372" t="n">
         <v>422.970205261525</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>459.4487048068605</v>
+        <v>459.4487048068604</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>38.6286882942305</v>
+        <v>37.16843624870832</v>
       </c>
       <c r="CD11" s="389" t="n">
         <v>45.44826524829606</v>
@@ -3200,28 +3200,28 @@
         <v>69.20346589917969</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>2.144729011069956</v>
+        <v>2.038917498258115</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>2.273394207306183</v>
+        <v>2.273394207306239</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>2.382907103635489</v>
+        <v>2.382907103635603</v>
       </c>
       <c r="CZ11" s="92" t="n">
         <v>2.521669468254004</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>2.636263747677958</v>
+        <v>2.636263747678015</v>
       </c>
       <c r="DC11" s="393" t="n">
-        <v>0.01509919443924004</v>
+        <v>0.01501787004944702</v>
       </c>
       <c r="DD11" s="394" t="n">
-        <v>0.01518172965937269</v>
+        <v>0.0151817296593727</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.01534942786781858</v>
+        <v>0.01534942786781859</v>
       </c>
       <c r="DF11" s="394" t="n">
         <v>0.01557349634666997</v>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="C12" s="369" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="D12" s="368" t="n">
         <v>19183612.89511097</v>
@@ -3252,7 +3252,7 @@
         <v>26435764.07323312</v>
       </c>
       <c r="H12" s="371" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="I12" s="372" t="n">
         <v>592.4035862418285</v>
@@ -3267,7 +3267,7 @@
         <v>695.2332407685739</v>
       </c>
       <c r="M12" s="371" t="n">
-        <v>60.98577537796256</v>
+        <v>59.23245962249033</v>
       </c>
       <c r="N12" s="372" t="n">
         <v>67.08361822745846</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="T12" s="374" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="U12" s="375" t="n">
         <v>19183612.89511097</v>
@@ -3302,7 +3302,7 @@
         <v>26435764.07323312</v>
       </c>
       <c r="Y12" s="377" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="Z12" s="372" t="n">
         <v>592.4035862418285</v>
@@ -3317,7 +3317,7 @@
         <v>695.2332407685739</v>
       </c>
       <c r="AD12" s="377" t="n">
-        <v>60.98577537796256</v>
+        <v>59.23245962249033</v>
       </c>
       <c r="AE12" s="372" t="n">
         <v>67.08361822745846</v>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="AK12" s="379" t="n">
-        <v>17295126.25561434</v>
+        <v>16797898.54687544</v>
       </c>
       <c r="AL12" s="368" t="n">
         <v>19183612.89511097</v>
@@ -3352,7 +3352,7 @@
         <v>26435764.07323312</v>
       </c>
       <c r="AP12" s="381" t="n">
-        <v>543.3473732819672</v>
+        <v>527.7263615892311</v>
       </c>
       <c r="AQ12" s="372" t="n">
         <v>592.4035862418285</v>
@@ -3367,7 +3367,7 @@
         <v>695.2332407685739</v>
       </c>
       <c r="AU12" s="372" t="n">
-        <v>60.98577537796041</v>
+        <v>59.23245962248824</v>
       </c>
       <c r="AV12" s="372" t="n">
         <v>67.0836182275476</v>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="BB12" s="383" t="n">
-        <v>18145030.69132207</v>
+        <v>17622941.59714622</v>
       </c>
       <c r="BC12" s="384" t="n">
         <v>20826724.18067933</v>
@@ -3402,7 +3402,7 @@
         <v>31269035.35373417</v>
       </c>
       <c r="BG12" s="386" t="n">
-        <v>570.048152209937</v>
+        <v>553.6460899325642</v>
       </c>
       <c r="BH12" s="372" t="n">
         <v>643.1440293214108</v>
@@ -3417,7 +3417,7 @@
         <v>822.3432742273291</v>
       </c>
       <c r="BL12" s="386" t="n">
-        <v>63.98269371453386</v>
+        <v>62.14171217128808</v>
       </c>
       <c r="BM12" s="372" t="n">
         <v>72.82945196539031</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="BS12" s="391" t="n">
-        <v>18191941.16370313</v>
+        <v>17669345.66016969</v>
       </c>
       <c r="BT12" s="375" t="n">
         <v>21058880.08272808</v>
@@ -3452,7 +3452,7 @@
         <v>32206181.46459534</v>
       </c>
       <c r="BX12" s="386" t="n">
-        <v>565.9086046083704</v>
+        <v>549.6518846949791</v>
       </c>
       <c r="BY12" s="372" t="n">
         <v>638.8115762007227</v>
@@ -3467,7 +3467,7 @@
         <v>817.4262300366823</v>
       </c>
       <c r="CC12" s="386" t="n">
-        <v>64.2268940149862</v>
+        <v>62.38186353054735</v>
       </c>
       <c r="CD12" s="372" t="n">
         <v>73.73722693051934</v>
@@ -3482,7 +3482,7 @@
         <v>109.5986592243839</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>4.139547601566619</v>
+        <v>3.994205237585106</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>4.332453120688115</v>
@@ -3497,19 +3497,19 @@
         <v>4.91704419064672</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.01565152476890455</v>
+        <v>0.01560453994728553</v>
       </c>
       <c r="DD12" s="397" t="n">
-        <v>0.01558388449696708</v>
+        <v>0.01558388449696707</v>
       </c>
       <c r="DE12" s="397" t="n">
-        <v>0.01579708867016908</v>
+        <v>0.01579708867016907</v>
       </c>
       <c r="DF12" s="397" t="n">
         <v>0.01599766935119004</v>
       </c>
       <c r="DG12" s="398" t="n">
-        <v>0.01597620874049981</v>
+        <v>0.0159762087404998</v>
       </c>
     </row>
     <row r="13">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C13" s="369" t="n">
-        <v>8050790.236236956</v>
+        <v>7835324.895783428</v>
       </c>
       <c r="D13" s="368" t="n">
         <v>9114259.644327773</v>
@@ -3534,7 +3534,7 @@
         <v>13221332.43027924</v>
       </c>
       <c r="H13" s="371" t="n">
-        <v>688.9527768236628</v>
+        <v>670.51415896643</v>
       </c>
       <c r="I13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3549,7 +3549,7 @@
         <v>845.0312067744577</v>
       </c>
       <c r="M13" s="371" t="n">
-        <v>117.4941092693843</v>
+        <v>114.3495846311614</v>
       </c>
       <c r="N13" s="372" t="n">
         <v>130.6461209288344</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="T13" s="374" t="n">
-        <v>8050790.236236956</v>
+        <v>7835324.895783428</v>
       </c>
       <c r="U13" s="375" t="n">
         <v>9114259.644327773</v>
@@ -3584,7 +3584,7 @@
         <v>13221332.43027924</v>
       </c>
       <c r="Y13" s="377" t="n">
-        <v>688.9527768236628</v>
+        <v>670.51415896643</v>
       </c>
       <c r="Z13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3599,7 +3599,7 @@
         <v>845.0312067744577</v>
       </c>
       <c r="AD13" s="377" t="n">
-        <v>117.4941092693843</v>
+        <v>114.3495846311614</v>
       </c>
       <c r="AE13" s="372" t="n">
         <v>130.6461209288344</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>8050790.236236956</v>
+        <v>7835324.895783428</v>
       </c>
       <c r="AL13" s="368" t="n">
         <v>9114259.644327773</v>
@@ -3634,7 +3634,7 @@
         <v>13221332.43027924</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>688.9527768236628</v>
+        <v>670.51415896643</v>
       </c>
       <c r="AQ13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3649,7 +3649,7 @@
         <v>845.0312067744577</v>
       </c>
       <c r="AU13" s="372" t="n">
-        <v>117.494109269693</v>
+        <v>114.3495846314617</v>
       </c>
       <c r="AV13" s="372" t="n">
         <v>130.6461209288344</v>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="BB13" s="383" t="n">
-        <v>8456624.195706248</v>
+        <v>8230385.588230044</v>
       </c>
       <c r="BC13" s="384" t="n">
         <v>9898183.571209885</v>
@@ -3684,7 +3684,7 @@
         <v>15641988.30953081</v>
       </c>
       <c r="BG13" s="386" t="n">
-        <v>723.6823406430276</v>
+        <v>704.3217918929332</v>
       </c>
       <c r="BH13" s="372" t="n">
         <v>803.8058499691623</v>
@@ -3699,7 +3699,7 @@
         <v>999.7455496454542</v>
       </c>
       <c r="BL13" s="386" t="n">
-        <v>123.4168942609865</v>
+        <v>120.1151433908438</v>
       </c>
       <c r="BM13" s="372" t="n">
         <v>141.8830863157253</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="BS13" s="391" t="n">
-        <v>8459639.181838185</v>
+        <v>8234394.396597154</v>
       </c>
       <c r="BT13" s="375" t="n">
         <v>9952954.78023549</v>
@@ -3734,22 +3734,22 @@
         <v>15903215.82847833</v>
       </c>
       <c r="BX13" s="386" t="n">
-        <v>722.1068685387845</v>
+        <v>702.8801848671825</v>
       </c>
       <c r="BY13" s="372" t="n">
         <v>802.3898184552372</v>
       </c>
       <c r="BZ13" s="372" t="n">
-        <v>873.7820185630104</v>
+        <v>873.7820185630105</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236424</v>
       </c>
       <c r="CB13" s="387" t="n">
-        <v>998.5916384034792</v>
+        <v>998.5916384034794</v>
       </c>
       <c r="CC13" s="386" t="n">
-        <v>123.6967833481126</v>
+        <v>120.4032557163351</v>
       </c>
       <c r="CD13" s="372" t="n">
         <v>142.9612665200117</v>
@@ -3764,22 +3764,22 @@
         <v>213.9019892506383</v>
       </c>
       <c r="CW13" s="102" t="n">
-        <v>1.57547210424309</v>
+        <v>1.441607025750727</v>
       </c>
       <c r="CX13" s="103" t="n">
         <v>1.416031513925077</v>
       </c>
       <c r="CY13" s="103" t="n">
-        <v>1.262268921135615</v>
+        <v>1.262268921135501</v>
       </c>
       <c r="CZ13" s="103" t="n">
-        <v>1.195333547514224</v>
+        <v>1.19533354751411</v>
       </c>
       <c r="DA13" s="104" t="n">
-        <v>1.153911241974924</v>
+        <v>1.153911241974811</v>
       </c>
       <c r="DC13" s="396" t="n">
-        <v>0.01255052524219418</v>
+        <v>0.0124216590811804</v>
       </c>
       <c r="DD13" s="397" t="n">
         <v>0.01250671103088637</v>
@@ -3788,7 +3788,7 @@
         <v>0.01253173068945308</v>
       </c>
       <c r="DF13" s="397" t="n">
-        <v>0.0125379336023419</v>
+        <v>0.01253793360234189</v>
       </c>
       <c r="DG13" s="398" t="n">
         <v>0.01247566905431304</v>
@@ -4001,64 +4001,64 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="BW14" s="421" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="BX14" s="416" t="n">
         <v>3301.597169367806</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>3686.742635471712</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437094</v>
       </c>
       <c r="CC14" s="417" t="n">
         <v>2900.977332425373</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="CW14" s="132" t="n">
         <v>67.81229001315251</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>71.20819560781456</v>
+        <v>71.20819560781638</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>73.37099834241417</v>
+        <v>73.37099834241599</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>78.47102417561109</v>
+        <v>78.47102417561246</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>80.37337236889653</v>
+        <v>80.37337236889834</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0.04866627713558654</v>
@@ -4067,10 +4067,10 @@
         <v>0.04942471132771884</v>
       </c>
       <c r="DE14" s="423" t="n">
-        <v>0.04960100930908167</v>
+        <v>0.04960100930908168</v>
       </c>
       <c r="DF14" s="423" t="n">
-        <v>0.04998498574654767</v>
+        <v>0.04998498574654765</v>
       </c>
       <c r="DG14" s="424" t="n">
         <v>0.05019646764910229</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C15" s="425" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="D15" s="425" t="n">
         <v>161532099.6256683</v>
@@ -4098,7 +4098,7 @@
         <v>238354658.0410133</v>
       </c>
       <c r="H15" s="427" t="n">
-        <v>643.3438188355618</v>
+        <v>632.22357308174</v>
       </c>
       <c r="I15" s="427" t="n">
         <v>691.7972564127136</v>
@@ -4113,7 +4113,7 @@
         <v>839.126686349459</v>
       </c>
       <c r="M15" s="427" t="n">
-        <v>87.15185013114962</v>
+        <v>85.64542392018085</v>
       </c>
       <c r="N15" s="427" t="n">
         <v>96.79669007575326</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="T15" s="429" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="U15" s="430" t="n">
         <v>161532099.6256683</v>
@@ -4148,7 +4148,7 @@
         <v>238354658.0410133</v>
       </c>
       <c r="Y15" s="432" t="n">
-        <v>643.3438188355618</v>
+        <v>632.22357308174</v>
       </c>
       <c r="Z15" s="433" t="n">
         <v>691.7972564127136</v>
@@ -4163,7 +4163,7 @@
         <v>839.126686349459</v>
       </c>
       <c r="AD15" s="433" t="n">
-        <v>87.15185013114962</v>
+        <v>85.64542392018085</v>
       </c>
       <c r="AE15" s="433" t="n">
         <v>96.79669007575326</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="AK15" s="435" t="n">
-        <v>143068778.4602869</v>
+        <v>140595823.9846271</v>
       </c>
       <c r="AL15" s="408" t="n">
         <v>161532099.6256683</v>
@@ -4198,7 +4198,7 @@
         <v>238354658.0410134</v>
       </c>
       <c r="AP15" s="436" t="n">
-        <v>643.3720511397373</v>
+        <v>632.2513173884383</v>
       </c>
       <c r="AQ15" s="437" t="n">
         <v>691.8333988481108</v>
@@ -4213,7 +4213,7 @@
         <v>839.1889598517764</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>87.15236821113018</v>
+        <v>85.64593304511044</v>
       </c>
       <c r="AV15" s="437" t="n">
         <v>96.79739763240835</v>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="BB15" s="439" t="n">
-        <v>150052098.3541718</v>
+        <v>147455496.1547291</v>
       </c>
       <c r="BC15" s="440" t="n">
         <v>175425786.1478831</v>
@@ -4248,7 +4248,7 @@
         <v>278690895.7052011</v>
       </c>
       <c r="BG15" s="442" t="n">
-        <v>674.7756382273338</v>
+        <v>663.0988677884699</v>
       </c>
       <c r="BH15" s="443" t="n">
         <v>751.3393199094292</v>
@@ -4263,7 +4263,7 @@
         <v>981.2030728040783</v>
       </c>
       <c r="BL15" s="443" t="n">
-        <v>91.40635621101312</v>
+        <v>89.82459928669239</v>
       </c>
       <c r="BM15" s="443" t="n">
         <v>105.1231279484721</v>
@@ -4283,37 +4283,37 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>146573182.8131704</v>
+        <v>143982034.6571719</v>
       </c>
       <c r="BT15" s="440" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="BU15" s="440" t="n">
         <v>201114502.5764502</v>
       </c>
       <c r="BV15" s="440" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="BW15" s="441" t="n">
         <v>275765716.3780742</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>656.9627481758932</v>
+        <v>645.3488377672923</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>730.1653162186614</v>
+        <v>730.1653162186611</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>804.512124264402</v>
+        <v>804.5121242644018</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>874.124505895719</v>
+        <v>874.1245058957189</v>
       </c>
       <c r="CB15" s="444" t="n">
         <v>949.2839689357262</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>89.45645662511873</v>
+        <v>87.87502864370011</v>
       </c>
       <c r="CD15" s="443" t="n">
         <v>103.3101833037134</v>
@@ -5264,7 +5264,7 @@
         <v>0.1029411561032852</v>
       </c>
       <c r="BY20" s="372" t="n">
-        <v>0.1178983509663407</v>
+        <v>0.1178983509663406</v>
       </c>
       <c r="BZ20" s="372" t="n">
         <v>0.134965310654519</v>
@@ -5294,16 +5294,16 @@
         <v>-0.0007016581515451176</v>
       </c>
       <c r="CX20" s="92" t="n">
-        <v>-0.0008888391821984393</v>
+        <v>-0.0008888391821984115</v>
       </c>
       <c r="CY20" s="92" t="n">
-        <v>-0.001109546786169202</v>
+        <v>-0.001109546786169174</v>
       </c>
       <c r="CZ20" s="92" t="n">
         <v>-0.001342965810719049</v>
       </c>
       <c r="DA20" s="93" t="n">
-        <v>-0.001577712896554062</v>
+        <v>-0.001577712896554034</v>
       </c>
       <c r="DC20" s="393" t="n">
         <v>0.001461865594343583</v>
@@ -5573,7 +5573,7 @@
         <v>0.001381848297625783</v>
       </c>
       <c r="CW21" s="102" t="n">
-        <v>-4.904418054423043e-05</v>
+        <v>-4.90441805442287e-05</v>
       </c>
       <c r="CX21" s="103" t="n">
         <v>-5.484568153329636e-05</v>
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="BS22" s="391" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="BT22" s="375" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="BU22" s="375" t="n">
-        <v>863.5965974050195</v>
+        <v>863.5965974050197</v>
       </c>
       <c r="BV22" s="375" t="n">
         <v>1005.619876619043</v>
@@ -5828,10 +5828,10 @@
         <v>0.05511847987654938</v>
       </c>
       <c r="BY22" s="372" t="n">
-        <v>0.06002765782677747</v>
+        <v>0.06002765782677748</v>
       </c>
       <c r="BZ22" s="372" t="n">
-        <v>0.06501912662649771</v>
+        <v>0.06501912662649773</v>
       </c>
       <c r="CA22" s="372" t="n">
         <v>0.06957975474179512</v>
@@ -5840,13 +5840,13 @@
         <v>0.07390165411824727</v>
       </c>
       <c r="CC22" s="386" t="n">
-        <v>0.009441786196499305</v>
+        <v>0.009441786196499307</v>
       </c>
       <c r="CD22" s="372" t="n">
         <v>0.01069508833707209</v>
       </c>
       <c r="CE22" s="372" t="n">
-        <v>0.01217239558540951</v>
+        <v>0.01217239558540952</v>
       </c>
       <c r="CF22" s="372" t="n">
         <v>0.01388566074660945</v>
@@ -5858,10 +5858,10 @@
         <v>-0.0005730192256924033</v>
       </c>
       <c r="CX22" s="103" t="n">
-        <v>-0.0006461386043902853</v>
+        <v>-0.0006461386043902922</v>
       </c>
       <c r="CY22" s="103" t="n">
-        <v>-0.0007220523663725442</v>
+        <v>-0.0007220523663725581</v>
       </c>
       <c r="CZ22" s="103" t="n">
         <v>-0.0007848145587732169</v>
@@ -6389,13 +6389,13 @@
         <v>36401.50179524109</v>
       </c>
       <c r="BX24" s="442" t="n">
-        <v>0.07718104575580054</v>
+        <v>0.07718104575580055</v>
       </c>
       <c r="BY24" s="443" t="n">
-        <v>0.08797366820908514</v>
+        <v>0.08797366820908513</v>
       </c>
       <c r="BZ24" s="443" t="n">
-        <v>0.09997933894145931</v>
+        <v>0.0999793389414593</v>
       </c>
       <c r="CA24" s="443" t="n">
         <v>0.1124814121024787</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="BB29" s="391" t="n">
-        <v>1082.764896368825</v>
+        <v>1087.098008869965</v>
       </c>
       <c r="BC29" s="375" t="n">
         <v>1064.135841095292</v>
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="BG29" s="386" t="n">
-        <v>0.006909841051221671</v>
+        <v>0.006937493516443201</v>
       </c>
       <c r="BH29" s="372" t="n">
         <v>0.006474500763672487</v>
@@ -7316,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="BL29" s="388" t="n">
-        <v>0.000856423618196472</v>
+        <v>0.0008598509364432337</v>
       </c>
       <c r="BM29" s="389" t="n">
         <v>0.0008279772983846429</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>1050.977606359472</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.006733567703092374</v>
+        <v>0.00676051474070819</v>
       </c>
       <c r="BY29" s="372" t="n">
-        <v>0.006312652989907675</v>
+        <v>0.006312652989907674</v>
       </c>
       <c r="BZ29" s="372" t="n">
-        <v>0.005913511288780401</v>
+        <v>0.0059135112887804</v>
       </c>
       <c r="CA29" s="372" t="n">
         <v>0.0002182438534425571</v>
@@ -7366,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.0008411748025817799</v>
+        <v>0.000844541096654421</v>
       </c>
       <c r="CD29" s="389" t="n">
         <v>0.0008191178618692286</v>
@@ -7381,13 +7381,13 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>0.0001762733481292973</v>
+        <v>0.0001769787757350113</v>
       </c>
       <c r="CX29" s="92" t="n">
-        <v>0.0001618477737648115</v>
+        <v>0.0001618477737648123</v>
       </c>
       <c r="CY29" s="92" t="n">
-        <v>0.0001484953160049776</v>
+        <v>0.0001484953160049794</v>
       </c>
       <c r="CZ29" s="92" t="n">
         <v>5.388852115648872e-06</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="BB33" s="439" t="n">
-        <v>1082.764896368825</v>
+        <v>1087.098008869965</v>
       </c>
       <c r="BC33" s="440" t="n">
         <v>1064.135841095292</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="BG33" s="442" t="n">
-        <v>0.004869131335124138</v>
+        <v>0.004888617092308058</v>
       </c>
       <c r="BH33" s="443" t="n">
         <v>0.004557637259016115</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="BL33" s="443" t="n">
-        <v>0.0006595815379846562</v>
+        <v>0.0006622211146991827</v>
       </c>
       <c r="BM33" s="443" t="n">
         <v>0.000637678705248688</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>1061.833219863856</v>
+        <v>1066.082565972644</v>
       </c>
       <c r="BT33" s="440" t="n">
         <v>1050.977606359472</v>
@@ -8479,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>0.00475929400479345</v>
+        <v>0.004778340204405136</v>
       </c>
       <c r="BY33" s="443" t="n">
-        <v>0.004460365371489599</v>
+        <v>0.004460365371489598</v>
       </c>
       <c r="BZ33" s="443" t="n">
         <v>0.004164063495649975</v>
@@ -8494,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>0.0006480574109995107</v>
+        <v>0.0006506508693564218</v>
       </c>
       <c r="CD33" s="443" t="n">
         <v>0.0006310915540558638</v>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="BB38" s="391" t="n">
-        <v>444.1441328636853</v>
+        <v>445.9215514897169</v>
       </c>
       <c r="BC38" s="375" t="n">
         <v>689.3364752758301</v>
@@ -9391,7 +9391,7 @@
         <v>1624.657186703561</v>
       </c>
       <c r="BG38" s="386" t="n">
-        <v>0.002834378332926074</v>
+        <v>0.002845721220221873</v>
       </c>
       <c r="BH38" s="372" t="n">
         <v>0.004194116355489805</v>
@@ -9406,7 +9406,7 @@
         <v>0.008249935551441285</v>
       </c>
       <c r="BL38" s="388" t="n">
-        <v>0.0003513002005730739</v>
+        <v>0.0003527060674384117</v>
       </c>
       <c r="BM38" s="389" t="n">
         <v>0.00053635535091968</v>
@@ -9426,13 +9426,13 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>450.6865261022974</v>
+        <v>452.4901267056214</v>
       </c>
       <c r="BT38" s="375" t="n">
         <v>704.4597020478225</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>997.0452295340147</v>
+        <v>997.0452295340144</v>
       </c>
       <c r="BV38" s="375" t="n">
         <v>1318.398827527651</v>
@@ -9441,28 +9441,28 @@
         <v>1688.256854667008</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.002858008376089823</v>
+        <v>0.002869445828360696</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.00423130770579009</v>
+        <v>0.004231307705790089</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>0.005664116158427144</v>
+        <v>0.005664116158427142</v>
       </c>
       <c r="CA38" s="372" t="n">
         <v>0.007022073357940789</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.008333118956914248</v>
+        <v>0.008333118956914246</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>0.0003570298447330322</v>
+        <v>0.0003584586410383803</v>
       </c>
       <c r="CD38" s="389" t="n">
         <v>0.0005490464510592812</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.0007655346816305535</v>
+        <v>0.0007655346816305533</v>
       </c>
       <c r="CF38" s="389" t="n">
         <v>0.0009978984895167369</v>
@@ -9471,19 +9471,19 @@
         <v>0.001255157991600049</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-2.363004316374966e-05</v>
+        <v>-2.372460813882329e-05</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>-3.719135030028509e-05</v>
+        <v>-3.719135030028423e-05</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>-5.267230080287493e-05</v>
+        <v>-5.26723008028732e-05</v>
       </c>
       <c r="CZ38" s="92" t="n">
         <v>-6.81459156262219e-05</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>-8.318340547296306e-05</v>
+        <v>-8.318340547296132e-05</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="BB40" s="391" t="n">
-        <v>74.97592112721192</v>
+        <v>75.10914895326566</v>
       </c>
       <c r="BC40" s="375" t="n">
         <v>118.1051228030125</v>
@@ -9955,7 +9955,7 @@
         <v>294.2621680813406</v>
       </c>
       <c r="BG40" s="386" t="n">
-        <v>0.006416124074752783</v>
+        <v>0.00642752515191621</v>
       </c>
       <c r="BH40" s="372" t="n">
         <v>0.009591011112030095</v>
@@ -9970,7 +9970,7 @@
         <v>0.01880753822000313</v>
       </c>
       <c r="BL40" s="386" t="n">
-        <v>0.001094206756234412</v>
+        <v>0.001096151097633554</v>
       </c>
       <c r="BM40" s="372" t="n">
         <v>0.001692948934765096</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="BS40" s="391" t="n">
-        <v>75.95593873923129</v>
+        <v>76.09090799925453</v>
       </c>
       <c r="BT40" s="375" t="n">
         <v>120.2627442393418</v>
@@ -9999,16 +9999,16 @@
         <v>172.6544121934863</v>
       </c>
       <c r="BV40" s="375" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="BW40" s="392" t="n">
         <v>302.956044420873</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.006483527712111256</v>
+        <v>0.006495048561595429</v>
       </c>
       <c r="BY40" s="372" t="n">
-        <v>0.009695372243502838</v>
+        <v>0.00969537224350284</v>
       </c>
       <c r="BZ40" s="372" t="n">
         <v>0.01299893853538077</v>
@@ -10020,31 +10020,31 @@
         <v>0.01902315707875442</v>
       </c>
       <c r="CC40" s="386" t="n">
-        <v>0.001110627190625365</v>
+        <v>0.001112600710175891</v>
       </c>
       <c r="CD40" s="372" t="n">
-        <v>0.001727418099574823</v>
+        <v>0.001727418099574824</v>
       </c>
       <c r="CE40" s="372" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248186</v>
       </c>
       <c r="CG40" s="387" t="n">
         <v>0.004074829975022104</v>
       </c>
       <c r="CW40" s="102" t="n">
-        <v>-6.740363735847302e-05</v>
+        <v>-6.752340967921839e-05</v>
       </c>
       <c r="CX40" s="103" t="n">
-        <v>-0.0001043611314727431</v>
+        <v>-0.0001043611314727449</v>
       </c>
       <c r="CY40" s="103" t="n">
-        <v>-0.0001443562043476898</v>
+        <v>-0.0001443562043476915</v>
       </c>
       <c r="CZ40" s="103" t="n">
-        <v>-0.0001816751258664866</v>
+        <v>-0.00018167512586649</v>
       </c>
       <c r="DA40" s="104" t="n">
         <v>-0.0002156188587512861</v>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="BB42" s="439" t="n">
-        <v>519.1200539908972</v>
+        <v>521.0307004429826</v>
       </c>
       <c r="BC42" s="440" t="n">
         <v>807.4415980788426</v>
@@ -10519,7 +10519,7 @@
         <v>1918.919354784902</v>
       </c>
       <c r="BG42" s="442" t="n">
-        <v>0.002334452963940018</v>
+        <v>0.002343045030917247</v>
       </c>
       <c r="BH42" s="443" t="n">
         <v>0.003458229456960944</v>
@@ -10534,7 +10534,7 @@
         <v>0.006756049789907169</v>
       </c>
       <c r="BL42" s="443" t="n">
-        <v>0.0003162293169627844</v>
+        <v>0.0003173932142498481</v>
       </c>
       <c r="BM42" s="443" t="n">
         <v>0.0004838558132736932</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>526.6424648415287</v>
+        <v>528.5810347048759</v>
       </c>
       <c r="BT42" s="440" t="n">
         <v>824.7224462871643</v>
@@ -10569,7 +10569,7 @@
         <v>1991.212899087881</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>0.002360489650070751</v>
+        <v>0.002369178607767597</v>
       </c>
       <c r="BY42" s="443" t="n">
         <v>0.003500134939365452</v>
@@ -10578,13 +10578,13 @@
         <v>0.004679113298454359</v>
       </c>
       <c r="CA42" s="443" t="n">
-        <v>0.00579016030296049</v>
+        <v>0.005790160302960491</v>
       </c>
       <c r="CB42" s="444" t="n">
         <v>0.006854465118683069</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.0003214201118433282</v>
+        <v>0.0003226032586343502</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>0.0004952297433767576</v>
@@ -10593,7 +10593,7 @@
         <v>0.0006915956769268278</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.0009033218384782984</v>
+        <v>0.0009033218384782986</v>
       </c>
       <c r="CG42" s="444" t="n">
         <v>0.001137719236600299</v>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="C47" s="454" t="n">
-        <v>46594302.08771283</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="D47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11249,7 +11249,7 @@
         <v>77062920.15333697</v>
       </c>
       <c r="H47" s="371" t="n">
-        <v>297.3306332319372</v>
+        <v>286.0979369335776</v>
       </c>
       <c r="I47" s="372" t="n">
         <v>325.1897713688447</v>
@@ -11264,7 +11264,7 @@
         <v>391.2801344977016</v>
       </c>
       <c r="M47" s="371" t="n">
-        <v>36.85394023174814</v>
+        <v>35.46165476986572</v>
       </c>
       <c r="N47" s="372" t="n">
         <v>41.58887079181889</v>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="T47" s="374" t="n">
-        <v>46594302.08771283</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="U47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11299,7 +11299,7 @@
         <v>77062920.15333697</v>
       </c>
       <c r="Y47" s="377" t="n">
-        <v>297.3306332319372</v>
+        <v>286.0979369335776</v>
       </c>
       <c r="Z47" s="372" t="n">
         <v>325.1897713688447</v>
@@ -11314,7 +11314,7 @@
         <v>391.2801344977016</v>
       </c>
       <c r="AD47" s="377" t="n">
-        <v>36.85394023174814</v>
+        <v>35.46165476986572</v>
       </c>
       <c r="AE47" s="372" t="n">
         <v>41.58887079181889</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="AK47" s="379" t="n">
-        <v>46594302.08771283</v>
+        <v>44834040.66124546</v>
       </c>
       <c r="AL47" s="375" t="n">
         <v>53451499.36762998</v>
@@ -11349,7 +11349,7 @@
         <v>77062920.15333697</v>
       </c>
       <c r="AP47" s="381" t="n">
-        <v>297.3491497539571</v>
+        <v>286.1157539297327</v>
       </c>
       <c r="AQ47" s="372" t="n">
         <v>325.2139060732657</v>
@@ -11364,7 +11364,7 @@
         <v>391.3220154221365</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>36.85422469376554</v>
+        <v>35.46192848534343</v>
       </c>
       <c r="AV47" s="372" t="n">
         <v>41.58926551657761</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="BB47" s="391" t="n">
-        <v>48808228.40045219</v>
+        <v>46959960.01319258</v>
       </c>
       <c r="BC47" s="375" t="n">
         <v>57961637.77898525</v>
@@ -11399,7 +11399,7 @@
         <v>91033404.66453952</v>
       </c>
       <c r="BG47" s="386" t="n">
-        <v>311.4776821541572</v>
+        <v>299.6826555340742</v>
       </c>
       <c r="BH47" s="372" t="n">
         <v>352.6548524833898</v>
@@ -11414,7 +11414,7 @@
         <v>462.2635025143667</v>
       </c>
       <c r="BL47" s="388" t="n">
-        <v>38.60535163696</v>
+        <v>37.14344545130191</v>
       </c>
       <c r="BM47" s="389" t="n">
         <v>45.0984906295398</v>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>48779577.64607865</v>
+        <v>46936275.83180135</v>
       </c>
       <c r="BT47" s="375" t="n">
         <v>58334248.7001003</v>
@@ -11449,22 +11449,22 @@
         <v>93118992.3570275</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>309.3335021579338</v>
+        <v>297.6442864398</v>
       </c>
       <c r="BY47" s="372" t="n">
-        <v>350.3822224588424</v>
+        <v>350.3822224588423</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>387.9614611168861</v>
+        <v>387.961461116886</v>
       </c>
       <c r="CA47" s="372" t="n">
         <v>423.130517841733</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>459.6288996629908</v>
+        <v>459.6288996629907</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>38.64274617601791</v>
+        <v>37.1824989255861</v>
       </c>
       <c r="CD47" s="389" t="n">
         <v>45.46493167869708</v>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="C48" s="454" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="D48" s="375" t="n">
         <v>19183960.51387434</v>
@@ -11501,7 +11501,7 @@
         <v>26436153.51971607</v>
       </c>
       <c r="H48" s="371" t="n">
-        <v>543.357928207859</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="I48" s="372" t="n">
         <v>592.4143209560448</v>
@@ -11516,7 +11516,7 @@
         <v>695.2434828080965</v>
       </c>
       <c r="M48" s="371" t="n">
-        <v>60.98696007190096</v>
+        <v>59.23364431642874</v>
       </c>
       <c r="N48" s="372" t="n">
         <v>67.08483382352674</v>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="T48" s="374" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="U48" s="375" t="n">
         <v>19183960.51387434</v>
@@ -11551,7 +11551,7 @@
         <v>26436153.51971607</v>
       </c>
       <c r="Y48" s="377" t="n">
-        <v>543.357928207859</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="Z48" s="372" t="n">
         <v>592.4143209560448</v>
@@ -11566,7 +11566,7 @@
         <v>695.2434828080965</v>
       </c>
       <c r="AD48" s="377" t="n">
-        <v>60.98696007190096</v>
+        <v>59.23364431642874</v>
       </c>
       <c r="AE48" s="372" t="n">
         <v>67.08483382352674</v>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="AK48" s="379" t="n">
-        <v>17295462.22627491</v>
+        <v>16798234.517536</v>
       </c>
       <c r="AL48" s="375" t="n">
         <v>19183960.51387434</v>
@@ -11601,7 +11601,7 @@
         <v>26436153.51971607</v>
       </c>
       <c r="AP48" s="381" t="n">
-        <v>543.3579282078591</v>
+        <v>527.7369165151231</v>
       </c>
       <c r="AQ48" s="372" t="n">
         <v>592.4143209560448</v>
@@ -11616,7 +11616,7 @@
         <v>695.2434828080964</v>
       </c>
       <c r="AU48" s="372" t="n">
-        <v>60.98696007189881</v>
+        <v>59.23364431642665</v>
       </c>
       <c r="AV48" s="372" t="n">
         <v>67.08483382361588</v>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="BB48" s="391" t="n">
-        <v>18145366.66198264</v>
+        <v>17623277.56780678</v>
       </c>
       <c r="BC48" s="375" t="n">
         <v>20827071.7994427</v>
@@ -11651,7 +11651,7 @@
         <v>31269424.80021711</v>
       </c>
       <c r="BG48" s="386" t="n">
-        <v>570.058707135829</v>
+        <v>553.6566448584562</v>
       </c>
       <c r="BH48" s="372" t="n">
         <v>643.1547640356271</v>
@@ -11666,7 +11666,7 @@
         <v>822.3535162668516</v>
       </c>
       <c r="BL48" s="386" t="n">
-        <v>63.98387840847226</v>
+        <v>62.14289686522649</v>
       </c>
       <c r="BM48" s="372" t="n">
         <v>72.83066756145858</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>18192282.0434814</v>
+        <v>17669686.53994796</v>
       </c>
       <c r="BT48" s="375" t="n">
         <v>21059235.76827997</v>
@@ -11701,7 +11701,7 @@
         <v>32206587.52847737</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>565.9192085784429</v>
+        <v>549.6624886650516</v>
       </c>
       <c r="BY48" s="372" t="n">
         <v>638.8223657606205</v>
@@ -11716,7 +11716,7 @@
         <v>817.436536358424</v>
       </c>
       <c r="CC48" s="386" t="n">
-        <v>64.22809749564799</v>
+        <v>62.38306701120914</v>
       </c>
       <c r="CD48" s="372" t="n">
         <v>73.73847235601929</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030712</v>
       </c>
       <c r="D49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11753,7 +11753,7 @@
         <v>13222813.69470703</v>
       </c>
       <c r="H49" s="371" t="n">
-        <v>689.0139876707993</v>
+        <v>670.5753698135666</v>
       </c>
       <c r="I49" s="372" t="n">
         <v>740.215038819186</v>
@@ -11768,7 +11768,7 @@
         <v>845.1258806413747</v>
       </c>
       <c r="M49" s="371" t="n">
-        <v>117.5045481763804</v>
+        <v>114.3600235381574</v>
       </c>
       <c r="N49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030712</v>
       </c>
       <c r="U49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11803,7 +11803,7 @@
         <v>13222813.69470703</v>
       </c>
       <c r="Y49" s="377" t="n">
-        <v>689.0139876707993</v>
+        <v>670.5753698135666</v>
       </c>
       <c r="Z49" s="372" t="n">
         <v>740.215038819186</v>
@@ -11818,7 +11818,7 @@
         <v>845.1258806413747</v>
       </c>
       <c r="AD49" s="377" t="n">
-        <v>117.5045481763804</v>
+        <v>114.3600235381574</v>
       </c>
       <c r="AE49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>8051505.518484239</v>
+        <v>7836040.178030712</v>
       </c>
       <c r="AL49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11853,7 +11853,7 @@
         <v>13222813.69470703</v>
       </c>
       <c r="AP49" s="381" t="n">
-        <v>689.0139876707993</v>
+        <v>670.5753698135666</v>
       </c>
       <c r="AQ49" s="372" t="n">
         <v>740.2150388191859</v>
@@ -11868,7 +11868,7 @@
         <v>845.1258806413746</v>
       </c>
       <c r="AU49" s="372" t="n">
-        <v>117.504548176689</v>
+        <v>114.3600235384578</v>
       </c>
       <c r="AV49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="BB49" s="391" t="n">
-        <v>8457336.565185849</v>
+        <v>8231098.090937469</v>
       </c>
       <c r="BC49" s="375" t="n">
         <v>9899032.909102421</v>
@@ -11903,7 +11903,7 @@
         <v>15643425.72900321</v>
       </c>
       <c r="BG49" s="386" t="n">
-        <v>723.7433022277532</v>
+        <v>704.382764878736</v>
       </c>
       <c r="BH49" s="372" t="n">
         <v>803.8748224994966</v>
@@ -11918,7 +11918,7 @@
         <v>999.8374211960563</v>
       </c>
       <c r="BL49" s="386" t="n">
-        <v>123.4272906587339</v>
+        <v>120.1255417329325</v>
       </c>
       <c r="BM49" s="372" t="n">
         <v>141.8952609415696</v>
@@ -11938,13 +11938,13 @@
         </is>
       </c>
       <c r="BS49" s="391" t="n">
-        <v>8460360.862769058</v>
+        <v>8235116.212497286</v>
       </c>
       <c r="BT49" s="375" t="n">
         <v>9953819.634386763</v>
       </c>
       <c r="BU49" s="375" t="n">
-        <v>11606777.78056714</v>
+        <v>11606777.78056715</v>
       </c>
       <c r="BV49" s="375" t="n">
         <v>13555603.20628449</v>
@@ -11953,22 +11953,22 @@
         <v>15904695.7160234</v>
       </c>
       <c r="BX49" s="386" t="n">
-        <v>722.1684705463732</v>
+        <v>702.9417983956207</v>
       </c>
       <c r="BY49" s="372" t="n">
         <v>802.4595414853076</v>
       </c>
       <c r="BZ49" s="372" t="n">
-        <v>873.8600366281722</v>
+        <v>873.8600366281723</v>
       </c>
       <c r="CA49" s="372" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542814</v>
       </c>
       <c r="CB49" s="387" t="n">
-        <v>998.6845632146762</v>
+        <v>998.6845632146764</v>
       </c>
       <c r="CC49" s="386" t="n">
-        <v>123.7073357614998</v>
+        <v>120.4138101032418</v>
       </c>
       <c r="CD49" s="372" t="n">
         <v>142.9736890264484</v>
@@ -11977,7 +11977,7 @@
         <v>163.5975535817733</v>
       </c>
       <c r="CF49" s="372" t="n">
-        <v>187.1765979516572</v>
+        <v>187.1765979516573</v>
       </c>
       <c r="CG49" s="387" t="n">
         <v>213.9218940858095</v>
@@ -12190,49 +12190,49 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100519</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>97003937.42761645</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="BX50" s="416" t="n">
         <v>3301.597169367806</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>3686.742635471712</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437094</v>
       </c>
       <c r="CC50" s="417" t="n">
         <v>2900.977332425373</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="C51" s="425" t="n">
-        <v>143087457.1623641</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="D51" s="425" t="n">
         <v>161554460.3331398</v>
@@ -12257,7 +12257,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="H51" s="427" t="n">
-        <v>643.427812196339</v>
+        <v>632.3075664425172</v>
       </c>
       <c r="I51" s="427" t="n">
         <v>691.8930211314048</v>
@@ -12272,7 +12272,7 @@
         <v>839.2584702569818</v>
       </c>
       <c r="M51" s="427" t="n">
-        <v>87.16322845884338</v>
+        <v>85.65680224787461</v>
       </c>
       <c r="N51" s="427" t="n">
         <v>96.81008953305006</v>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="T51" s="429" t="n">
-        <v>143087457.1623641</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="U51" s="430" t="n">
         <v>161554460.3331398</v>
@@ -12307,7 +12307,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="Y51" s="432" t="n">
-        <v>643.4278121963391</v>
+        <v>632.3075664425173</v>
       </c>
       <c r="Z51" s="433" t="n">
         <v>691.8930211314047</v>
@@ -12322,7 +12322,7 @@
         <v>839.2584702569818</v>
       </c>
       <c r="AD51" s="433" t="n">
-        <v>87.16322845884339</v>
+        <v>85.65680224787464</v>
       </c>
       <c r="AE51" s="433" t="n">
         <v>96.81008953305005</v>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="AK51" s="435" t="n">
-        <v>143087457.1623641</v>
+        <v>140614502.6867042</v>
       </c>
       <c r="AL51" s="408" t="n">
         <v>161554460.3331398</v>
@@ -12357,7 +12357,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="AP51" s="436" t="n">
-        <v>643.4560481864538</v>
+        <v>632.3353144351547</v>
       </c>
       <c r="AQ51" s="437" t="n">
         <v>691.9291685699586</v>
@@ -12372,7 +12372,7 @@
         <v>839.3207535392831</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>87.16374660646321</v>
+        <v>85.65731144044345</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>96.81079718765139</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="BB51" s="439" t="n">
-        <v>150070694.4261914</v>
+        <v>147474098.4705076</v>
       </c>
       <c r="BC51" s="440" t="n">
         <v>175447968.0233843</v>
@@ -12407,7 +12407,7 @@
         <v>278727881.2071357</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>674.8592636914439</v>
+        <v>663.1825213304038</v>
       </c>
       <c r="BH51" s="443" t="n">
         <v>751.4343237034518</v>
@@ -12422,7 +12422,7 @@
         <v>981.3332897889409</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>91.41768427107887</v>
+        <v>89.83593115023211</v>
       </c>
       <c r="BM51" s="443" t="n">
         <v>105.1364203394464</v>
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>146591990.9433343</v>
+        <v>144000848.9752518</v>
       </c>
       <c r="BT51" s="440" t="n">
         <v>172068464.5824612</v>
@@ -12457,22 +12457,22 @@
         <v>275804109.0927685</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>657.047049005304</v>
+        <v>645.4331663318602</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>730.2612503871811</v>
+        <v>730.261250387181</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>804.6209467801376</v>
+        <v>804.6209467801375</v>
       </c>
       <c r="CA51" s="417" t="n">
-        <v>874.2429304181996</v>
+        <v>874.2429304181995</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>949.4161303554341</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>89.46793559178857</v>
+        <v>87.8865113869751</v>
       </c>
       <c r="CD51" s="417" t="n">
         <v>103.3237569100115</v>
@@ -12484,7 +12484,7 @@
         <v>136.3904779593478</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>157.5861830706237</v>
+        <v>157.5861830706236</v>
       </c>
     </row>
     <row r="52">
@@ -13599,7 +13599,7 @@
         <v>157692.5140852467</v>
       </c>
       <c r="BY58" s="190" t="n">
-        <v>166487.4670031312</v>
+        <v>166487.4670031313</v>
       </c>
       <c r="BZ58" s="190" t="n">
         <v>176028.3867149508</v>
@@ -13653,25 +13653,25 @@
         <v>29501926</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>2615.148328173741</v>
+        <v>2615.148328173728</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333039</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.009848161142163608</v>
+        <v>0.009848161142163612</v>
       </c>
       <c r="DD58" s="394" t="n">
-        <v>0.01024095992489388</v>
+        <v>0.01024095992489387</v>
       </c>
       <c r="DE58" s="394" t="n">
         <v>0.01065955492973541</v>
@@ -13962,25 +13962,25 @@
         <v>24983100</v>
       </c>
       <c r="CW59" s="102" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="CX59" s="103" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="CZ59" s="103" t="n">
-        <v>446.7528256294408</v>
+        <v>446.7528256294383</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469131</v>
       </c>
       <c r="DC59" s="396" t="n">
-        <v>0.009375041997651625</v>
+        <v>0.009375041997651623</v>
       </c>
       <c r="DD59" s="397" t="n">
-        <v>0.009757353086509017</v>
+        <v>0.00975735308650902</v>
       </c>
       <c r="DE59" s="397" t="n">
         <v>0.01026840829288288</v>
@@ -14271,19 +14271,19 @@
         <v>5144414</v>
       </c>
       <c r="CW60" s="102" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="CY60" s="103" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="CZ60" s="103" t="n">
-        <v>174.2565804322958</v>
+        <v>174.2565804322947</v>
       </c>
       <c r="DA60" s="104" t="n">
-        <v>192.9148478658448</v>
+        <v>192.9148478658435</v>
       </c>
       <c r="DC60" s="396" t="n">
         <v>0.01079627364896513</v>
@@ -14298,7 +14298,7 @@
         <v>0.01164983319294991</v>
       </c>
       <c r="DG60" s="398" t="n">
-        <v>0.01169494806446233</v>
+        <v>0.01169494806446232</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" thickBot="1">
@@ -14526,7 +14526,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="BY61" s="212" t="n">
-        <v>23768.57981326902</v>
+        <v>23768.57981326903</v>
       </c>
       <c r="BZ61" s="212" t="n">
         <v>26311.55657416943</v>
@@ -14538,7 +14538,7 @@
         <v>32577.47994622752</v>
       </c>
       <c r="CC61" s="212" t="n">
-        <v>24529.58511451443</v>
+        <v>24529.58511451442</v>
       </c>
       <c r="CD61" s="212" t="n">
         <v>27059.18855224806</v>
@@ -14580,34 +14580,34 @@
         <v>837210</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>950.5574286398318</v>
+        <v>950.5574286398316</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="DC61" s="422" t="n">
-        <v>0.02947412316679579</v>
+        <v>0.0294741231667958</v>
       </c>
       <c r="DD61" s="423" t="n">
-        <v>0.03031253335912444</v>
+        <v>0.03031253335912443</v>
       </c>
       <c r="DE61" s="423" t="n">
-        <v>0.03101698224883411</v>
+        <v>0.0310169822488341</v>
       </c>
       <c r="DF61" s="423" t="n">
         <v>0.03114673314234719</v>
       </c>
       <c r="DG61" s="424" t="n">
-        <v>0.03202818225091575</v>
+        <v>0.03202818225091576</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" thickBot="1">
@@ -14889,19 +14889,19 @@
         <v>60466650</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027919</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875293</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.789813563166</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15781,7 +15781,7 @@
         <v>0.721646058437451</v>
       </c>
       <c r="CB67" s="464" t="n">
-        <v>0.7433596047961799</v>
+        <v>0.74335960479618</v>
       </c>
       <c r="CC67" s="199" t="n">
         <v>101965.7843942914</v>
@@ -15796,7 +15796,7 @@
         <v>135489.5155371729</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>150601.7080481506</v>
+        <v>150601.7080481507</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16038,16 +16038,16 @@
         <v>0.6509786380086139</v>
       </c>
       <c r="BZ68" s="463" t="n">
-        <v>0.6763319833499947</v>
+        <v>0.6763319833499948</v>
       </c>
       <c r="CA68" s="463" t="n">
         <v>0.6929421555022224</v>
       </c>
       <c r="CB68" s="464" t="n">
-        <v>0.714253308151782</v>
+        <v>0.7142533081517821</v>
       </c>
       <c r="CC68" s="197" t="n">
-        <v>19824.70474124874</v>
+        <v>19824.70474124875</v>
       </c>
       <c r="CD68" s="190" t="n">
         <v>21459.97596939845</v>
@@ -16304,13 +16304,13 @@
         <v>0.7144401067588553</v>
       </c>
       <c r="CA69" s="463" t="n">
-        <v>0.7384979676256798</v>
+        <v>0.7384979676256799</v>
       </c>
       <c r="CB69" s="464" t="n">
         <v>0.7670945895092585</v>
       </c>
       <c r="CC69" s="197" t="n">
-        <v>7684.536209253197</v>
+        <v>7684.536209253199</v>
       </c>
       <c r="CD69" s="190" t="n">
         <v>8535.248537910204</v>
@@ -16558,10 +16558,10 @@
         <v>25652.86382685493</v>
       </c>
       <c r="BX70" s="466" t="n">
-        <v>0.7000174703382454</v>
+        <v>0.7000174703382455</v>
       </c>
       <c r="BY70" s="467" t="n">
-        <v>0.7171947087988734</v>
+        <v>0.7171947087988735</v>
       </c>
       <c r="BZ70" s="467" t="n">
         <v>0.7283718889056494</v>
@@ -16821,25 +16821,25 @@
         <v>212088.9797710218</v>
       </c>
       <c r="BX71" s="466" t="n">
-        <v>0.6479510023941699</v>
+        <v>0.64795100239417</v>
       </c>
       <c r="BY71" s="467" t="n">
         <v>0.6803922139883306</v>
       </c>
       <c r="BZ71" s="467" t="n">
-        <v>0.703403312819713</v>
+        <v>0.7034033128197131</v>
       </c>
       <c r="CA71" s="467" t="n">
         <v>0.7205849213555851</v>
       </c>
       <c r="CB71" s="468" t="n">
-        <v>0.7425296329386261</v>
+        <v>0.7425296329386262</v>
       </c>
       <c r="CC71" s="212" t="n">
         <v>144562.5965727818</v>
       </c>
       <c r="CD71" s="212" t="n">
-        <v>160318.027983494</v>
+        <v>160318.0279834941</v>
       </c>
       <c r="CE71" s="212" t="n">
         <v>175838.9999376462</v>
@@ -18502,7 +18502,7 @@
         <v>0</v>
       </c>
       <c r="BX79" s="466" t="n">
-        <v>0.1213412225632432</v>
+        <v>0.1213412225632433</v>
       </c>
       <c r="BY79" s="467" t="n">
         <v>0.1216078129107701</v>
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="C96" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D96" s="368" t="n">
         <v>141265555.356126</v>
@@ -20902,7 +20902,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H96" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I96" s="372" t="n">
         <v>859.4354544219096</v>
@@ -20922,7 +20922,7 @@
         </is>
       </c>
       <c r="T96" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U96" s="375" t="n">
         <v>141265555.356126</v>
@@ -20937,7 +20937,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y96" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z96" s="372" t="n">
         <v>859.4354544219096</v>
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="AK96" s="506" t="n">
-        <v>126617344.103984</v>
+        <v>126640275.655196</v>
       </c>
       <c r="AL96" s="368" t="n">
         <v>141248374.026126</v>
@@ -20972,7 +20972,7 @@
         <v>194794539.810586</v>
       </c>
       <c r="AP96" s="381" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="AQ96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -20987,7 +20987,7 @@
         <v>989.1578434898606</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>109383903.5623858</v>
+        <v>109406835.1135978</v>
       </c>
       <c r="AV96" s="375" t="n">
         <v>125092448.4504666</v>
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="BB96" s="391" t="n">
-        <v>126617344.103984</v>
+        <v>126640275.655196</v>
       </c>
       <c r="BC96" s="375" t="n">
         <v>141248374.026126</v>
@@ -21022,7 +21022,7 @@
         <v>194794539.810586</v>
       </c>
       <c r="BG96" s="386" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="BH96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -21042,7 +21042,7 @@
         </is>
       </c>
       <c r="BS96" s="391" t="n">
-        <v>127420166.0637988</v>
+        <v>127443243.0133605</v>
       </c>
       <c r="BT96" s="375" t="n">
         <v>143078447.3193804</v>
@@ -21057,7 +21057,7 @@
         <v>200399456.4644708</v>
       </c>
       <c r="BX96" s="386" t="n">
-        <v>808.0292638046026</v>
+        <v>808.1756052444333</v>
       </c>
       <c r="BY96" s="372" t="n">
         <v>859.3947033664067</v>
@@ -21087,10 +21087,10 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>91214772.24990706</v>
+        <v>91237642.06254111</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>104988005.1745432</v>
+        <v>104988005.1745433</v>
       </c>
       <c r="DE96" s="375" t="n">
         <v>118016580.220932</v>
@@ -21099,7 +21099,7 @@
         <v>131624915.6046412</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>150667262.2450605</v>
+        <v>150667262.2450604</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="C97" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D97" s="368" t="n">
         <v>53602589.259965</v>
@@ -21129,7 +21129,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H97" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="T97" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U97" s="375" t="n">
         <v>53602589.259965</v>
@@ -21164,7 +21164,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y97" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21184,7 +21184,7 @@
         </is>
       </c>
       <c r="AK97" s="506" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="AL97" s="368" t="n">
         <v>53602589.259965</v>
@@ -21199,7 +21199,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="AP97" s="381" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="AQ97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21214,7 +21214,7 @@
         <v>1911.879093778504</v>
       </c>
       <c r="AU97" s="379" t="n">
-        <v>41689376.3923699</v>
+        <v>41695853.95444989</v>
       </c>
       <c r="AV97" s="375" t="n">
         <v>46504050.28654232</v>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="BB97" s="391" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="BC97" s="375" t="n">
         <v>53602589.259965</v>
@@ -21249,7 +21249,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="BG97" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BH97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21269,7 +21269,7 @@
         </is>
       </c>
       <c r="BS97" s="391" t="n">
-        <v>50132747.34533089</v>
+        <v>50139289.15891635</v>
       </c>
       <c r="BT97" s="375" t="n">
         <v>54567686.23949162</v>
@@ -21284,7 +21284,7 @@
         <v>75327072.67031722</v>
       </c>
       <c r="BX97" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BY97" s="372" t="n">
         <v>1655.286013279789</v>
@@ -21314,16 +21314,16 @@
         <v>0</v>
       </c>
       <c r="DC97" s="391" t="n">
-        <v>34750578.12386221</v>
+        <v>34757061.96014754</v>
       </c>
       <c r="DD97" s="375" t="n">
         <v>39059424.72252001</v>
       </c>
       <c r="DE97" s="375" t="n">
-        <v>43435991.25102002</v>
+        <v>43435991.25102001</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>48299721.45663889</v>
+        <v>48299721.45663891</v>
       </c>
       <c r="DG97" s="392" t="n">
         <v>55445858.27455462</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="C98" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D98" s="368" t="n">
         <v>30609035.168748</v>
@@ -21356,7 +21356,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H98" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="T98" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U98" s="375" t="n">
         <v>30609035.168748</v>
@@ -21391,7 +21391,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y98" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="AK98" s="506" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="AL98" s="368" t="n">
         <v>30609035.168748</v>
@@ -21426,7 +21426,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="AP98" s="381" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="AQ98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21441,7 +21441,7 @@
         <v>2797.787340780611</v>
       </c>
       <c r="AU98" s="379" t="n">
-        <v>22190726.19047777</v>
+        <v>22193533.13404577</v>
       </c>
       <c r="AV98" s="375" t="n">
         <v>25281751.22556119</v>
@@ -21461,7 +21461,7 @@
         </is>
       </c>
       <c r="BB98" s="391" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="BC98" s="375" t="n">
         <v>30609035.168748</v>
@@ -21476,7 +21476,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="BG98" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BH98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="BS98" s="391" t="n">
-        <v>27524559.52788378</v>
+        <v>27527373.59848597</v>
       </c>
       <c r="BT98" s="375" t="n">
         <v>30832725.79709084</v>
@@ -21511,7 +21511,7 @@
         <v>44556567.68141378</v>
       </c>
       <c r="BX98" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BY98" s="372" t="n">
         <v>2485.680463849397</v>
@@ -21541,16 +21541,16 @@
         <v>0</v>
       </c>
       <c r="DC98" s="391" t="n">
-        <v>18936636.22699493</v>
+        <v>18939430.84554149</v>
       </c>
       <c r="DD98" s="375" t="n">
         <v>21655757.83449386</v>
       </c>
       <c r="DE98" s="375" t="n">
-        <v>24654357.0821007</v>
+        <v>24654357.08210071</v>
       </c>
       <c r="DF98" s="375" t="n">
-        <v>28165319.75427984</v>
+        <v>28165319.75427985</v>
       </c>
       <c r="DG98" s="392" t="n">
         <v>32487496.48841153</v>
@@ -21723,7 +21723,7 @@
         </is>
       </c>
       <c r="BS99" s="419" t="n">
-        <v>269873908.3383856</v>
+        <v>269873908.3383855</v>
       </c>
       <c r="BT99" s="420" t="n">
         <v>304550625.5077929</v>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>163797061.6705361</v>
+        <v>163797061.670536</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>188089957.4893995</v>
+        <v>188089957.4893994</v>
       </c>
       <c r="DE99" s="420" t="n">
         <v>215978942.3423741</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>246346883.7616733</v>
+        <v>246346883.7616732</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>286688358.6587338</v>
+        <v>286688358.6587337</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="C100" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D100" s="425" t="n">
         <v>538493761.125447</v>
@@ -21810,7 +21810,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="H100" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I100" s="427" t="n">
         <v>2306.219676493023</v>
@@ -21830,7 +21830,7 @@
         </is>
       </c>
       <c r="T100" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U100" s="430" t="n">
         <v>538493761.125447</v>
@@ -21845,7 +21845,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="Y100" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z100" s="433" t="n">
         <v>2306.219676493023</v>
@@ -21865,7 +21865,7 @@
         </is>
       </c>
       <c r="AK100" s="435" t="n">
-        <v>481161614.853311</v>
+        <v>481193830.910171</v>
       </c>
       <c r="AL100" s="408" t="n">
         <v>538476579.7954481</v>
@@ -21880,7 +21880,7 @@
         <v>769448594.491678</v>
       </c>
       <c r="AP100" s="436" t="n">
-        <v>2163.756050827067</v>
+        <v>2163.900924578033</v>
       </c>
       <c r="AQ100" s="437" t="n">
         <v>2306.266576508939</v>
@@ -21895,7 +21895,7 @@
         <v>2709.041941860333</v>
       </c>
       <c r="AU100" s="435" t="n">
-        <v>379489526.4173334</v>
+        <v>379521742.4741934</v>
       </c>
       <c r="AV100" s="408" t="n">
         <v>433432828.6743559</v>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="BB100" s="439" t="n">
-        <v>481161614.853311</v>
+        <v>481193830.910171</v>
       </c>
       <c r="BC100" s="440" t="n">
         <v>538476579.7954481</v>
@@ -21930,7 +21930,7 @@
         <v>769448594.491678</v>
       </c>
       <c r="BG100" s="442" t="n">
-        <v>2163.756050827067</v>
+        <v>2163.900924578033</v>
       </c>
       <c r="BH100" s="443" t="n">
         <v>2306.266576508939</v>
@@ -21950,13 +21950,13 @@
         </is>
       </c>
       <c r="BS100" s="439" t="n">
-        <v>474951381.275399</v>
+        <v>474983814.1091484</v>
       </c>
       <c r="BT100" s="440" t="n">
-        <v>533029484.8637557</v>
+        <v>533029484.8637558</v>
       </c>
       <c r="BU100" s="440" t="n">
-        <v>598231970.5696801</v>
+        <v>598231970.5696802</v>
       </c>
       <c r="BV100" s="440" t="n">
         <v>672371281.2531219</v>
@@ -21965,7 +21965,7 @@
         <v>766783160.6296258</v>
       </c>
       <c r="BX100" s="442" t="n">
-        <v>2128.802545622182</v>
+        <v>2128.947914394164</v>
       </c>
       <c r="BY100" s="443" t="n">
         <v>2262.185456552957</v>
@@ -21997,10 +21997,10 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>308699048.2713003</v>
+        <v>308731196.5387661</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>353793145.2209566</v>
+        <v>353793145.2209565</v>
       </c>
       <c r="DE100" s="440" t="n">
         <v>402085870.8964268</v>
@@ -22009,7 +22009,7 @@
         <v>454436840.5772332</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>525288975.6667604</v>
+        <v>525288975.6667603</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23081,34 +23081,34 @@
         <v>0</v>
       </c>
       <c r="BX108" s="197" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="BY108" s="190" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="BZ108" s="190" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="CA108" s="190" t="n">
-        <v>2615.148328173741</v>
+        <v>2615.148328173728</v>
       </c>
       <c r="CB108" s="198" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333039</v>
       </c>
       <c r="CC108" s="199" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="CD108" s="200" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="CE108" s="200" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="CF108" s="200" t="n">
-        <v>2615.148328173741</v>
+        <v>2615.148328173728</v>
       </c>
       <c r="CG108" s="201" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333039</v>
       </c>
       <c r="CI108" s="199" t="n">
         <v>0</v>
@@ -23138,19 +23138,19 @@
         <v>0</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>2615.148328173741</v>
+        <v>2615.148328173728</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333039</v>
       </c>
     </row>
     <row r="109">
@@ -23376,34 +23376,34 @@
         <v>0</v>
       </c>
       <c r="BX109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="BY109" s="190" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="BZ109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="CA109" s="190" t="n">
-        <v>446.7528256294408</v>
+        <v>446.7528256294383</v>
       </c>
       <c r="CB109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469131</v>
       </c>
       <c r="CC109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="CD109" s="190" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="CE109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="CF109" s="190" t="n">
-        <v>446.7528256294408</v>
+        <v>446.7528256294383</v>
       </c>
       <c r="CG109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469131</v>
       </c>
       <c r="CI109" s="197" t="n">
         <v>0</v>
@@ -23433,19 +23433,19 @@
         <v>0</v>
       </c>
       <c r="CW109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="CX109" s="190" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="CZ109" s="190" t="n">
-        <v>446.7528256294408</v>
+        <v>446.7528256294383</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469131</v>
       </c>
     </row>
     <row r="110">
@@ -23671,34 +23671,34 @@
         <v>0</v>
       </c>
       <c r="BX110" s="197" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="BY110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="BZ110" s="190" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="CA110" s="190" t="n">
-        <v>174.2565804322958</v>
+        <v>174.2565804322947</v>
       </c>
       <c r="CB110" s="198" t="n">
-        <v>192.9148478658448</v>
+        <v>192.9148478658435</v>
       </c>
       <c r="CC110" s="197" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="CD110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="CE110" s="190" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="CF110" s="190" t="n">
-        <v>174.2565804322958</v>
+        <v>174.2565804322947</v>
       </c>
       <c r="CG110" s="198" t="n">
-        <v>192.9148478658448</v>
+        <v>192.9148478658435</v>
       </c>
       <c r="CI110" s="197" t="n">
         <v>0</v>
@@ -23728,19 +23728,19 @@
         <v>0</v>
       </c>
       <c r="CW110" s="197" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="CY110" s="190" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="CZ110" s="190" t="n">
-        <v>174.2565804322958</v>
+        <v>174.2565804322947</v>
       </c>
       <c r="DA110" s="198" t="n">
-        <v>192.9148478658448</v>
+        <v>192.9148478658435</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" thickBot="1">
@@ -23966,34 +23966,34 @@
         <v>0</v>
       </c>
       <c r="BX111" s="211" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="BY111" s="212" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="BZ111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CA111" s="212" t="n">
-        <v>950.5574286398318</v>
+        <v>950.5574286398316</v>
       </c>
       <c r="CB111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CC111" s="212" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CD111" s="212" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="CE111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CF111" s="212" t="n">
-        <v>950.5574286398318</v>
+        <v>950.5574286398316</v>
       </c>
       <c r="CG111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CI111" s="211" t="n">
         <v>0</v>
@@ -24023,19 +24023,19 @@
         <v>0</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>950.5574286398318</v>
+        <v>950.5574286398316</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24261,34 +24261,34 @@
         <v>0</v>
       </c>
       <c r="BX112" s="221" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027919</v>
       </c>
       <c r="BY112" s="222" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="BZ112" s="222" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="CA112" s="222" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875293</v>
       </c>
       <c r="CB112" s="214" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.789813563166</v>
       </c>
       <c r="CC112" s="222" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027919</v>
       </c>
       <c r="CD112" s="222" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="CE112" s="222" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="CF112" s="222" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875293</v>
       </c>
       <c r="CG112" s="214" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.789813563166</v>
       </c>
       <c r="CI112" s="349" t="n">
         <v>0</v>
@@ -24318,19 +24318,19 @@
         <v>0</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027919</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875293</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.789813563166</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -30296,28 +30296,28 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>1587676.557721971</v>
+        <v>1587964.100369055</v>
       </c>
       <c r="BT146" s="375" t="n">
-        <v>1859004.22412202</v>
+        <v>1859004.22412201</v>
       </c>
       <c r="BU146" s="375" t="n">
-        <v>2152911.242960695</v>
+        <v>2152911.242960684</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>2465352.406803232</v>
+        <v>2465352.40680322</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>2848333.99196949</v>
+        <v>2848333.991969475</v>
       </c>
       <c r="BX146" s="386" t="n">
-        <v>808.0292638046028</v>
+        <v>808.1756052444334</v>
       </c>
       <c r="BY146" s="372" t="n">
-        <v>859.3947033664069</v>
+        <v>859.3947033664067</v>
       </c>
       <c r="BZ146" s="372" t="n">
-        <v>905.0157360461151</v>
+        <v>905.0157360461154</v>
       </c>
       <c r="CA146" s="372" t="n">
         <v>942.7199139120659</v>
@@ -30326,19 +30326,19 @@
         <v>989.1578434898606</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>1587676.557721971</v>
+        <v>1587964.100369055</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>1859004.22412202</v>
+        <v>1859004.22412201</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>2152911.242960695</v>
+        <v>2152911.242960684</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>2465352.406803232</v>
+        <v>2465352.40680322</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>2848333.99196949</v>
+        <v>2848333.991969475</v>
       </c>
     </row>
     <row r="147">
@@ -30488,22 +30488,22 @@
         </is>
       </c>
       <c r="BS147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542587.089917258</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>615908.7206401865</v>
+        <v>615908.7206401831</v>
       </c>
       <c r="BU147" s="375" t="n">
-        <v>709964.9410228857</v>
+        <v>709964.9410228818</v>
       </c>
       <c r="BV147" s="375" t="n">
-        <v>811268.0615034171</v>
+        <v>811268.0615034124</v>
       </c>
       <c r="BW147" s="392" t="n">
-        <v>938677.3753287442</v>
+        <v>938677.3753287386</v>
       </c>
       <c r="BX147" s="386" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="BY147" s="372" t="n">
         <v>1655.286013279789</v>
@@ -30518,19 +30518,19 @@
         <v>1911.879093778504</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542587.089917258</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>615908.7206401865</v>
+        <v>615908.7206401831</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>709964.9410228857</v>
+        <v>709964.9410228818</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>811268.0615034171</v>
+        <v>811268.0615034124</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>938677.3753287442</v>
+        <v>938677.3753287386</v>
       </c>
     </row>
     <row r="148">
@@ -30680,22 +30680,22 @@
         </is>
       </c>
       <c r="BS148" s="391" t="n">
-        <v>307001.1257340743</v>
+        <v>307032.5130789595</v>
       </c>
       <c r="BT148" s="375" t="n">
-        <v>355493.4875790518</v>
+        <v>355493.4875790495</v>
       </c>
       <c r="BU148" s="375" t="n">
-        <v>411894.9442355951</v>
+        <v>411894.9442355924</v>
       </c>
       <c r="BV148" s="375" t="n">
-        <v>471930.3932149258</v>
+        <v>471930.3932149229</v>
       </c>
       <c r="BW148" s="392" t="n">
-        <v>539734.7192076782</v>
+        <v>539734.7192076744</v>
       </c>
       <c r="BX148" s="386" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="BY148" s="372" t="n">
         <v>2485.680463849397</v>
@@ -30704,25 +30704,25 @@
         <v>2610.628996407854</v>
       </c>
       <c r="CA148" s="372" t="n">
-        <v>2708.250053135214</v>
+        <v>2708.250053135215</v>
       </c>
       <c r="CB148" s="387" t="n">
-        <v>2797.787340780611</v>
+        <v>2797.78734078061</v>
       </c>
       <c r="CW148" s="391" t="n">
-        <v>307001.1257340743</v>
+        <v>307032.5130789595</v>
       </c>
       <c r="CX148" s="375" t="n">
-        <v>355493.4875790518</v>
+        <v>355493.4875790495</v>
       </c>
       <c r="CY148" s="375" t="n">
-        <v>411894.9442355951</v>
+        <v>411894.9442355924</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>471930.3932149258</v>
+        <v>471930.3932149229</v>
       </c>
       <c r="DA148" s="392" t="n">
-        <v>539734.7192076782</v>
+        <v>539734.7192076744</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" thickBot="1">
@@ -30872,10 +30872,10 @@
         </is>
       </c>
       <c r="BS149" s="419" t="n">
-        <v>8313320.311779676</v>
+        <v>8313320.311779679</v>
       </c>
       <c r="BT149" s="420" t="n">
-        <v>9656231.481041212</v>
+        <v>9656231.481041208</v>
       </c>
       <c r="BU149" s="420" t="n">
         <v>11180930.84122668</v>
@@ -30899,13 +30899,13 @@
         <v>13374.31064525911</v>
       </c>
       <c r="CB149" s="418" t="n">
-        <v>13705.78892383384</v>
+        <v>13705.78892383383</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>8313320.311779676</v>
+        <v>8313320.311779679</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>9656231.481041212</v>
+        <v>9656231.481041208</v>
       </c>
       <c r="CY149" s="420" t="n">
         <v>11180930.84122668</v>
@@ -31064,49 +31064,49 @@
         </is>
       </c>
       <c r="BS150" s="439" t="n">
-        <v>10750514.29229461</v>
+        <v>10750904.01514495</v>
       </c>
       <c r="BT150" s="440" t="n">
-        <v>12486637.91338247</v>
+        <v>12486637.91338245</v>
       </c>
       <c r="BU150" s="440" t="n">
-        <v>14455701.96944586</v>
+        <v>14455701.96944584</v>
       </c>
       <c r="BV150" s="440" t="n">
-        <v>16461601.19830941</v>
+        <v>16461601.19830938</v>
       </c>
       <c r="BW150" s="441" t="n">
-        <v>19311960.75363057</v>
+        <v>19311960.75363054</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>3459.703149058871</v>
+        <v>3459.82856867472</v>
       </c>
       <c r="BY150" s="443" t="n">
-        <v>3638.429096094124</v>
+        <v>3638.429096094134</v>
       </c>
       <c r="BZ150" s="443" t="n">
-        <v>3805.614893757383</v>
+        <v>3805.614893757394</v>
       </c>
       <c r="CA150" s="443" t="n">
-        <v>3931.865569523024</v>
+        <v>3931.865569523034</v>
       </c>
       <c r="CB150" s="444" t="n">
-        <v>4147.054414477394</v>
+        <v>4147.054414477407</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>10750514.29229461</v>
+        <v>10750904.01514495</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>12486637.91338247</v>
+        <v>12486637.91338245</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>14455701.96944586</v>
+        <v>14455701.96944584</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>16461601.19830941</v>
+        <v>16461601.19830938</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>19311960.75363057</v>
+        <v>19311960.75363054</v>
       </c>
     </row>
     <row r="151">
@@ -34174,7 +34174,7 @@
         </is>
       </c>
       <c r="AK172" s="194" t="n">
-        <v>1107587.632076551</v>
+        <v>1107587.63207655</v>
       </c>
       <c r="AL172" s="179" t="n">
         <v>1120865.475386316</v>
@@ -34186,10 +34186,10 @@
         <v>1140493.683591617</v>
       </c>
       <c r="AO172" s="195" t="n">
-        <v>1151005.129087162</v>
+        <v>1151005.129087163</v>
       </c>
       <c r="AP172" s="194" t="n">
-        <v>156698.958534845</v>
+        <v>156698.958534844</v>
       </c>
       <c r="AQ172" s="179" t="n">
         <v>164357.975995239</v>
@@ -34204,7 +34204,7 @@
         <v>196929.682247454</v>
       </c>
       <c r="AU172" s="190" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611394</v>
       </c>
       <c r="AV172" s="190" t="n">
         <v>1285223.451381555</v>
@@ -34216,7 +34216,7 @@
         <v>1323790.439580504</v>
       </c>
       <c r="AY172" s="196" t="n">
-        <v>1347934.811334616</v>
+        <v>1347934.811334617</v>
       </c>
       <c r="BA172" s="83" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         </is>
       </c>
       <c r="BB172" s="197" t="n">
-        <v>1107587.632076551</v>
+        <v>1107587.63207655</v>
       </c>
       <c r="BC172" s="190" t="n">
         <v>1120865.475386316</v>
@@ -34236,10 +34236,10 @@
         <v>1140493.683591617</v>
       </c>
       <c r="BF172" s="198" t="n">
-        <v>1151005.129087162</v>
+        <v>1151005.129087163</v>
       </c>
       <c r="BG172" s="197" t="n">
-        <v>156698.958534845</v>
+        <v>156698.958534844</v>
       </c>
       <c r="BH172" s="190" t="n">
         <v>164357.975995239</v>
@@ -34254,7 +34254,7 @@
         <v>196929.682247454</v>
       </c>
       <c r="BL172" s="199" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611394</v>
       </c>
       <c r="BM172" s="200" t="n">
         <v>1285223.451381555</v>
@@ -34266,7 +34266,7 @@
         <v>1323790.439580504</v>
       </c>
       <c r="BP172" s="201" t="n">
-        <v>1347934.811334616</v>
+        <v>1347934.811334617</v>
       </c>
       <c r="BR172" s="83" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="BS172" s="197" t="n">
-        <v>1104629.20145452</v>
+        <v>1104629.201454519</v>
       </c>
       <c r="BT172" s="190" t="n">
         <v>1116572.829058702</v>
@@ -34286,10 +34286,10 @@
         <v>1133424.642644257</v>
       </c>
       <c r="BW172" s="198" t="n">
-        <v>1142459.222383301</v>
+        <v>1142459.222383302</v>
       </c>
       <c r="BX172" s="197" t="n">
-        <v>157692.5140850912</v>
+        <v>157692.5140850902</v>
       </c>
       <c r="BY172" s="190" t="n">
         <v>166487.4670033711</v>
@@ -34301,10 +34301,10 @@
         <v>187750.6486080731</v>
       </c>
       <c r="CB172" s="198" t="n">
-        <v>202596.0343779826</v>
+        <v>202596.0343779827</v>
       </c>
       <c r="CC172" s="199" t="n">
-        <v>1262321.715539611</v>
+        <v>1262321.715539609</v>
       </c>
       <c r="CD172" s="200" t="n">
         <v>1283060.296062073</v>
@@ -34316,7 +34316,7 @@
         <v>1321175.29125233</v>
       </c>
       <c r="CG172" s="201" t="n">
-        <v>1345055.256761284</v>
+        <v>1345055.256761285</v>
       </c>
       <c r="CI172" s="199" t="n">
         <v>1070496</v>
@@ -34471,7 +34471,7 @@
         <v>31830.698197501</v>
       </c>
       <c r="AQ173" s="179" t="n">
-        <v>32382.675157112</v>
+        <v>32382.675157113</v>
       </c>
       <c r="AR173" s="179" t="n">
         <v>33517.010563425</v>
@@ -34483,16 +34483,16 @@
         <v>38024.309718277</v>
       </c>
       <c r="AU173" s="190" t="n">
-        <v>283592.7910795145</v>
+        <v>283592.7910795146</v>
       </c>
       <c r="AV173" s="190" t="n">
-        <v>285965.6858407335</v>
+        <v>285965.6858407346</v>
       </c>
       <c r="AW173" s="190" t="n">
-        <v>288420.5176779933</v>
+        <v>288420.5176779931</v>
       </c>
       <c r="AX173" s="190" t="n">
-        <v>290894.5708527532</v>
+        <v>290894.5708527533</v>
       </c>
       <c r="AY173" s="196" t="n">
         <v>294346.5865991117</v>
@@ -34521,7 +34521,7 @@
         <v>31830.698197501</v>
       </c>
       <c r="BH173" s="190" t="n">
-        <v>32382.675157112</v>
+        <v>32382.675157113</v>
       </c>
       <c r="BI173" s="190" t="n">
         <v>33517.010563425</v>
@@ -34536,7 +34536,7 @@
         <v>283592.791079515</v>
       </c>
       <c r="BM173" s="190" t="n">
-        <v>285965.685840734</v>
+        <v>285965.685840735</v>
       </c>
       <c r="BN173" s="190" t="n">
         <v>288420.517677993</v>
@@ -34571,7 +34571,7 @@
         <v>32146.42968012392</v>
       </c>
       <c r="BY173" s="190" t="n">
-        <v>32965.71456648575</v>
+        <v>32965.71456648678</v>
       </c>
       <c r="BZ173" s="190" t="n">
         <v>34361.04780651606</v>
@@ -34586,7 +34586,7 @@
         <v>283244.9154310119</v>
       </c>
       <c r="CD173" s="190" t="n">
-        <v>285593.5998593997</v>
+        <v>285593.5998594008</v>
       </c>
       <c r="CE173" s="190" t="n">
         <v>288012.8098743621</v>
@@ -34768,7 +34768,7 @@
         <v>69762.95644698211</v>
       </c>
       <c r="AW174" s="190" t="n">
-        <v>71104.911504344</v>
+        <v>71104.91150434389</v>
       </c>
       <c r="AX174" s="190" t="n">
         <v>72595.7203454608</v>
@@ -34847,7 +34847,7 @@
         <v>58422.498776601</v>
       </c>
       <c r="BX174" s="197" t="n">
-        <v>11715.21771961826</v>
+        <v>11715.21771961827</v>
       </c>
       <c r="BY174" s="190" t="n">
         <v>12404.13892512452</v>
@@ -34862,7 +34862,7 @@
         <v>15925.64489480927</v>
       </c>
       <c r="CC174" s="197" t="n">
-        <v>68390.13071195326</v>
+        <v>68390.13071195327</v>
       </c>
       <c r="CD174" s="190" t="n">
         <v>69619.93987958752</v>
@@ -35290,7 +35290,7 @@
         </is>
       </c>
       <c r="AK176" s="206" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="AL176" s="207" t="n">
         <v>1435280.798812628</v>
@@ -35302,13 +35302,13 @@
         <v>1458495.409587526</v>
       </c>
       <c r="AO176" s="208" t="n">
-        <v>1470806.519645696</v>
+        <v>1470806.519645697</v>
       </c>
       <c r="AP176" s="206" t="n">
-        <v>222373.319148925</v>
+        <v>222373.319148924</v>
       </c>
       <c r="AQ176" s="207" t="n">
-        <v>233484.101656683</v>
+        <v>233484.101656684</v>
       </c>
       <c r="AR176" s="207" t="n">
         <v>246424.951742656</v>
@@ -35320,19 +35320,19 @@
         <v>284029.782855784</v>
       </c>
       <c r="AU176" s="207" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447798</v>
       </c>
       <c r="AV176" s="207" t="n">
-        <v>1668764.900469311</v>
+        <v>1668764.900469312</v>
       </c>
       <c r="AW176" s="207" t="n">
         <v>1695104.119977999</v>
       </c>
       <c r="AX176" s="207" t="n">
-        <v>1721390.552400128</v>
+        <v>1721390.552400127</v>
       </c>
       <c r="AY176" s="208" t="n">
-        <v>1754836.30250148</v>
+        <v>1754836.302501481</v>
       </c>
       <c r="BA176" s="155" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="BB176" s="221" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="BC176" s="222" t="n">
         <v>1435280.798812628</v>
@@ -35352,13 +35352,13 @@
         <v>1458495.409587526</v>
       </c>
       <c r="BF176" s="214" t="n">
-        <v>1470806.519645696</v>
+        <v>1470806.519645697</v>
       </c>
       <c r="BG176" s="221" t="n">
-        <v>222373.319148925</v>
+        <v>222373.319148924</v>
       </c>
       <c r="BH176" s="222" t="n">
-        <v>233484.101656683</v>
+        <v>233484.101656684</v>
       </c>
       <c r="BI176" s="222" t="n">
         <v>246424.951742656</v>
@@ -35370,10 +35370,10 @@
         <v>284029.782855784</v>
       </c>
       <c r="BL176" s="222" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447798</v>
       </c>
       <c r="BM176" s="222" t="n">
-        <v>1668764.900469311</v>
+        <v>1668764.900469312</v>
       </c>
       <c r="BN176" s="222" t="n">
         <v>1695104.119977999</v>
@@ -35382,7 +35382,7 @@
         <v>1721390.552400127</v>
       </c>
       <c r="BP176" s="214" t="n">
-        <v>1754836.30250148</v>
+        <v>1754836.302501481</v>
       </c>
       <c r="BR176" s="155" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         </is>
       </c>
       <c r="BS176" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BT176" s="222" t="n">
         <v>1429707.124045061</v>
@@ -35402,13 +35402,13 @@
         <v>1449303.184037709</v>
       </c>
       <c r="BW176" s="214" t="n">
-        <v>1459680.857487838</v>
+        <v>1459680.857487839</v>
       </c>
       <c r="BX176" s="221" t="n">
-        <v>223107.2967522648</v>
+        <v>223107.2967522638</v>
       </c>
       <c r="BY176" s="222" t="n">
-        <v>235625.9003085975</v>
+        <v>235625.9003085986</v>
       </c>
       <c r="BZ176" s="222" t="n">
         <v>249983.1842321427</v>
@@ -35420,7 +35420,7 @@
         <v>290498.6552000805</v>
       </c>
       <c r="CC176" s="222" t="n">
-        <v>1638486.346796772</v>
+        <v>1638486.34679677</v>
       </c>
       <c r="CD176" s="222" t="n">
         <v>1665333.024353659</v>
@@ -35432,7 +35432,7 @@
         <v>1717203.837237251</v>
       </c>
       <c r="CG176" s="214" t="n">
-        <v>1750179.512687918</v>
+        <v>1750179.512687919</v>
       </c>
       <c r="CI176" s="349" t="n">
         <v>1375594</v>
@@ -38446,7 +38446,7 @@
         </is>
       </c>
       <c r="AK190" s="194" t="n">
-        <v>1107587.632076551</v>
+        <v>1107587.63207655</v>
       </c>
       <c r="AL190" s="179" t="n">
         <v>1120865.475386316</v>
@@ -38458,37 +38458,37 @@
         <v>1140493.683591617</v>
       </c>
       <c r="AO190" s="195" t="n">
-        <v>1151005.129087162</v>
+        <v>1151005.129087163</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>156698.9585348447</v>
+        <v>156698.958534844</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>164357.9759952394</v>
+        <v>164357.9759952388</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>172744.4396161547</v>
+        <v>172744.439616155</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>183296.7559888874</v>
+        <v>183296.7559888869</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>196929.6822474545</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611394</v>
       </c>
       <c r="AV190" s="190" t="n">
         <v>1285223.451381555</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>1304795.66503686</v>
+        <v>1304795.665036861</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>1323790.439580505</v>
+        <v>1323790.439580503</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>1347934.811334617</v>
+        <v>1347934.811334618</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         </is>
       </c>
       <c r="BB190" s="197" t="n">
-        <v>1107587.632076551</v>
+        <v>1107587.63207655</v>
       </c>
       <c r="BC190" s="190" t="n">
         <v>1120865.475386316</v>
@@ -38508,25 +38508,25 @@
         <v>1140493.683591617</v>
       </c>
       <c r="BF190" s="198" t="n">
-        <v>1151005.129087162</v>
+        <v>1151005.129087163</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>156698.9585348447</v>
+        <v>156698.958534844</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>164357.9759952394</v>
+        <v>164357.9759952388</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>172744.4396161547</v>
+        <v>172744.439616155</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>183296.7559888874</v>
+        <v>183296.7559888869</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>196929.6822474545</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611394</v>
       </c>
       <c r="BM190" s="200" t="n">
         <v>1285223.451381555</v>
@@ -38546,7 +38546,7 @@
         </is>
       </c>
       <c r="BS190" s="197" t="n">
-        <v>1104629.20145452</v>
+        <v>1104629.201454519</v>
       </c>
       <c r="BT190" s="190" t="n">
         <v>1116572.829058702</v>
@@ -38558,25 +38558,25 @@
         <v>1133424.642644257</v>
       </c>
       <c r="BW190" s="198" t="n">
-        <v>1142459.222383301</v>
+        <v>1142459.222383302</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>157692.5140850909</v>
+        <v>157692.5140850903</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>166487.4670033715</v>
+        <v>166487.4670033709</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>176028.3867151062</v>
+        <v>176028.3867151065</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>187750.6486080735</v>
+        <v>187750.648608073</v>
       </c>
       <c r="CB190" s="198" t="n">
         <v>202596.0343779831</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>1262321.715539611</v>
+        <v>1262321.715539609</v>
       </c>
       <c r="CD190" s="200" t="n">
         <v>1283060.296062073</v>
@@ -38585,10 +38585,10 @@
         <v>1302416.798949552</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>1321175.291252331</v>
+        <v>1321175.29125233</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>1345055.256761284</v>
+        <v>1345055.256761285</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>1070496</v>
@@ -38618,31 +38618,31 @@
         <v>29501926</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178443</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>2163.155319482305</v>
+        <v>2163.155319482293</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>2378.866087308497</v>
+        <v>2378.866087308485</v>
       </c>
       <c r="CZ190" s="92" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173779</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>2879.554573332819</v>
+        <v>2879.554573332804</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.009848161142173373</v>
+        <v>0.009848161142173417</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.01024095992487896</v>
+        <v>0.010240959924879</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.01065955492972586</v>
+        <v>0.01065955492972584</v>
       </c>
       <c r="DF190" s="394" t="n">
-        <v>0.0109974095527448</v>
+        <v>0.01099740955274483</v>
       </c>
       <c r="DG190" s="395" t="n">
         <v>0.01119286179102339</v>
@@ -38770,31 +38770,31 @@
         <v>256322.276880835</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>31830.69819750121</v>
+        <v>31830.6981975012</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.6751571125</v>
       </c>
       <c r="AR191" s="179" t="n">
         <v>33517.01056342496</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>35440.16241287874</v>
+        <v>35440.16241287877</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>38024.30971827687</v>
+        <v>38024.30971827685</v>
       </c>
       <c r="AU191" s="190" t="n">
-        <v>283592.7910795147</v>
+        <v>283592.7910795148</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>285965.6858407339</v>
+        <v>285965.685840734</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>288420.5176779932</v>
+        <v>288420.517677993</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>290894.5708527529</v>
+        <v>290894.5708527531</v>
       </c>
       <c r="AY191" s="196" t="n">
         <v>294346.5865991116</v>
@@ -38820,25 +38820,25 @@
         <v>256322.276880835</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>31830.69819750121</v>
+        <v>31830.6981975012</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.6751571125</v>
       </c>
       <c r="BI191" s="190" t="n">
         <v>33517.01056342496</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>35440.16241287874</v>
+        <v>35440.16241287877</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>38024.30971827687</v>
+        <v>38024.30971827685</v>
       </c>
       <c r="BL191" s="197" t="n">
         <v>283592.7910795152</v>
       </c>
       <c r="BM191" s="190" t="n">
-        <v>285965.6858407344</v>
+        <v>285965.6858407345</v>
       </c>
       <c r="BN191" s="190" t="n">
         <v>288420.5176779929</v>
@@ -38847,7 +38847,7 @@
         <v>290894.5708527528</v>
       </c>
       <c r="BP191" s="198" t="n">
-        <v>294346.5865991119</v>
+        <v>294346.5865991118</v>
       </c>
       <c r="BR191" s="101" t="inlineStr">
         <is>
@@ -38870,22 +38870,22 @@
         <v>254456.119521797</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>32146.42968012413</v>
+        <v>32146.42968012412</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>32965.71456648616</v>
+        <v>32965.71456648627</v>
       </c>
       <c r="BZ191" s="190" t="n">
         <v>34361.04780651602</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>36546.78659560294</v>
+        <v>36546.78659560297</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>39399.49598066847</v>
+        <v>39399.49598066845</v>
       </c>
       <c r="CC191" s="197" t="n">
-        <v>283244.9154310122</v>
+        <v>283244.9154310121</v>
       </c>
       <c r="CD191" s="190" t="n">
         <v>285593.5998594002</v>
@@ -38894,7 +38894,7 @@
         <v>288012.809874362</v>
       </c>
       <c r="CF191" s="190" t="n">
-        <v>290447.8180271229</v>
+        <v>290447.818027123</v>
       </c>
       <c r="CG191" s="198" t="n">
         <v>293855.6155024655</v>
@@ -38927,25 +38927,25 @@
         <v>24983100</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031423</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>372.0859813342884</v>
+        <v>372.0859813342864</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314235</v>
       </c>
       <c r="CZ191" s="103" t="n">
-        <v>446.7528256294974</v>
+        <v>446.752825629495</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467678</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.009375041997798532</v>
+        <v>0.009375041997798534</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.00975735308647515</v>
+        <v>0.009757353086475122</v>
       </c>
       <c r="DE191" s="397" t="n">
         <v>0.01026840829275269</v>
@@ -39079,34 +39079,34 @@
         <v>58895.089087613</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>11685.54726389713</v>
+        <v>11685.54726389712</v>
       </c>
       <c r="AQ192" s="179" t="n">
         <v>12314.14721798622</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>13131.37395224124</v>
+        <v>13131.37395224121</v>
       </c>
       <c r="AS192" s="179" t="n">
-        <v>14239.36090163694</v>
+        <v>14239.36090163693</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>15645.96943166314</v>
+        <v>15645.96943166313</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>68520.79892571837</v>
+        <v>68520.79892571835</v>
       </c>
       <c r="AV192" s="190" t="n">
         <v>69762.95644698229</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>71104.91150434419</v>
+        <v>71104.91150434416</v>
       </c>
       <c r="AX192" s="190" t="n">
-        <v>72595.72034546069</v>
+        <v>72595.72034546068</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>74541.05851927647</v>
+        <v>74541.05851927646</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39129,31 +39129,31 @@
         <v>58895.089087613</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>11685.54726389713</v>
+        <v>11685.54726389712</v>
       </c>
       <c r="BH192" s="190" t="n">
         <v>12314.14721798622</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>13131.37395224124</v>
+        <v>13131.37395224121</v>
       </c>
       <c r="BJ192" s="190" t="n">
-        <v>14239.36090163694</v>
+        <v>14239.36090163693</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>15645.96943166314</v>
+        <v>15645.96943166313</v>
       </c>
       <c r="BL192" s="197" t="n">
-        <v>68520.79892571813</v>
+        <v>68520.79892571812</v>
       </c>
       <c r="BM192" s="190" t="n">
-        <v>69762.95644698222</v>
+        <v>69762.95644698221</v>
       </c>
       <c r="BN192" s="190" t="n">
-        <v>71104.91150434424</v>
+        <v>71104.91150434421</v>
       </c>
       <c r="BO192" s="190" t="n">
-        <v>72595.72034546094</v>
+        <v>72595.72034546093</v>
       </c>
       <c r="BP192" s="198" t="n">
         <v>74541.05851927614</v>
@@ -39185,13 +39185,13 @@
         <v>12404.13892512474</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>13282.19313651668</v>
+        <v>13282.19313651666</v>
       </c>
       <c r="CA192" s="190" t="n">
-        <v>14452.76546784931</v>
+        <v>14452.7654678493</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>15925.64489480941</v>
+        <v>15925.6448948094</v>
       </c>
       <c r="CC192" s="197" t="n">
         <v>68390.13071195339</v>
@@ -39200,7 +39200,7 @@
         <v>69619.93987958774</v>
       </c>
       <c r="CE192" s="190" t="n">
-        <v>70947.13537269068</v>
+        <v>70947.13537269065</v>
       </c>
       <c r="CF192" s="190" t="n">
         <v>72421.46376502831</v>
@@ -39236,34 +39236,34 @@
         <v>5144414</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>130.6682137649147</v>
+        <v>130.6682137649139</v>
       </c>
       <c r="CX192" s="103" t="n">
-        <v>143.0165673943987</v>
+        <v>143.0165673943978</v>
       </c>
       <c r="CY192" s="103" t="n">
-        <v>157.7761316534094</v>
+        <v>157.7761316534084</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323896</v>
       </c>
       <c r="DA192" s="104" t="n">
-        <v>192.9148478659413</v>
+        <v>192.91484786594</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.01079627364906017</v>
+        <v>0.01079627364906018</v>
       </c>
       <c r="DD192" s="397" t="n">
-        <v>0.01115257791953112</v>
+        <v>0.01115257791953111</v>
       </c>
       <c r="DE192" s="397" t="n">
-        <v>0.01148428654087755</v>
+        <v>0.01148428654087757</v>
       </c>
       <c r="DF192" s="397" t="n">
-        <v>0.01164983319324695</v>
+        <v>0.01164983319324696</v>
       </c>
       <c r="DG192" s="398" t="n">
-        <v>0.01169494806471412</v>
+        <v>0.01169494806471413</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" thickBot="1">
@@ -39388,34 +39388,34 @@
         <v>4584.024590086</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>22158.11515268233</v>
+        <v>22158.11515268232</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>24429.30328634564</v>
+        <v>24429.30328634561</v>
       </c>
       <c r="AR193" s="207" t="n">
-        <v>27032.12761083537</v>
+        <v>27032.12761083534</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>29918.86350919778</v>
+        <v>29918.86350919776</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>33429.82145839032</v>
+        <v>33429.82145839034</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>25193.517831171</v>
+        <v>25193.51783117099</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>27812.80680003977</v>
+        <v>27812.80680003974</v>
       </c>
       <c r="AW193" s="209" t="n">
-        <v>30783.02575880155</v>
+        <v>30783.02575880152</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>34109.82162140912</v>
+        <v>34109.8216214091</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>38013.84604847605</v>
+        <v>38013.84604847607</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,34 +39438,34 @@
         <v>4584.024590086</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>22158.11515268233</v>
+        <v>22158.11515268232</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>24429.30328634564</v>
+        <v>24429.30328634561</v>
       </c>
       <c r="BI193" s="212" t="n">
-        <v>27032.12761083537</v>
+        <v>27032.12761083534</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>29918.86350919778</v>
+        <v>29918.86350919776</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>33429.82145839032</v>
+        <v>33429.82145839034</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>25193.51783117133</v>
+        <v>25193.51783117132</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>27812.80680003963</v>
+        <v>27812.80680003961</v>
       </c>
       <c r="BN193" s="212" t="n">
-        <v>30783.02575880137</v>
+        <v>30783.02575880134</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>34109.82162140878</v>
+        <v>34109.82162140876</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>38013.84604847633</v>
+        <v>38013.84604847634</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,34 +39488,34 @@
         <v>4343.016806139</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>21553.13526743169</v>
+        <v>21553.13526743168</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>23768.57981361583</v>
+        <v>23768.57981361581</v>
       </c>
       <c r="BZ193" s="212" t="n">
-        <v>26311.55657400407</v>
+        <v>26311.55657400404</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>29150.45252801628</v>
+        <v>29150.45252801626</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>32577.4799466203</v>
+        <v>32577.47994662032</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>24529.5851141957</v>
+        <v>24529.58511419568</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>27059.18855259783</v>
+        <v>27059.18855259781</v>
       </c>
       <c r="CE193" s="212" t="n">
-        <v>29928.85639017707</v>
+        <v>29928.85639017704</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>33159.26419276927</v>
+        <v>33159.26419276926</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>36920.4967527593</v>
+        <v>36920.49675275932</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>2510</v>
@@ -39545,34 +39545,34 @@
         <v>837210</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>663.932716975579</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>753.618247441934</v>
+        <v>753.6182474419337</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398271</v>
       </c>
       <c r="DA193" s="134" t="n">
         <v>1093.349295717359</v>
       </c>
       <c r="DC193" s="422" t="n">
-        <v>0.02947412316721835</v>
+        <v>0.02947412316721838</v>
       </c>
       <c r="DD193" s="423" t="n">
-        <v>0.03031253335869557</v>
+        <v>0.03031253335869559</v>
       </c>
       <c r="DE193" s="423" t="n">
-        <v>0.031016982249023</v>
+        <v>0.03101698224902303</v>
       </c>
       <c r="DF193" s="423" t="n">
-        <v>0.03114673314214129</v>
+        <v>0.03114673314214131</v>
       </c>
       <c r="DG193" s="424" t="n">
-        <v>0.03202818225054179</v>
+        <v>0.03202818225054178</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" thickBot="1">
@@ -39682,7 +39682,7 @@
         </is>
       </c>
       <c r="AK194" s="220" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="AL194" s="209" t="n">
         <v>1435280.798812628</v>
@@ -39694,25 +39694,25 @@
         <v>1458495.409587526</v>
       </c>
       <c r="AO194" s="210" t="n">
-        <v>1470806.519645696</v>
+        <v>1470806.519645697</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>222373.3191489253</v>
+        <v>222373.3191489246</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>233484.1016566837</v>
+        <v>233484.1016566831</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>246424.9517426563</v>
+        <v>246424.9517426565</v>
       </c>
       <c r="AS194" s="207" t="n">
-        <v>262895.1428126008</v>
+        <v>262895.1428126004</v>
       </c>
       <c r="AT194" s="208" t="n">
         <v>284029.7828557848</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447798</v>
       </c>
       <c r="AV194" s="207" t="n">
         <v>1668764.900469311</v>
@@ -39721,10 +39721,10 @@
         <v>1695104.119977999</v>
       </c>
       <c r="AX194" s="207" t="n">
-        <v>1721390.552400128</v>
+        <v>1721390.552400126</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>1754836.302501481</v>
+        <v>1754836.302501482</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         </is>
       </c>
       <c r="BB194" s="221" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="BC194" s="222" t="n">
         <v>1435280.798812628</v>
@@ -39744,37 +39744,37 @@
         <v>1458495.409587526</v>
       </c>
       <c r="BF194" s="214" t="n">
-        <v>1470806.519645696</v>
+        <v>1470806.519645697</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>222373.3191489253</v>
+        <v>222373.3191489246</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>233484.1016566837</v>
+        <v>233484.1016566831</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>246424.9517426563</v>
+        <v>246424.9517426565</v>
       </c>
       <c r="BJ194" s="222" t="n">
-        <v>262895.1428126008</v>
+        <v>262895.1428126004</v>
       </c>
       <c r="BK194" s="214" t="n">
         <v>284029.7828557848</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447799</v>
       </c>
       <c r="BM194" s="222" t="n">
-        <v>1668764.900469312</v>
+        <v>1668764.900469311</v>
       </c>
       <c r="BN194" s="222" t="n">
         <v>1695104.119977999</v>
       </c>
       <c r="BO194" s="222" t="n">
-        <v>1721390.552400127</v>
+        <v>1721390.552400126</v>
       </c>
       <c r="BP194" s="214" t="n">
-        <v>1754836.302501481</v>
+        <v>1754836.302501482</v>
       </c>
       <c r="BR194" s="155" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         </is>
       </c>
       <c r="BS194" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BT194" s="222" t="n">
         <v>1429707.124045061</v>
@@ -39794,25 +39794,25 @@
         <v>1449303.184037709</v>
       </c>
       <c r="BW194" s="214" t="n">
-        <v>1459680.857487838</v>
+        <v>1459680.857487839</v>
       </c>
       <c r="BX194" s="221" t="n">
-        <v>223107.2967522651</v>
+        <v>223107.2967522644</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>235625.9003085983</v>
+        <v>235625.9003085977</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>249983.184232143</v>
+        <v>249983.1842321432</v>
       </c>
       <c r="CA194" s="222" t="n">
-        <v>267900.653199542</v>
+        <v>267900.6531995416</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>290498.6552000813</v>
+        <v>290498.6552000812</v>
       </c>
       <c r="CC194" s="222" t="n">
-        <v>1638486.346796772</v>
+        <v>1638486.346796771</v>
       </c>
       <c r="CD194" s="222" t="n">
         <v>1665333.024353659</v>
@@ -39824,7 +39824,7 @@
         <v>1717203.837237251</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>1750179.512687919</v>
+        <v>1750179.51268792</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>1375594</v>
@@ -39854,19 +39854,19 @@
         <v>60466650</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028065</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>3431.876115652927</v>
+        <v>3431.876115652911</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217817</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875491</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>4656.78981356289</v>
+        <v>4656.78981356287</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40639,7 +40639,7 @@
         </is>
       </c>
       <c r="CI198" s="396" t="n">
-        <v>0.9999999999999991</v>
+        <v>1</v>
       </c>
       <c r="CJ198" s="397" t="n">
         <v>1.000000000000004</v>
@@ -40651,26 +40651,26 @@
         <v>1.000000000000002</v>
       </c>
       <c r="CM198" s="398" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="CN198" s="396" t="n">
-        <v>1.000000000000986</v>
+        <v>1.000000000000992</v>
       </c>
       <c r="CO198" s="397" t="n">
-        <v>0.9999999999985593</v>
+        <v>0.9999999999985594</v>
       </c>
       <c r="CP198" s="397" t="n">
-        <v>0.9999999999991155</v>
+        <v>0.9999999999991156</v>
       </c>
       <c r="CQ198" s="397" t="n">
         <v>1.000000000000606</v>
       </c>
       <c r="CR198" s="398" t="n">
-        <v>0.9999999999977438</v>
+        <v>0.9999999999977436</v>
       </c>
       <c r="CS198" s="465" t="n"/>
       <c r="CT198" s="396" t="n">
-        <v>0.9999999999999991</v>
+        <v>1</v>
       </c>
       <c r="CU198" s="397" t="n">
         <v>1.000000000000004</v>
@@ -40682,10 +40682,10 @@
         <v>1.000000000000002</v>
       </c>
       <c r="CX198" s="398" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="CY198" s="396" t="n">
-        <v>1.012460167074764</v>
+        <v>1.012460167074771</v>
       </c>
       <c r="CZ198" s="397" t="n">
         <v>1.012992901857283</v>
@@ -40822,31 +40822,31 @@
         <v>0.00634</v>
       </c>
       <c r="AP199" s="233" t="n">
-        <v>2958.430622030667</v>
+        <v>2958.430622030663</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>4292.646327614394</v>
+        <v>4292.646327614393</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>5662.813186259974</v>
+        <v>5662.813186259977</v>
       </c>
       <c r="AS199" s="190" t="n">
-        <v>7069.040947359896</v>
+        <v>7069.040947359888</v>
       </c>
       <c r="AT199" s="196" t="n">
-        <v>8545.906703861468</v>
+        <v>8545.906703861478</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>159657.3891568753</v>
+        <v>159657.3891568747</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>168650.6223228538</v>
+        <v>168650.6223228532</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>178407.2528024147</v>
+        <v>178407.252802415</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>190365.7969362473</v>
+        <v>190365.7969362468</v>
       </c>
       <c r="AY199" s="196" t="n">
         <v>205475.5889513159</v>
@@ -40872,31 +40872,31 @@
         <v>0.00634</v>
       </c>
       <c r="BG199" s="197" t="n">
-        <v>2958.430622030666</v>
+        <v>2958.430622030662</v>
       </c>
       <c r="BH199" s="190" t="n">
-        <v>4292.646327614395</v>
+        <v>4292.646327614393</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>5662.813186259975</v>
+        <v>5662.813186259978</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>7069.040947359893</v>
+        <v>7069.040947359891</v>
       </c>
       <c r="BK199" s="198" t="n">
-        <v>8545.906703861468</v>
+        <v>8545.906703861474</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>159657.3891568753</v>
+        <v>159657.3891568747</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>168650.6223228538</v>
+        <v>168650.6223228532</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>178407.2528024147</v>
+        <v>178407.252802415</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>190365.7969362473</v>
+        <v>190365.7969362468</v>
       </c>
       <c r="BP199" s="201" t="n">
         <v>205475.5889513159</v>
@@ -40922,22 +40922,22 @@
         <v>147097.8447281431</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.6466114449749486</v>
+        <v>0.6466114449749513</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.6803881747816339</v>
+        <v>0.6803881747816369</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.7041227667519326</v>
+        <v>0.7041227667519313</v>
       </c>
       <c r="CA199" s="463" t="n">
-        <v>0.7216460584379004</v>
+        <v>0.7216460584379024</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.74335960479444</v>
+        <v>0.7433596047944402</v>
       </c>
       <c r="CC199" s="199" t="n">
-        <v>101965.784394293</v>
+        <v>101965.7843942931</v>
       </c>
       <c r="CD199" s="200" t="n">
         <v>113276.1037984415</v>
@@ -40946,7 +40946,7 @@
         <v>123945.5946807197</v>
       </c>
       <c r="CF199" s="200" t="n">
-        <v>135489.5155371755</v>
+        <v>135489.5155371756</v>
       </c>
       <c r="CG199" s="201" t="n">
         <v>150601.7080481383</v>
@@ -40970,7 +40970,7 @@
         <v>1.000000000015562</v>
       </c>
       <c r="CO199" s="397" t="n">
-        <v>0.9999999999965904</v>
+        <v>0.9999999999965593</v>
       </c>
       <c r="CP199" s="397" t="n">
         <v>0.9999999999875733</v>
@@ -41001,7 +41001,7 @@
         <v>1.010821595196259</v>
       </c>
       <c r="CZ199" s="397" t="n">
-        <v>1.011287059483315</v>
+        <v>1.011287059483284</v>
       </c>
       <c r="DA199" s="397" t="n">
         <v>1.011865406593546</v>
@@ -41135,34 +41135,34 @@
         <v>0.00634</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>663.6071311260645</v>
+        <v>663.6071311260646</v>
       </c>
       <c r="AQ200" s="190" t="n">
-        <v>955.1253907080513</v>
+        <v>955.1253907080518</v>
       </c>
       <c r="AR200" s="190" t="n">
-        <v>1251.745046722491</v>
+        <v>1251.74504672249</v>
       </c>
       <c r="AS200" s="190" t="n">
-        <v>1553.377008353701</v>
+        <v>1553.377008353702</v>
       </c>
       <c r="AT200" s="196" t="n">
         <v>1866.157359038367</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>32494.30532862727</v>
+        <v>32494.30532862726</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782055</v>
       </c>
       <c r="AW200" s="190" t="n">
         <v>34768.75561014745</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>36993.53942123244</v>
+        <v>36993.53942123247</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>39890.46707731524</v>
+        <v>39890.46707731522</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>663.6071311260655</v>
       </c>
       <c r="BH200" s="190" t="n">
-        <v>955.1253907080529</v>
+        <v>955.1253907080533</v>
       </c>
       <c r="BI200" s="190" t="n">
         <v>1251.745046722489</v>
@@ -41197,22 +41197,22 @@
         <v>1553.3770083537</v>
       </c>
       <c r="BK200" s="198" t="n">
-        <v>1866.15735903837</v>
+        <v>1866.157359038369</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>32494.30532862727</v>
+        <v>32494.30532862726</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782055</v>
       </c>
       <c r="BN200" s="190" t="n">
         <v>34768.75561014745</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>36993.53942123244</v>
+        <v>36993.53942123247</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>39890.46707731524</v>
+        <v>39890.46707731522</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41235,19 +41235,19 @@
         <v>27292.71916327556</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.6167000484508497</v>
+        <v>0.6167000484508498</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>0.6509786380063289</v>
+        <v>0.6509786380063267</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.6763319833413179</v>
+        <v>0.6763319833413181</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.6929421555046223</v>
+        <v>0.6929421555046218</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.7142533081465166</v>
+        <v>0.7142533081465169</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>19824.70474125438</v>
@@ -41256,7 +41256,7 @@
         <v>21459.97596939656</v>
       </c>
       <c r="CE200" s="190" t="n">
-        <v>23239.47561266682</v>
+        <v>23239.47561266683</v>
       </c>
       <c r="CF200" s="190" t="n">
         <v>25324.80908032454</v>
@@ -41280,7 +41280,7 @@
         <v>0.9999999999999089</v>
       </c>
       <c r="CN200" s="396" t="n">
-        <v>1.000000000008814</v>
+        <v>1.000000000008813</v>
       </c>
       <c r="CO200" s="397" t="n">
         <v>1.000000000001134</v>
@@ -41448,34 +41448,34 @@
         <v>0.00634</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>160.338669486181</v>
+        <v>160.3386694861809</v>
       </c>
       <c r="AQ201" s="190" t="n">
         <v>233.0082745329209</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>308.5953159288538</v>
+        <v>308.5953159288537</v>
       </c>
       <c r="AS201" s="190" t="n">
-        <v>387.6611466447601</v>
+        <v>387.66114664476</v>
       </c>
       <c r="AT201" s="196" t="n">
-        <v>472.5903110122129</v>
+        <v>472.5903110122127</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>11845.88593338331</v>
+        <v>11845.8859333833</v>
       </c>
       <c r="AV201" s="190" t="n">
         <v>12547.15549251914</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>13439.96926817009</v>
+        <v>13439.96926817007</v>
       </c>
       <c r="AX201" s="190" t="n">
-        <v>14627.0220482817</v>
+        <v>14627.02204828169</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>16118.55974267535</v>
+        <v>16118.55974267534</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41504,28 +41504,28 @@
         <v>233.0082745329206</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>308.595315928854</v>
+        <v>308.5953159288539</v>
       </c>
       <c r="BJ201" s="190" t="n">
-        <v>387.6611466447615</v>
+        <v>387.6611466447613</v>
       </c>
       <c r="BK201" s="198" t="n">
         <v>472.5903110122107</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>11845.88593338331</v>
+        <v>11845.8859333833</v>
       </c>
       <c r="BM201" s="190" t="n">
         <v>12547.15549251914</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>13439.96926817009</v>
+        <v>13439.96926817007</v>
       </c>
       <c r="BO201" s="190" t="n">
-        <v>14627.0220482817</v>
+        <v>14627.02204828169</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>16118.55974267535</v>
+        <v>16118.55974267534</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41548,28 +41548,28 @@
         <v>12045.55205274821</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.655944805565617</v>
+        <v>0.6559448055656173</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.6880968190885129</v>
+        <v>0.6880968190885131</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.7144401067455742</v>
+        <v>0.7144401067455758</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.7384979676447364</v>
+        <v>0.7384979676447367</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.7670945895259743</v>
+        <v>0.7670945895259746</v>
       </c>
       <c r="CC201" s="197" t="n">
-        <v>7684.536209253957</v>
+        <v>7684.536209253959</v>
       </c>
       <c r="CD201" s="190" t="n">
-        <v>8535.248537910338</v>
+        <v>8535.24853791034</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>9489.331482268313</v>
+        <v>9489.331482268315</v>
       </c>
       <c r="CF201" s="190" t="n">
         <v>10673.33792485274</v>
@@ -41596,7 +41596,7 @@
         <v>1.000000000014788</v>
       </c>
       <c r="CO201" s="423" t="n">
-        <v>0.9999999999853939</v>
+        <v>0.9999999999853941</v>
       </c>
       <c r="CP201" s="423" t="n">
         <v>1.000000000006299</v>
@@ -41760,34 +41760,34 @@
         <v>0.00634</v>
       </c>
       <c r="AP202" s="220" t="n">
-        <v>58.95283172494014</v>
+        <v>58.95283172494011</v>
       </c>
       <c r="AQ202" s="209" t="n">
-        <v>92.89477471213283</v>
+        <v>92.89477471213274</v>
       </c>
       <c r="AR202" s="209" t="n">
-        <v>133.5983317931988</v>
+        <v>133.5983317931986</v>
       </c>
       <c r="AS202" s="209" t="n">
-        <v>182.1464474583247</v>
+        <v>182.1464474583246</v>
       </c>
       <c r="AT202" s="210" t="n">
-        <v>241.0077839473382</v>
+        <v>241.0077839473383</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>22217.06798440727</v>
+        <v>22217.06798440725</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>24522.19806105777</v>
+        <v>24522.19806105774</v>
       </c>
       <c r="AW202" s="209" t="n">
-        <v>27165.72594262857</v>
+        <v>27165.72594262854</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>30101.00995665611</v>
+        <v>30101.00995665609</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>33670.82924233766</v>
+        <v>33670.82924233768</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41810,34 +41810,34 @@
         <v>0.00634</v>
       </c>
       <c r="BG202" s="211" t="n">
-        <v>58.95283172494091</v>
+        <v>58.95283172494089</v>
       </c>
       <c r="BH202" s="212" t="n">
-        <v>92.89477471213237</v>
+        <v>92.89477471213229</v>
       </c>
       <c r="BI202" s="212" t="n">
-        <v>133.598331793198</v>
+        <v>133.5983317931978</v>
       </c>
       <c r="BJ202" s="212" t="n">
-        <v>182.1464474583229</v>
+        <v>182.1464474583228</v>
       </c>
       <c r="BK202" s="213" t="n">
-        <v>241.0077839473399</v>
+        <v>241.00778394734</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>22217.06798440727</v>
+        <v>22217.06798440726</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>24522.19806105777</v>
+        <v>24522.19806105774</v>
       </c>
       <c r="BN202" s="212" t="n">
-        <v>27165.72594262857</v>
+        <v>27165.72594262854</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>30101.0099566561</v>
+        <v>30101.00995665608</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>33670.82924233766</v>
+        <v>33670.82924233768</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41860,19 +41860,19 @@
         <v>25652.86382685493</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.7000174703485902</v>
+        <v>0.7000174703485907</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.7171947087884045</v>
+        <v>0.7171947087884053</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.7283718889102291</v>
+        <v>0.72837188891023</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.7395256918955586</v>
+        <v>0.7395256918955594</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>0.7595570753068651</v>
+        <v>0.7595570753068648</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>15087.57122798852</v>
@@ -42022,31 +42022,31 @@
         <v>0.02536</v>
       </c>
       <c r="AP203" s="206" t="n">
-        <v>3841.329254367853</v>
+        <v>3841.329254367848</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>5573.6747675675</v>
+        <v>5573.674767567499</v>
       </c>
       <c r="AR203" s="207" t="n">
-        <v>7356.751880704517</v>
+        <v>7356.751880704519</v>
       </c>
       <c r="AS203" s="207" t="n">
-        <v>9192.225549816681</v>
+        <v>9192.225549816674</v>
       </c>
       <c r="AT203" s="208" t="n">
         <v>11125.66215785939</v>
       </c>
       <c r="AU203" s="207" t="n">
-        <v>226214.6484032932</v>
+        <v>226214.6484032925</v>
       </c>
       <c r="AV203" s="207" t="n">
-        <v>239057.7764242512</v>
+        <v>239057.7764242506</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>253781.7036233608</v>
+        <v>253781.7036233611</v>
       </c>
       <c r="AX203" s="207" t="n">
-        <v>272087.3683624176</v>
+        <v>272087.3683624171</v>
       </c>
       <c r="AY203" s="208" t="n">
         <v>295155.4450136442</v>
@@ -42072,34 +42072,34 @@
         <v>0.02536</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>3841.329254367853</v>
+        <v>3841.329254367849</v>
       </c>
       <c r="BH203" s="222" t="n">
-        <v>5573.674767567501</v>
+        <v>5573.6747675675</v>
       </c>
       <c r="BI203" s="222" t="n">
-        <v>7356.751880704516</v>
+        <v>7356.751880704518</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>9192.225549816678</v>
+        <v>9192.225549816674</v>
       </c>
       <c r="BK203" s="214" t="n">
         <v>11125.66215785939</v>
       </c>
       <c r="BL203" s="222" t="n">
-        <v>226214.6484032932</v>
+        <v>226214.6484032925</v>
       </c>
       <c r="BM203" s="222" t="n">
-        <v>239057.7764242512</v>
+        <v>239057.7764242506</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>253781.7036233608</v>
+        <v>253781.7036233611</v>
       </c>
       <c r="BO203" s="222" t="n">
-        <v>272087.3683624176</v>
+        <v>272087.3683624171</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>295155.4450136442</v>
+        <v>295155.4450136441</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42122,25 +42122,25 @@
         <v>212088.9797710218</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.6479510023973352</v>
+        <v>0.6479510023973372</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.6803922139863261</v>
+        <v>0.680392213986328</v>
       </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.7034033128177951</v>
+        <v>0.7034033128177943</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.7205849213567079</v>
+        <v>0.7205849213567093</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.7425296329365555</v>
+        <v>0.7425296329365557</v>
       </c>
       <c r="CC203" s="212" t="n">
         <v>144562.5965727899</v>
       </c>
       <c r="CD203" s="212" t="n">
-        <v>160318.0279834885</v>
+        <v>160318.0279834886</v>
       </c>
       <c r="CE203" s="212" t="n">
         <v>175838.9999376306</v>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AK208" s="233" t="n">
-        <v>1104629.20145452</v>
+        <v>1104629.201454519</v>
       </c>
       <c r="AL208" s="190" t="n">
         <v>1116572.829058702</v>
@@ -42937,34 +42937,34 @@
         <v>1142459.222383301</v>
       </c>
       <c r="AP208" s="473" t="n">
-        <v>0.876057406842331</v>
+        <v>0.8760574068423314</v>
       </c>
       <c r="AQ208" s="463" t="n">
-        <v>0.87211719812725</v>
+        <v>0.8721171981272503</v>
       </c>
       <c r="AR208" s="463" t="n">
-        <v>0.8676080521686323</v>
+        <v>0.867608052168632</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.8615364256241552</v>
+        <v>0.8615364256241556</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0.8539026660699781</v>
+        <v>0.8539026660699782</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.8737174068423306</v>
+        <v>0.8737174068423311</v>
       </c>
       <c r="AV208" s="463" t="n">
-        <v>0.8687771981272503</v>
+        <v>0.8687771981272504</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.8632680521686326</v>
+        <v>0.8632680521686322</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.856196425624155</v>
+        <v>0.8561964256241559</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.8475626660699781</v>
+        <v>0.847562666069978</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="BB208" s="197" t="n">
-        <v>1104629.20145452</v>
+        <v>1104629.201454519</v>
       </c>
       <c r="BC208" s="190" t="n">
         <v>1116572.829058702</v>
@@ -42984,37 +42984,37 @@
         <v>1133424.642644257</v>
       </c>
       <c r="BF208" s="198" t="n">
-        <v>1142459.222383301</v>
+        <v>1142459.222383302</v>
       </c>
       <c r="BG208" s="462" t="n">
-        <v>0.8760574068423309</v>
+        <v>0.8760574068423314</v>
       </c>
       <c r="BH208" s="463" t="n">
-        <v>0.8721171981272501</v>
+        <v>0.8721171981272503</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.8676080521686323</v>
+        <v>0.8676080521686321</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.8615364256241553</v>
+        <v>0.8615364256241557</v>
       </c>
       <c r="BK208" s="464" t="n">
-        <v>0.8539026660699781</v>
+        <v>0.8539026660699782</v>
       </c>
       <c r="BL208" s="475" t="n">
-        <v>0.8737174068423307</v>
+        <v>0.8737174068423311</v>
       </c>
       <c r="BM208" s="476" t="n">
-        <v>0.8687771981272503</v>
+        <v>0.8687771981272506</v>
       </c>
       <c r="BN208" s="476" t="n">
-        <v>0.8632680521686324</v>
+        <v>0.8632680521686321</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.8561964256241552</v>
+        <v>0.8561964256241555</v>
       </c>
       <c r="BP208" s="477" t="n">
-        <v>0.8475626660699784</v>
+        <v>0.8475626660699785</v>
       </c>
       <c r="BR208" s="83" t="inlineStr">
         <is>
@@ -43037,19 +43037,19 @@
         <v>0</v>
       </c>
       <c r="BX208" s="462" t="n">
-        <v>0.8750773973513707</v>
+        <v>0.875077397351371</v>
       </c>
       <c r="BY208" s="463" t="n">
-        <v>0.8702418993757741</v>
+        <v>0.8702418993757746</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.8648448124616638</v>
+        <v>0.8648448124616637</v>
       </c>
       <c r="CA208" s="463" t="n">
-        <v>0.8578911898737477</v>
+        <v>0.8578911898737479</v>
       </c>
       <c r="CB208" s="464" t="n">
-        <v>0.8493771662096562</v>
+        <v>0.8493771662096563</v>
       </c>
       <c r="CC208" s="478" t="n">
         <v>0</v>
@@ -43192,31 +43192,31 @@
         <v>254456.1195217966</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.887759141985466</v>
+        <v>0.8877591419854661</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.8867602766328136</v>
+        <v>0.8867602766328135</v>
       </c>
       <c r="AR209" s="463" t="n">
         <v>0.8837911711924566</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>0.8781683607604417</v>
+        <v>0.8781683607604416</v>
       </c>
       <c r="AT209" s="474" t="n">
         <v>0.8708179015846225</v>
       </c>
       <c r="AU209" s="463" t="n">
-        <v>0.8854191419854677</v>
+        <v>0.8854191419854676</v>
       </c>
       <c r="AV209" s="463" t="n">
-        <v>0.8834202766328154</v>
+        <v>0.8834202766328151</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.8794511711924556</v>
+        <v>0.8794511711924562</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.8728283607604409</v>
+        <v>0.8728283607604406</v>
       </c>
       <c r="AY209" s="474" t="n">
         <v>0.8644779015846236</v>
@@ -43245,7 +43245,7 @@
         <v>0.8877591419854662</v>
       </c>
       <c r="BH209" s="463" t="n">
-        <v>0.886760276632814</v>
+        <v>0.8867602766328136</v>
       </c>
       <c r="BI209" s="463" t="n">
         <v>0.8837911711924565</v>
@@ -43254,13 +43254,13 @@
         <v>0.8781683607604415</v>
       </c>
       <c r="BK209" s="464" t="n">
-        <v>0.8708179015846226</v>
+        <v>0.8708179015846227</v>
       </c>
       <c r="BL209" s="462" t="n">
         <v>0.8854191419854666</v>
       </c>
       <c r="BM209" s="463" t="n">
-        <v>0.8834202766328141</v>
+        <v>0.8834202766328138</v>
       </c>
       <c r="BN209" s="463" t="n">
         <v>0.8794511711924583</v>
@@ -43269,7 +43269,7 @@
         <v>0.8728283607604405</v>
       </c>
       <c r="BP209" s="464" t="n">
-        <v>0.8644779015846238</v>
+        <v>0.8644779015846239</v>
       </c>
       <c r="BR209" s="101" t="inlineStr">
         <is>
@@ -43292,16 +43292,16 @@
         <v>0</v>
       </c>
       <c r="BX209" s="462" t="n">
-        <v>0.8865065957805205</v>
+        <v>0.8865065957805206</v>
       </c>
       <c r="BY209" s="463" t="n">
-        <v>0.8845712418530547</v>
+        <v>0.8845712418530545</v>
       </c>
       <c r="BZ209" s="463" t="n">
         <v>0.880696112712816</v>
       </c>
       <c r="CA209" s="463" t="n">
-        <v>0.8741709032491679</v>
+        <v>0.8741709032491677</v>
       </c>
       <c r="CB209" s="464" t="n">
         <v>0.8659222628320408</v>
@@ -43447,13 +43447,13 @@
         <v>58422.49877660078</v>
       </c>
       <c r="AP210" s="473" t="n">
-        <v>0.8294598509196436</v>
+        <v>0.8294598509196438</v>
       </c>
       <c r="AQ210" s="463" t="n">
-        <v>0.8234858749522092</v>
+        <v>0.8234858749522093</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.8153239533750215</v>
+        <v>0.8153239533750217</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.8038539898236949</v>
@@ -43462,19 +43462,19 @@
         <v>0.7901026663363379</v>
       </c>
       <c r="AU210" s="463" t="n">
-        <v>0.8271198509196401</v>
+        <v>0.8271198509196404</v>
       </c>
       <c r="AV210" s="463" t="n">
         <v>0.820145874952208</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.8109839533750222</v>
+        <v>0.8109839533750225</v>
       </c>
       <c r="AX210" s="463" t="n">
-        <v>0.7985139898236983</v>
+        <v>0.7985139898236985</v>
       </c>
       <c r="AY210" s="474" t="n">
-        <v>0.7837626663363334</v>
+        <v>0.7837626663363335</v>
       </c>
       <c r="BA210" s="111" t="inlineStr">
         <is>
@@ -43497,31 +43497,31 @@
         <v>58422.498776601</v>
       </c>
       <c r="BG210" s="462" t="n">
-        <v>0.829459850919643</v>
+        <v>0.8294598509196432</v>
       </c>
       <c r="BH210" s="463" t="n">
-        <v>0.8234858749522089</v>
+        <v>0.823485874952209</v>
       </c>
       <c r="BI210" s="463" t="n">
-        <v>0.8153239533750216</v>
+        <v>0.8153239533750219</v>
       </c>
       <c r="BJ210" s="463" t="n">
-        <v>0.8038539898236955</v>
+        <v>0.8038539898236957</v>
       </c>
       <c r="BK210" s="464" t="n">
         <v>0.790102666336337</v>
       </c>
       <c r="BL210" s="462" t="n">
-        <v>0.8271198509196457</v>
+        <v>0.8271198509196458</v>
       </c>
       <c r="BM210" s="463" t="n">
-        <v>0.8201458749522077</v>
+        <v>0.8201458749522079</v>
       </c>
       <c r="BN210" s="463" t="n">
-        <v>0.8109839533750195</v>
+        <v>0.8109839533750198</v>
       </c>
       <c r="BO210" s="463" t="n">
-        <v>0.7985139898236923</v>
+        <v>0.7985139898236924</v>
       </c>
       <c r="BP210" s="464" t="n">
         <v>0.7837626663363398</v>
@@ -43553,7 +43553,7 @@
         <v>0.8218306573292291</v>
       </c>
       <c r="BZ210" s="463" t="n">
-        <v>0.8127874639794219</v>
+        <v>0.8127874639794223</v>
       </c>
       <c r="CA210" s="463" t="n">
         <v>0.800435330681228</v>
@@ -43696,7 +43696,7 @@
         <v>3617.299816172801</v>
       </c>
       <c r="AN211" s="209" t="n">
-        <v>4008.811664752675</v>
+        <v>4008.811664752676</v>
       </c>
       <c r="AO211" s="210" t="n">
         <v>4343.016806138662</v>
@@ -43705,28 +43705,28 @@
         <v>0.1204834790770299</v>
       </c>
       <c r="AQ211" s="490" t="n">
-        <v>0.1216527169666779</v>
+        <v>0.121652716966678</v>
       </c>
       <c r="AR211" s="490" t="n">
         <v>0.12184956012304</v>
       </c>
       <c r="AS211" s="490" t="n">
-        <v>0.1228666088825536</v>
+        <v>0.1228666088825537</v>
       </c>
       <c r="AT211" s="491" t="n">
-        <v>0.1205882873372003</v>
+        <v>0.1205882873372002</v>
       </c>
       <c r="AU211" s="490" t="n">
         <v>0.118143479077043</v>
       </c>
       <c r="AV211" s="490" t="n">
-        <v>0.1183127169666731</v>
+        <v>0.1183127169666732</v>
       </c>
       <c r="AW211" s="490" t="n">
-        <v>0.1175095601230342</v>
+        <v>0.1175095601230343</v>
       </c>
       <c r="AX211" s="490" t="n">
-        <v>0.1175266088825435</v>
+        <v>0.1175266088825436</v>
       </c>
       <c r="AY211" s="491" t="n">
         <v>0.1142482873372075</v>
@@ -43752,34 +43752,34 @@
         <v>4343.016806139</v>
       </c>
       <c r="BG211" s="466" t="n">
-        <v>0.1204834790770414</v>
+        <v>0.1204834790770415</v>
       </c>
       <c r="BH211" s="467" t="n">
-        <v>0.1216527169666737</v>
+        <v>0.1216527169666738</v>
       </c>
       <c r="BI211" s="467" t="n">
-        <v>0.1218495601230349</v>
+        <v>0.121849560123035</v>
       </c>
       <c r="BJ211" s="467" t="n">
-        <v>0.1228666088825447</v>
+        <v>0.1228666088825448</v>
       </c>
       <c r="BK211" s="468" t="n">
         <v>0.1205882873372066</v>
       </c>
       <c r="BL211" s="467" t="n">
-        <v>0.118143479077039</v>
+        <v>0.1181434790770391</v>
       </c>
       <c r="BM211" s="467" t="n">
-        <v>0.1183127169666785</v>
+        <v>0.1183127169666786</v>
       </c>
       <c r="BN211" s="467" t="n">
-        <v>0.1175095601230413</v>
+        <v>0.1175095601230415</v>
       </c>
       <c r="BO211" s="467" t="n">
-        <v>0.1175266088825542</v>
+        <v>0.1175266088825543</v>
       </c>
       <c r="BP211" s="468" t="n">
-        <v>0.1142482873372156</v>
+        <v>0.1142482873372155</v>
       </c>
       <c r="BR211" s="111" t="inlineStr">
         <is>
@@ -43802,16 +43802,16 @@
         <v>0</v>
       </c>
       <c r="BX211" s="466" t="n">
-        <v>0.1213412225648071</v>
+        <v>0.1213412225648072</v>
       </c>
       <c r="BY211" s="467" t="n">
-        <v>0.1216078129093078</v>
+        <v>0.1216078129093079</v>
       </c>
       <c r="BZ211" s="467" t="n">
-        <v>0.120863282212154</v>
+        <v>0.1208632822121541</v>
       </c>
       <c r="CA211" s="467" t="n">
-        <v>0.1208956761358765</v>
+        <v>0.1208956761358766</v>
       </c>
       <c r="CB211" s="468" t="n">
         <v>0.1176315918830214</v>
@@ -43942,7 +43942,7 @@
         </is>
       </c>
       <c r="AK212" s="206" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="AL212" s="207" t="n">
         <v>1429707.12404506</v>
@@ -43954,37 +43954,37 @@
         <v>1449303.184037709</v>
       </c>
       <c r="AO212" s="208" t="n">
-        <v>1459680.857487837</v>
+        <v>1459680.857487838</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.8645381501164454</v>
+        <v>0.8645381501164457</v>
       </c>
       <c r="AQ212" s="501" t="n">
-        <v>0.8600856827759142</v>
+        <v>0.8600856827759144</v>
       </c>
       <c r="AR212" s="501" t="n">
         <v>0.8546254776692686</v>
       </c>
       <c r="AS212" s="501" t="n">
-        <v>0.8472774569106075</v>
+        <v>0.8472774569106083</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.8381445708349512</v>
+        <v>0.838144570834951</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.8621981501164453</v>
+        <v>0.8621981501164456</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.8567456827759142</v>
+        <v>0.8567456827759143</v>
       </c>
       <c r="AW212" s="501" t="n">
         <v>0.8502854776692687</v>
       </c>
       <c r="AX212" s="501" t="n">
-        <v>0.8419374569106075</v>
+        <v>0.8419374569106083</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.8318045708349512</v>
+        <v>0.8318045708349511</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         </is>
       </c>
       <c r="BB212" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BC212" s="222" t="n">
         <v>1429707.124045061</v>
@@ -44004,37 +44004,37 @@
         <v>1449303.184037709</v>
       </c>
       <c r="BF212" s="214" t="n">
-        <v>1459680.857487838</v>
+        <v>1459680.857487839</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.8645381501164454</v>
+        <v>0.8645381501164456</v>
       </c>
       <c r="BH212" s="504" t="n">
-        <v>0.860085682775914</v>
+        <v>0.8600856827759141</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.8546254776692687</v>
+        <v>0.8546254776692686</v>
       </c>
       <c r="BJ212" s="504" t="n">
-        <v>0.847277456910608</v>
+        <v>0.8472774569106082</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.838144570834951</v>
+        <v>0.8381445708349511</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.8621981501164453</v>
+        <v>0.8621981501164455</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.8567456827759143</v>
+        <v>0.8567456827759145</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.850285477669269</v>
+        <v>0.8502854776692689</v>
       </c>
       <c r="BO212" s="504" t="n">
-        <v>0.8419374569106078</v>
+        <v>0.8419374569106081</v>
       </c>
       <c r="BP212" s="505" t="n">
-        <v>0.8318045708349517</v>
+        <v>0.831804570834952</v>
       </c>
       <c r="BR212" s="155" t="inlineStr">
         <is>
@@ -44057,19 +44057,19 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.8638332890668036</v>
+        <v>0.8638332890668038</v>
       </c>
       <c r="BY212" s="504" t="n">
-        <v>0.8585112425786138</v>
+        <v>0.858511242578614</v>
       </c>
       <c r="BZ212" s="504" t="n">
-        <v>0.8521951419392133</v>
+        <v>0.8521951419392131</v>
       </c>
       <c r="CA212" s="504" t="n">
-        <v>0.8439901848632261</v>
+        <v>0.8439901848632262</v>
       </c>
       <c r="CB212" s="505" t="n">
-        <v>0.8340177946924229</v>
+        <v>0.834017794692423</v>
       </c>
       <c r="CC212" s="492" t="n">
         <v>0</v>
@@ -44731,34 +44731,34 @@
         </is>
       </c>
       <c r="AK219" s="506" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684381</v>
       </c>
       <c r="AL219" s="368" t="n">
-        <v>159778964.1900266</v>
+        <v>159778964.1900264</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>166038998.9901036</v>
+        <v>166038998.9901035</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>173883609.5679223</v>
+        <v>173883609.5679224</v>
       </c>
       <c r="AO219" s="380" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="AP219" s="381" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="AQ219" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="AR219" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="AS219" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44766,34 +44766,34 @@
         </is>
       </c>
       <c r="BB219" s="391" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684381</v>
       </c>
       <c r="BC219" s="375" t="n">
-        <v>159778964.1900266</v>
+        <v>159778964.1900264</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>166038998.9901036</v>
+        <v>166038998.9901035</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>173883609.5679223</v>
+        <v>173883609.5679224</v>
       </c>
       <c r="BF219" s="392" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="BG219" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="BH219" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="BI219" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="BJ219" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44801,34 +44801,34 @@
         </is>
       </c>
       <c r="BS219" s="391" t="n">
-        <v>153147878.8592605</v>
+        <v>153147878.8592607</v>
       </c>
       <c r="BT219" s="375" t="n">
-        <v>159167049.0236469</v>
+        <v>159167049.0236467</v>
       </c>
       <c r="BU219" s="375" t="n">
-        <v>165208428.9489245</v>
+        <v>165208428.9489243</v>
       </c>
       <c r="BV219" s="375" t="n">
-        <v>172805839.1481515</v>
+        <v>172805839.1481517</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>179867333.8774217</v>
+        <v>179867333.8774216</v>
       </c>
       <c r="BX219" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="BY219" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="BZ219" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="CA219" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="CI219" s="199" t="n">
         <v>140012326.4220064</v>
@@ -44926,31 +44926,31 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>99621263.56557636</v>
+        <v>99621263.56557631</v>
       </c>
       <c r="AL220" s="368" t="n">
-        <v>102867455.4246781</v>
+        <v>102867455.424678</v>
       </c>
       <c r="AM220" s="368" t="n">
         <v>105943211.5840001</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>109119948.3533169</v>
+        <v>109119948.3533168</v>
       </c>
       <c r="AO220" s="380" t="n">
         <v>112154742.9937821</v>
       </c>
       <c r="AP220" s="381" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="AQ220" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="AR220" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="AS220" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="AT220" s="382" t="n">
         <v>437.5536311497546</v>
@@ -44961,31 +44961,31 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>99621263.56557636</v>
+        <v>99621263.56557631</v>
       </c>
       <c r="BC220" s="375" t="n">
-        <v>102867455.4246781</v>
+        <v>102867455.424678</v>
       </c>
       <c r="BD220" s="375" t="n">
         <v>105943211.5840001</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>109119948.3533169</v>
+        <v>109119948.3533168</v>
       </c>
       <c r="BF220" s="392" t="n">
         <v>112154742.9937821</v>
       </c>
       <c r="BG220" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="BH220" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="BI220" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="BJ220" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="BK220" s="387" t="n">
         <v>437.5536311497546</v>
@@ -44996,31 +44996,31 @@
         </is>
       </c>
       <c r="BS220" s="391" t="n">
-        <v>99358676.85064593</v>
+        <v>99358676.85064588</v>
       </c>
       <c r="BT220" s="375" t="n">
-        <v>102480003.1332617</v>
+        <v>102480003.1332616</v>
       </c>
       <c r="BU220" s="375" t="n">
         <v>105422960.2471894</v>
       </c>
       <c r="BV220" s="375" t="n">
-        <v>108456407.5674678</v>
+        <v>108456407.5674677</v>
       </c>
       <c r="BW220" s="392" t="n">
         <v>111338199.0650382</v>
       </c>
       <c r="BX220" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="BY220" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="BZ220" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="CA220" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="CB220" s="387" t="n">
         <v>437.5536311497546</v>
@@ -45121,7 +45121,7 @@
         </is>
       </c>
       <c r="AK221" s="506" t="n">
-        <v>24428704.35144113</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="AL221" s="368" t="n">
         <v>25266859.46546124</v>
@@ -45136,7 +45136,7 @@
         <v>27898487.10720398</v>
       </c>
       <c r="AP221" s="381" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="AQ221" s="372" t="n">
         <v>439.8151990365077</v>
@@ -45145,7 +45145,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="AS221" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="AT221" s="382" t="n">
         <v>473.6980203171418</v>
@@ -45156,7 +45156,7 @@
         </is>
       </c>
       <c r="BB221" s="391" t="n">
-        <v>24428704.35144113</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="BC221" s="375" t="n">
         <v>25266859.46546124</v>
@@ -45171,7 +45171,7 @@
         <v>27898487.10720398</v>
       </c>
       <c r="BG221" s="386" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="BH221" s="372" t="n">
         <v>439.8151990365077</v>
@@ -45180,7 +45180,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="BJ221" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="BK221" s="387" t="n">
         <v>473.6980203171418</v>
@@ -45191,7 +45191,7 @@
         </is>
       </c>
       <c r="BS221" s="391" t="n">
-        <v>24359788.21509175</v>
+        <v>24359788.21509174</v>
       </c>
       <c r="BT221" s="375" t="n">
         <v>25164378.88482035</v>
@@ -45206,7 +45206,7 @@
         <v>27674622.01245653</v>
       </c>
       <c r="BX221" s="386" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="BY221" s="372" t="n">
         <v>439.8151990365077</v>
@@ -45215,7 +45215,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="CA221" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="CB221" s="387" t="n">
         <v>473.6980203171418</v>
@@ -45316,28 +45316,28 @@
         </is>
       </c>
       <c r="AK222" s="435" t="n">
-        <v>24369432.4027078</v>
+        <v>24369432.40270781</v>
       </c>
       <c r="AL222" s="408" t="n">
         <v>28456663.68210901</v>
       </c>
       <c r="AM222" s="408" t="n">
-        <v>33847051.45428761</v>
+        <v>33847051.4542876</v>
       </c>
       <c r="AN222" s="408" t="n">
         <v>40344383.15839814</v>
       </c>
       <c r="AO222" s="409" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371122</v>
       </c>
       <c r="AP222" s="410" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="AQ222" s="411" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="AR222" s="411" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="AS222" s="411" t="n">
         <v>9626.529800154427</v>
@@ -45351,28 +45351,28 @@
         </is>
       </c>
       <c r="BB222" s="419" t="n">
-        <v>24369432.4027078</v>
+        <v>24369432.40270781</v>
       </c>
       <c r="BC222" s="420" t="n">
         <v>28456663.68210901</v>
       </c>
       <c r="BD222" s="420" t="n">
-        <v>33847051.45428761</v>
+        <v>33847051.4542876</v>
       </c>
       <c r="BE222" s="420" t="n">
         <v>40344383.15839814</v>
       </c>
       <c r="BF222" s="421" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371122</v>
       </c>
       <c r="BG222" s="416" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="BH222" s="417" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="BI222" s="417" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="BJ222" s="417" t="n">
         <v>9626.529800154427</v>
@@ -45386,28 +45386,28 @@
         </is>
       </c>
       <c r="BS222" s="419" t="n">
-        <v>23896135.38091504</v>
+        <v>23896135.38091505</v>
       </c>
       <c r="BT222" s="420" t="n">
         <v>27675380.21333004</v>
       </c>
       <c r="BU222" s="420" t="n">
-        <v>32641497.62903731</v>
+        <v>32641497.6290373</v>
       </c>
       <c r="BV222" s="420" t="n">
         <v>38590944.95395144</v>
       </c>
       <c r="BW222" s="421" t="n">
-        <v>43653353.27833575</v>
+        <v>43653353.27833574</v>
       </c>
       <c r="BX222" s="416" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="BY222" s="417" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="BZ222" s="417" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="CA222" s="417" t="n">
         <v>9626.529800154427</v>
@@ -45511,34 +45511,34 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881634</v>
       </c>
       <c r="AL223" s="408" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622747</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>331898217.3375409</v>
+        <v>331898217.3375407</v>
       </c>
       <c r="AN223" s="408" t="n">
-        <v>350263780.7229206</v>
+        <v>350263780.7229207</v>
       </c>
       <c r="AO223" s="409" t="n">
         <v>367341837.0863926</v>
       </c>
       <c r="AP223" s="436" t="n">
-        <v>212.7769907992348</v>
+        <v>212.776990799235</v>
       </c>
       <c r="AQ223" s="437" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>229.1040173800738</v>
+        <v>229.1040173800737</v>
       </c>
       <c r="AS223" s="437" t="n">
-        <v>240.1541879531715</v>
+        <v>240.1541879531716</v>
       </c>
       <c r="AT223" s="438" t="n">
-        <v>249.7553771891642</v>
+        <v>249.7553771891641</v>
       </c>
       <c r="BA223" s="155" t="inlineStr">
         <is>
@@ -45546,34 +45546,34 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881634</v>
       </c>
       <c r="BC223" s="440" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622747</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>331898217.3375409</v>
+        <v>331898217.3375407</v>
       </c>
       <c r="BE223" s="440" t="n">
-        <v>350263780.7229206</v>
+        <v>350263780.7229207</v>
       </c>
       <c r="BF223" s="441" t="n">
         <v>367341837.0863926</v>
       </c>
       <c r="BG223" s="442" t="n">
-        <v>212.7769907992348</v>
+        <v>212.776990799235</v>
       </c>
       <c r="BH223" s="443" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>229.1040173800738</v>
+        <v>229.1040173800737</v>
       </c>
       <c r="BJ223" s="443" t="n">
-        <v>240.1541879531715</v>
+        <v>240.1541879531716</v>
       </c>
       <c r="BK223" s="444" t="n">
-        <v>249.7553771891642</v>
+        <v>249.7553771891641</v>
       </c>
       <c r="BR223" s="155" t="inlineStr">
         <is>
@@ -45581,34 +45581,34 @@
         </is>
       </c>
       <c r="BS223" s="439" t="n">
-        <v>300762479.3059133</v>
+        <v>300762479.3059134</v>
       </c>
       <c r="BT223" s="440" t="n">
-        <v>314486811.2550589</v>
+        <v>314486811.2550587</v>
       </c>
       <c r="BU223" s="440" t="n">
-        <v>329203076.1069157</v>
+        <v>329203076.1069155</v>
       </c>
       <c r="BV223" s="440" t="n">
-        <v>346590229.458892</v>
+        <v>346590229.4588921</v>
       </c>
       <c r="BW223" s="441" t="n">
-        <v>362533508.2332522</v>
+        <v>362533508.2332521</v>
       </c>
       <c r="BX223" s="442" t="n">
-        <v>212.4960654861012</v>
+        <v>212.4960654861014</v>
       </c>
       <c r="BY223" s="443" t="n">
-        <v>219.9658978863332</v>
+        <v>219.965897886333</v>
       </c>
       <c r="BZ223" s="443" t="n">
-        <v>228.4034941602649</v>
+        <v>228.4034941602648</v>
       </c>
       <c r="CA223" s="443" t="n">
         <v>239.1426675081908</v>
       </c>
       <c r="CB223" s="444" t="n">
-        <v>248.3649123529544</v>
+        <v>248.3649123529542</v>
       </c>
       <c r="CI223" s="349" t="n">
         <v>272232002.8271314</v>
@@ -47629,34 +47629,34 @@
         </is>
       </c>
       <c r="AK237" s="506" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684381</v>
       </c>
       <c r="AL237" s="368" t="n">
-        <v>159778964.1900266</v>
+        <v>159778964.1900264</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>166038998.9901036</v>
+        <v>166038998.9901035</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>173883609.5679223</v>
+        <v>173883609.5679224</v>
       </c>
       <c r="AO237" s="380" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="AP237" s="381" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="AQ237" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="AR237" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="AS237" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47664,34 +47664,34 @@
         </is>
       </c>
       <c r="BB237" s="391" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684381</v>
       </c>
       <c r="BC237" s="375" t="n">
-        <v>159778964.1900266</v>
+        <v>159778964.1900264</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>166038998.9901036</v>
+        <v>166038998.9901035</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>173883609.5679223</v>
+        <v>173883609.5679224</v>
       </c>
       <c r="BF237" s="392" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="BG237" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="BH237" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="BI237" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="BJ237" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47699,34 +47699,34 @@
         </is>
       </c>
       <c r="BS237" s="391" t="n">
-        <v>153147878.8592605</v>
+        <v>153147878.8592607</v>
       </c>
       <c r="BT237" s="375" t="n">
-        <v>159167049.0236469</v>
+        <v>159167049.0236467</v>
       </c>
       <c r="BU237" s="375" t="n">
-        <v>165208428.9489245</v>
+        <v>165208428.9489243</v>
       </c>
       <c r="BV237" s="375" t="n">
-        <v>172805839.1481515</v>
+        <v>172805839.1481517</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>179867333.8774217</v>
+        <v>179867333.8774216</v>
       </c>
       <c r="BX237" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510881</v>
       </c>
       <c r="BY237" s="372" t="n">
-        <v>142.5496348122931</v>
+        <v>142.5496348122929</v>
       </c>
       <c r="BZ237" s="372" t="n">
-        <v>146.6709237723746</v>
+        <v>146.6709237723745</v>
       </c>
       <c r="CA237" s="372" t="n">
-        <v>152.4634568955541</v>
+        <v>152.4634568955543</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>157.4387342265029</v>
+        <v>157.4387342265027</v>
       </c>
       <c r="CI237" s="199" t="n">
         <v>140012326.4220064</v>
@@ -47824,31 +47824,31 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>99621263.56557636</v>
+        <v>99621263.56557631</v>
       </c>
       <c r="AL238" s="368" t="n">
-        <v>102867455.4246781</v>
+        <v>102867455.424678</v>
       </c>
       <c r="AM238" s="368" t="n">
         <v>105943211.5840001</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>109119948.3533169</v>
+        <v>109119948.3533168</v>
       </c>
       <c r="AO238" s="380" t="n">
         <v>112154742.9937821</v>
       </c>
       <c r="AP238" s="381" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="AQ238" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="AR238" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="AS238" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="AT238" s="382" t="n">
         <v>437.5536311497546</v>
@@ -47859,31 +47859,31 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>99621263.56557636</v>
+        <v>99621263.56557631</v>
       </c>
       <c r="BC238" s="375" t="n">
-        <v>102867455.4246781</v>
+        <v>102867455.424678</v>
       </c>
       <c r="BD238" s="375" t="n">
         <v>105943211.5840001</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>109119948.3533169</v>
+        <v>109119948.3533168</v>
       </c>
       <c r="BF238" s="392" t="n">
         <v>112154742.9937821</v>
       </c>
       <c r="BG238" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="BH238" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="BI238" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="BJ238" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="BK238" s="387" t="n">
         <v>437.5536311497546</v>
@@ -47894,31 +47894,31 @@
         </is>
       </c>
       <c r="BS238" s="391" t="n">
-        <v>99358676.85064593</v>
+        <v>99358676.85064588</v>
       </c>
       <c r="BT238" s="375" t="n">
-        <v>102480003.1332617</v>
+        <v>102480003.1332616</v>
       </c>
       <c r="BU238" s="375" t="n">
         <v>105422960.2471894</v>
       </c>
       <c r="BV238" s="375" t="n">
-        <v>108456407.5674678</v>
+        <v>108456407.5674677</v>
       </c>
       <c r="BW238" s="392" t="n">
         <v>111338199.0650382</v>
       </c>
       <c r="BX238" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492848</v>
       </c>
       <c r="BY238" s="372" t="n">
-        <v>405.655943382653</v>
+        <v>405.6559433826527</v>
       </c>
       <c r="BZ238" s="372" t="n">
         <v>415.6208472109536</v>
       </c>
       <c r="CA238" s="372" t="n">
-        <v>427.1601692832023</v>
+        <v>427.160169283202</v>
       </c>
       <c r="CB238" s="387" t="n">
         <v>437.5536311497546</v>
@@ -48019,7 +48019,7 @@
         </is>
       </c>
       <c r="AK239" s="506" t="n">
-        <v>24428704.35144113</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="AL239" s="368" t="n">
         <v>25266859.46546124</v>
@@ -48034,7 +48034,7 @@
         <v>27898487.10720398</v>
       </c>
       <c r="AP239" s="381" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="AQ239" s="372" t="n">
         <v>439.8151990365077</v>
@@ -48043,7 +48043,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="AS239" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="AT239" s="382" t="n">
         <v>473.6980203171418</v>
@@ -48054,7 +48054,7 @@
         </is>
       </c>
       <c r="BB239" s="391" t="n">
-        <v>24428704.35144113</v>
+        <v>24428704.35144112</v>
       </c>
       <c r="BC239" s="375" t="n">
         <v>25266859.46546124</v>
@@ -48069,7 +48069,7 @@
         <v>27898487.10720398</v>
       </c>
       <c r="BG239" s="386" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="BH239" s="372" t="n">
         <v>439.8151990365077</v>
@@ -48078,7 +48078,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="BJ239" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="BK239" s="387" t="n">
         <v>473.6980203171418</v>
@@ -48089,7 +48089,7 @@
         </is>
       </c>
       <c r="BS239" s="391" t="n">
-        <v>24359788.21509175</v>
+        <v>24359788.21509174</v>
       </c>
       <c r="BT239" s="375" t="n">
         <v>25164378.88482035</v>
@@ -48104,7 +48104,7 @@
         <v>27674622.01245653</v>
       </c>
       <c r="BX239" s="386" t="n">
-        <v>429.816067267475</v>
+        <v>429.8160672674748</v>
       </c>
       <c r="BY239" s="372" t="n">
         <v>439.8151990365077</v>
@@ -48113,7 +48113,7 @@
         <v>449.6699082011411</v>
       </c>
       <c r="CA239" s="372" t="n">
-        <v>461.2323301146551</v>
+        <v>461.232330114655</v>
       </c>
       <c r="CB239" s="387" t="n">
         <v>473.6980203171418</v>
@@ -48214,28 +48214,28 @@
         </is>
       </c>
       <c r="AK240" s="435" t="n">
-        <v>24369432.4027078</v>
+        <v>24369432.40270781</v>
       </c>
       <c r="AL240" s="408" t="n">
         <v>28456663.68210901</v>
       </c>
       <c r="AM240" s="408" t="n">
-        <v>33847051.45428761</v>
+        <v>33847051.4542876</v>
       </c>
       <c r="AN240" s="408" t="n">
         <v>40344383.15839814</v>
       </c>
       <c r="AO240" s="409" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371122</v>
       </c>
       <c r="AP240" s="410" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="AQ240" s="411" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="AR240" s="411" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="AS240" s="411" t="n">
         <v>9626.529800154427</v>
@@ -48249,28 +48249,28 @@
         </is>
       </c>
       <c r="BB240" s="419" t="n">
-        <v>24369432.4027078</v>
+        <v>24369432.40270781</v>
       </c>
       <c r="BC240" s="420" t="n">
         <v>28456663.68210901</v>
       </c>
       <c r="BD240" s="420" t="n">
-        <v>33847051.45428761</v>
+        <v>33847051.4542876</v>
       </c>
       <c r="BE240" s="420" t="n">
         <v>40344383.15839814</v>
       </c>
       <c r="BF240" s="421" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371122</v>
       </c>
       <c r="BG240" s="416" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="BH240" s="417" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="BI240" s="417" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="BJ240" s="417" t="n">
         <v>9626.529800154427</v>
@@ -48284,28 +48284,28 @@
         </is>
       </c>
       <c r="BS240" s="419" t="n">
-        <v>23896135.38091504</v>
+        <v>23896135.38091505</v>
       </c>
       <c r="BT240" s="420" t="n">
         <v>27675380.21333004</v>
       </c>
       <c r="BU240" s="420" t="n">
-        <v>32641497.62903731</v>
+        <v>32641497.6290373</v>
       </c>
       <c r="BV240" s="420" t="n">
         <v>38590944.95395144</v>
       </c>
       <c r="BW240" s="421" t="n">
-        <v>43653353.27833575</v>
+        <v>43653353.27833574</v>
       </c>
       <c r="BX240" s="416" t="n">
-        <v>8028.401824709041</v>
+        <v>8028.401824709043</v>
       </c>
       <c r="BY240" s="417" t="n">
         <v>8410.413515735037</v>
       </c>
       <c r="BZ240" s="417" t="n">
-        <v>9023.719151809508</v>
+        <v>9023.719151809504</v>
       </c>
       <c r="CA240" s="417" t="n">
         <v>9626.529800154427</v>
@@ -48409,34 +48409,34 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881634</v>
       </c>
       <c r="AL241" s="408" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622747</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>331898217.3375409</v>
+        <v>331898217.3375407</v>
       </c>
       <c r="AN241" s="408" t="n">
-        <v>350263780.7229206</v>
+        <v>350263780.7229207</v>
       </c>
       <c r="AO241" s="409" t="n">
         <v>367341837.0863926</v>
       </c>
       <c r="AP241" s="436" t="n">
-        <v>212.7769907992348</v>
+        <v>212.776990799235</v>
       </c>
       <c r="AQ241" s="437" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>229.1040173800738</v>
+        <v>229.1040173800737</v>
       </c>
       <c r="AS241" s="437" t="n">
-        <v>240.1541879531715</v>
+        <v>240.1541879531716</v>
       </c>
       <c r="AT241" s="438" t="n">
-        <v>249.7553771891642</v>
+        <v>249.7553771891641</v>
       </c>
       <c r="BA241" s="155" t="inlineStr">
         <is>
@@ -48444,34 +48444,34 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881634</v>
       </c>
       <c r="BC241" s="440" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622747</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>331898217.3375409</v>
+        <v>331898217.3375407</v>
       </c>
       <c r="BE241" s="440" t="n">
-        <v>350263780.7229206</v>
+        <v>350263780.7229207</v>
       </c>
       <c r="BF241" s="441" t="n">
         <v>367341837.0863926</v>
       </c>
       <c r="BG241" s="442" t="n">
-        <v>212.7769907992348</v>
+        <v>212.776990799235</v>
       </c>
       <c r="BH241" s="443" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>229.1040173800738</v>
+        <v>229.1040173800737</v>
       </c>
       <c r="BJ241" s="443" t="n">
-        <v>240.1541879531715</v>
+        <v>240.1541879531716</v>
       </c>
       <c r="BK241" s="444" t="n">
-        <v>249.7553771891642</v>
+        <v>249.7553771891641</v>
       </c>
       <c r="BR241" s="155" t="inlineStr">
         <is>
@@ -48479,34 +48479,34 @@
         </is>
       </c>
       <c r="BS241" s="439" t="n">
-        <v>300762479.3059133</v>
+        <v>300762479.3059134</v>
       </c>
       <c r="BT241" s="440" t="n">
-        <v>314486811.2550589</v>
+        <v>314486811.2550587</v>
       </c>
       <c r="BU241" s="440" t="n">
-        <v>329203076.1069157</v>
+        <v>329203076.1069155</v>
       </c>
       <c r="BV241" s="440" t="n">
-        <v>346590229.458892</v>
+        <v>346590229.4588921</v>
       </c>
       <c r="BW241" s="441" t="n">
-        <v>362533508.2332522</v>
+        <v>362533508.2332521</v>
       </c>
       <c r="BX241" s="442" t="n">
-        <v>212.4960654861012</v>
+        <v>212.4960654861014</v>
       </c>
       <c r="BY241" s="443" t="n">
-        <v>219.9658978863332</v>
+        <v>219.965897886333</v>
       </c>
       <c r="BZ241" s="443" t="n">
-        <v>228.4034941602649</v>
+        <v>228.4034941602648</v>
       </c>
       <c r="CA241" s="443" t="n">
         <v>239.1426675081908</v>
       </c>
       <c r="CB241" s="444" t="n">
-        <v>248.3649123529544</v>
+        <v>248.3649123529542</v>
       </c>
       <c r="CI241" s="349" t="n">
         <v>272232002.8271314</v>
@@ -48966,7 +48966,7 @@
         </is>
       </c>
       <c r="C246" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D246" s="368" t="n">
         <v>141265555.356126</v>
@@ -48981,7 +48981,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H246" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I246" s="372" t="n">
         <v>859.4354544219096</v>
@@ -49001,7 +49001,7 @@
         </is>
       </c>
       <c r="T246" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U246" s="375" t="n">
         <v>141265555.356126</v>
@@ -49016,7 +49016,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y246" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z246" s="372" t="n">
         <v>859.4354544219096</v>
@@ -49036,34 +49036,34 @@
         </is>
       </c>
       <c r="AK246" s="506" t="n">
-        <v>126617344.1039844</v>
+        <v>126640275.6551961</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>141248374.0261257</v>
+        <v>141248374.0261259</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>156336436.1669482</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="AN246" s="368" t="n">
         <v>172797502.0263113</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105862</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>808.0292638054046</v>
+        <v>808.1756052452387</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>859.3947033651554</v>
+        <v>859.3947033651566</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>905.0157360453045</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="AS246" s="372" t="n">
-        <v>942.7199139126486</v>
+        <v>942.7199139126488</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875809</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49071,34 +49071,34 @@
         </is>
       </c>
       <c r="BB246" s="391" t="n">
-        <v>126617344.1039844</v>
+        <v>126640275.6551961</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>141248374.0261257</v>
+        <v>141248374.0261259</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>156336436.1669482</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="BE246" s="375" t="n">
         <v>172797502.0263113</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105862</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>808.0292638054046</v>
+        <v>808.1756052452387</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>859.3947033651554</v>
+        <v>859.3947033651566</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>905.0157360453045</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="BJ246" s="372" t="n">
-        <v>942.7199139126486</v>
+        <v>942.7199139126488</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875809</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49106,34 +49106,34 @@
         </is>
       </c>
       <c r="BS246" s="391" t="n">
-        <v>127420166.0637996</v>
+        <v>127443243.0133611</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>143078447.3193782</v>
+        <v>143078447.3193784</v>
       </c>
       <c r="BU246" s="375" t="n">
-        <v>159308459.9678396</v>
+        <v>159308459.9678395</v>
       </c>
       <c r="BV246" s="375" t="n">
         <v>176996275.2928466</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>200399456.4644607</v>
+        <v>200399456.4644611</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>808.0292638054046</v>
+        <v>808.1756052452387</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>859.3947033651554</v>
+        <v>859.3947033651566</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>905.0157360453045</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="CA246" s="372" t="n">
-        <v>942.7199139126486</v>
+        <v>942.7199139126488</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875809</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49145,7 +49145,7 @@
         </is>
       </c>
       <c r="C247" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D247" s="368" t="n">
         <v>53602589.259965</v>
@@ -49160,7 +49160,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H247" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I247" s="372" t="n">
         <v>1655.286013279789</v>
@@ -49180,7 +49180,7 @@
         </is>
       </c>
       <c r="T247" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U247" s="375" t="n">
         <v>53602589.259965</v>
@@ -49195,7 +49195,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y247" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z247" s="372" t="n">
         <v>1655.286013279789</v>
@@ -49215,25 +49215,25 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>49640360.26519074</v>
+        <v>49646837.8272707</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996546</v>
       </c>
       <c r="AM247" s="368" t="n">
-        <v>58365089.44804496</v>
+        <v>58365089.44804497</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>64356552.90965888</v>
+        <v>64356552.9096589</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>72697882.80520257</v>
+        <v>72697882.80520251</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>1559.512140047495</v>
+        <v>1559.715640518637</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.286013274027</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49242,7 +49242,7 @@
         <v>1815.921500581827</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>1911.879093764565</v>
+        <v>1911.879093764564</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49250,25 +49250,25 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>49640360.26519074</v>
+        <v>49646837.8272707</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996546</v>
       </c>
       <c r="BD247" s="375" t="n">
-        <v>58365089.44804496</v>
+        <v>58365089.44804497</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>64356552.90965888</v>
+        <v>64356552.9096589</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>72697882.80520257</v>
+        <v>72697882.80520251</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>1559.512140047495</v>
+        <v>1559.715640518637</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.286013274027</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49277,7 +49277,7 @@
         <v>1815.921500581827</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>1911.879093764565</v>
+        <v>1911.879093764564</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49285,25 +49285,25 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>50132747.34533638</v>
+        <v>50139289.15892181</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>54567686.23948944</v>
+        <v>54567686.23948943</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>59834859.82321822</v>
+        <v>59834859.82321823</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>66366095.55613157</v>
+        <v>66366095.55613159</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>75327072.67030132</v>
+        <v>75327072.67030124</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>1559.512140047495</v>
+        <v>1559.715640518637</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>1655.286013274079</v>
+        <v>1655.286013274027</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>1741.357253135669</v>
@@ -49312,7 +49312,7 @@
         <v>1815.921500581827</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>1911.879093764565</v>
+        <v>1911.879093764564</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49324,7 +49324,7 @@
         </is>
       </c>
       <c r="C248" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D248" s="368" t="n">
         <v>30609035.168748</v>
@@ -49339,7 +49339,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H248" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I248" s="372" t="n">
         <v>2485.680463849397</v>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="T248" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U248" s="375" t="n">
         <v>30609035.168748</v>
@@ -49374,7 +49374,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y248" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z248" s="372" t="n">
         <v>2485.680463849397</v>
@@ -49394,34 +49394,34 @@
         </is>
       </c>
       <c r="AK248" s="506" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>30609035.16874772</v>
+        <v>30609035.16874774</v>
       </c>
       <c r="AM248" s="368" t="n">
         <v>34281145.60176639</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>38563749.91945267</v>
+        <v>38563749.91945266</v>
       </c>
       <c r="AO248" s="380" t="n">
         <v>43774095.21109042</v>
       </c>
       <c r="AP248" s="381" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858963</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2485.6804638522</v>
+        <v>2485.680463852202</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.628996359972</v>
       </c>
       <c r="AS248" s="372" t="n">
         <v>2708.250053204232</v>
       </c>
       <c r="AT248" s="382" t="n">
-        <v>2797.787340840899</v>
+        <v>2797.7873408409</v>
       </c>
       <c r="BA248" s="111" t="inlineStr">
         <is>
@@ -49429,34 +49429,34 @@
         </is>
       </c>
       <c r="BB248" s="391" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>30609035.16874772</v>
+        <v>30609035.16874774</v>
       </c>
       <c r="BD248" s="375" t="n">
         <v>34281145.60176639</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>38563749.91945267</v>
+        <v>38563749.91945266</v>
       </c>
       <c r="BF248" s="392" t="n">
         <v>43774095.21109042</v>
       </c>
       <c r="BG248" s="386" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858963</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2485.6804638522</v>
+        <v>2485.680463852202</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.628996359972</v>
       </c>
       <c r="BJ248" s="372" t="n">
         <v>2708.250053204232</v>
       </c>
       <c r="BK248" s="387" t="n">
-        <v>2797.787340840899</v>
+        <v>2797.7873408409</v>
       </c>
       <c r="BR248" s="111" t="inlineStr">
         <is>
@@ -49464,34 +49464,34 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>27524559.52788394</v>
+        <v>27527373.59848613</v>
       </c>
       <c r="BT248" s="375" t="n">
-        <v>30832725.79709065</v>
+        <v>30832725.79709067</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>34674878.53744322</v>
+        <v>34674878.53744323</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>39141702.84725135</v>
+        <v>39141702.84725134</v>
       </c>
       <c r="BW248" s="392" t="n">
-        <v>44556567.68142486</v>
+        <v>44556567.68142487</v>
       </c>
       <c r="BX248" s="386" t="n">
-        <v>2349.470593430919</v>
+        <v>2349.710799858963</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2485.6804638522</v>
+        <v>2485.680463852202</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.628996359972</v>
       </c>
       <c r="CA248" s="372" t="n">
         <v>2708.250053204232</v>
       </c>
       <c r="CB248" s="387" t="n">
-        <v>2797.787340840899</v>
+        <v>2797.7873408409</v>
       </c>
       <c r="CI248" s="225" t="n"/>
       <c r="CJ248" s="225" t="n"/>
@@ -49573,34 +49573,34 @@
         </is>
       </c>
       <c r="AK249" s="435" t="n">
-        <v>277449060.8194634</v>
+        <v>277449060.8194629</v>
       </c>
       <c r="AL249" s="408" t="n">
-        <v>313016581.3406088</v>
+        <v>313016581.3406091</v>
       </c>
       <c r="AM249" s="408" t="n">
-        <v>353845923.7850231</v>
+        <v>353845923.7850234</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>400144174.7224731</v>
+        <v>400144174.7224728</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647978</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>12521.32949520669</v>
+        <v>12521.32949520667</v>
       </c>
       <c r="AQ249" s="411" t="n">
-        <v>12813.16039477719</v>
+        <v>12813.1603947772</v>
       </c>
       <c r="AR249" s="411" t="n">
-        <v>13089.82884659048</v>
+        <v>13089.8288465905</v>
       </c>
       <c r="AS249" s="411" t="n">
-        <v>13374.3106451706</v>
+        <v>13374.31064517059</v>
       </c>
       <c r="AT249" s="412" t="n">
-        <v>13705.78892367393</v>
+        <v>13705.7889236739</v>
       </c>
       <c r="BA249" s="111" t="inlineStr">
         <is>
@@ -49608,34 +49608,34 @@
         </is>
       </c>
       <c r="BB249" s="419" t="n">
-        <v>277449060.8194634</v>
+        <v>277449060.8194629</v>
       </c>
       <c r="BC249" s="420" t="n">
-        <v>313016581.3406088</v>
+        <v>313016581.3406091</v>
       </c>
       <c r="BD249" s="420" t="n">
-        <v>353845923.7850231</v>
+        <v>353845923.7850234</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>400144174.7224731</v>
+        <v>400144174.7224728</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647978</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>12521.32949520669</v>
+        <v>12521.32949520667</v>
       </c>
       <c r="BH249" s="417" t="n">
-        <v>12813.16039477719</v>
+        <v>12813.1603947772</v>
       </c>
       <c r="BI249" s="417" t="n">
-        <v>13089.82884659048</v>
+        <v>13089.8288465905</v>
       </c>
       <c r="BJ249" s="417" t="n">
-        <v>13374.3106451706</v>
+        <v>13374.31064517059</v>
       </c>
       <c r="BK249" s="418" t="n">
-        <v>13705.78892367393</v>
+        <v>13705.7889236739</v>
       </c>
       <c r="BR249" s="111" t="inlineStr">
         <is>
@@ -49643,34 +49643,34 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>269873908.338268</v>
+        <v>269873908.3382675</v>
       </c>
       <c r="BT249" s="420" t="n">
-        <v>304550625.5079275</v>
+        <v>304550625.5079278</v>
       </c>
       <c r="BU249" s="420" t="n">
-        <v>344413772.2410911</v>
+        <v>344413772.2410914</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>389867207.5569912</v>
+        <v>389867207.556991</v>
       </c>
       <c r="BW249" s="421" t="n">
-        <v>446500063.8135937</v>
+        <v>446500063.8135929</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>12521.32949520669</v>
+        <v>12521.32949520667</v>
       </c>
       <c r="BY249" s="417" t="n">
-        <v>12813.16039477719</v>
+        <v>12813.1603947772</v>
       </c>
       <c r="BZ249" s="417" t="n">
-        <v>13089.82884659048</v>
+        <v>13089.8288465905</v>
       </c>
       <c r="CA249" s="417" t="n">
-        <v>13374.3106451706</v>
+        <v>13374.31064517059</v>
       </c>
       <c r="CB249" s="418" t="n">
-        <v>13705.78892367393</v>
+        <v>13705.7889236739</v>
       </c>
       <c r="CI249" s="225" t="n"/>
       <c r="CJ249" s="225" t="n"/>
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="C250" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D250" s="425" t="n">
         <v>538493761.125447</v>
@@ -49697,7 +49697,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="H250" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I250" s="427" t="n">
         <v>2306.219676493023</v>
@@ -49717,7 +49717,7 @@
         </is>
       </c>
       <c r="T250" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U250" s="430" t="n">
         <v>538493761.125447</v>
@@ -49732,7 +49732,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="Y250" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z250" s="433" t="n">
         <v>2306.219676493023</v>
@@ -49752,34 +49752,34 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>481161614.8533117</v>
+        <v>481193830.9101709</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>538476579.7954477</v>
+        <v>538476579.7954482</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017829</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>675861979.5778959</v>
+        <v>675861979.5778958</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916769</v>
       </c>
       <c r="AP250" s="436" t="n">
-        <v>2163.75605083753</v>
+        <v>2163.900924588503</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>2306.266576502191</v>
+        <v>2306.266576502183</v>
       </c>
       <c r="AR250" s="437" t="n">
-        <v>2446.296897853601</v>
+        <v>2446.296897853602</v>
       </c>
       <c r="AS250" s="437" t="n">
         <v>2570.842398787372</v>
       </c>
       <c r="AT250" s="438" t="n">
-        <v>2709.041941852854</v>
+        <v>2709.041941852852</v>
       </c>
       <c r="BA250" s="155" t="inlineStr">
         <is>
@@ -49787,34 +49787,34 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>481161614.8533117</v>
+        <v>481193830.9101709</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>538476579.7954477</v>
+        <v>538476579.7954482</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017829</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>675861979.5778959</v>
+        <v>675861979.5778958</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916769</v>
       </c>
       <c r="BG250" s="442" t="n">
-        <v>2163.75605083753</v>
+        <v>2163.900924588503</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>2306.266576502191</v>
+        <v>2306.266576502183</v>
       </c>
       <c r="BI250" s="443" t="n">
-        <v>2446.296897853601</v>
+        <v>2446.296897853602</v>
       </c>
       <c r="BJ250" s="443" t="n">
         <v>2570.842398787372</v>
       </c>
       <c r="BK250" s="444" t="n">
-        <v>2709.041941852854</v>
+        <v>2709.041941852852</v>
       </c>
       <c r="BR250" s="155" t="inlineStr">
         <is>
@@ -49822,34 +49822,34 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>474951381.275288</v>
+        <v>474983814.1090366</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>533029484.8638858</v>
+        <v>533029484.8638863</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>598231970.5695921</v>
+        <v>598231970.5695924</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>672371281.2532208</v>
+        <v>672371281.2532206</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>766783160.6297805</v>
+        <v>766783160.6297802</v>
       </c>
       <c r="BX250" s="442" t="n">
-        <v>2128.802545631967</v>
+        <v>2128.947914403956</v>
       </c>
       <c r="BY250" s="443" t="n">
-        <v>2262.185456546928</v>
+        <v>2262.185456546921</v>
       </c>
       <c r="BZ250" s="443" t="n">
-        <v>2393.088848784541</v>
+        <v>2393.088848784542</v>
       </c>
       <c r="CA250" s="443" t="n">
-        <v>2509.778431754753</v>
+        <v>2509.778431754752</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>2639.541171375337</v>
+        <v>2639.541171375335</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51872,7 +51872,7 @@
         </is>
       </c>
       <c r="C264" s="369" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="D264" s="368" t="n">
         <v>141265555.356126</v>
@@ -51887,7 +51887,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="H264" s="371" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="I264" s="372" t="n">
         <v>859.4354544219096</v>
@@ -51907,7 +51907,7 @@
         </is>
       </c>
       <c r="T264" s="374" t="n">
-        <v>126630762.484102</v>
+        <v>126653694.035314</v>
       </c>
       <c r="U264" s="375" t="n">
         <v>141265555.356126</v>
@@ -51922,7 +51922,7 @@
         <v>194826216.478621</v>
       </c>
       <c r="Y264" s="377" t="n">
-        <v>808.0645724699008</v>
+        <v>808.2109047967596</v>
       </c>
       <c r="Z264" s="372" t="n">
         <v>859.4354544219096</v>
@@ -51942,34 +51942,34 @@
         </is>
       </c>
       <c r="AK264" s="506" t="n">
-        <v>126617344.1039844</v>
+        <v>126640275.6551961</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>141248374.0261257</v>
+        <v>141248374.0261259</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>156336436.1669482</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="AN264" s="368" t="n">
         <v>172797502.0263113</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105862</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>808.0292638054063</v>
+        <v>808.1756052452386</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>859.3947033651531</v>
+        <v>859.3947033651579</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>905.0157360453059</v>
+        <v>905.0157360453038</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>942.7199139126466</v>
+        <v>942.7199139126491</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875787</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51977,34 +51977,34 @@
         </is>
       </c>
       <c r="BB264" s="391" t="n">
-        <v>126617344.1039844</v>
+        <v>126640275.6551961</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>141248374.0261257</v>
+        <v>141248374.0261259</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>156336436.1669482</v>
+        <v>156336436.1669481</v>
       </c>
       <c r="BE264" s="375" t="n">
         <v>172797502.0263113</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105862</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>808.0292638054063</v>
+        <v>808.1756052452386</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>859.3947033651531</v>
+        <v>859.3947033651579</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>905.0157360453059</v>
+        <v>905.0157360453038</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>942.7199139126466</v>
+        <v>942.7199139126491</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875787</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,94 +52012,94 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>127420166.0637996</v>
+        <v>127443243.0133611</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>143078447.3193782</v>
+        <v>143078447.3193784</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>159308459.9678396</v>
+        <v>159308459.9678395</v>
       </c>
       <c r="BV264" s="375" t="n">
         <v>176996275.2928466</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>200399456.4644607</v>
+        <v>200399456.4644611</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>808.0292638054063</v>
+        <v>808.1756052452386</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>859.3947033651531</v>
+        <v>859.3947033651579</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>905.0157360453059</v>
+        <v>905.0157360453038</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>942.7199139126466</v>
+        <v>942.7199139126491</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875787</v>
       </c>
       <c r="CI264" s="396" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="CJ264" s="397" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CK264" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CL264" s="397" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CM264" s="398" t="n">
         <v>1.000000000000002</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.9999999999999932</v>
+        <v>0.9999999999999956</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>1.000000000000015</v>
+        <v>1.000000000000014</v>
       </c>
       <c r="CP264" s="103" t="n">
         <v>1.000000000000012</v>
       </c>
       <c r="CQ264" s="103" t="n">
-        <v>0.9999999999999872</v>
+        <v>0.999999999999987</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000000051</v>
+        <v>1.000000000000048</v>
       </c>
       <c r="CT264" s="396" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="CU264" s="397" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="CV264" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CW264" s="397" t="n">
-        <v>0.9999999999999994</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CX264" s="398" t="n">
         <v>1.000000000000002</v>
       </c>
       <c r="CY264" s="102" t="n">
-        <v>1.012460167073759</v>
+        <v>1.012460167073762</v>
       </c>
       <c r="CZ264" s="103" t="n">
-        <v>1.012992901858758</v>
+        <v>1.012992901858757</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>1.013514104921968</v>
+        <v>1.013514104921969</v>
       </c>
       <c r="DB264" s="103" t="n">
         <v>1.013928837783292</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>1.014213282022972</v>
+        <v>1.014213282022969</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,16 +52117,16 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>91214772.24990852</v>
+        <v>91237642.06254259</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>104988005.1745398</v>
+        <v>104988005.1745399</v>
       </c>
       <c r="DM264" s="375" t="n">
         <v>118016580.2209291</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>131624915.6046437</v>
+        <v>131624915.6046438</v>
       </c>
       <c r="DO264" s="392" t="n">
         <v>150667262.2450481</v>
@@ -52139,7 +52139,7 @@
         </is>
       </c>
       <c r="C265" s="369" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="D265" s="368" t="n">
         <v>53602589.259965</v>
@@ -52154,7 +52154,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="H265" s="371" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="I265" s="372" t="n">
         <v>1655.286013279789</v>
@@ -52174,7 +52174,7 @@
         </is>
       </c>
       <c r="T265" s="374" t="n">
-        <v>49640360.265191</v>
+        <v>49646837.827271</v>
       </c>
       <c r="U265" s="375" t="n">
         <v>53602589.259965</v>
@@ -52189,7 +52189,7 @@
         <v>72697882.80520301</v>
       </c>
       <c r="Y265" s="377" t="n">
-        <v>1559.512140023056</v>
+        <v>1559.715640494195</v>
       </c>
       <c r="Z265" s="372" t="n">
         <v>1655.286013279789</v>
@@ -52209,34 +52209,34 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>49640360.26519074</v>
+        <v>49646837.8272707</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996546</v>
       </c>
       <c r="AM265" s="368" t="n">
-        <v>58365089.44804496</v>
+        <v>58365089.44804497</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>64356552.90965888</v>
+        <v>64356552.9096589</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>72697882.80520257</v>
+        <v>72697882.80520251</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518627</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.286013274053</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>1741.357253135671</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>1815.92150058184</v>
+        <v>1815.921500581839</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>1911.879093764572</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52244,34 +52244,34 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>49640360.26519074</v>
+        <v>49646837.8272707</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>53602589.25996549</v>
+        <v>53602589.25996546</v>
       </c>
       <c r="BD265" s="375" t="n">
-        <v>58365089.44804496</v>
+        <v>58365089.44804497</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>64356552.90965888</v>
+        <v>64356552.9096589</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>72697882.80520257</v>
+        <v>72697882.80520251</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518627</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.286013274053</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>1741.357253135671</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>1815.92150058184</v>
+        <v>1815.921500581839</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>1911.879093764572</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,52 +52279,52 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>50132747.34533637</v>
+        <v>50139289.15892181</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>54567686.23948944</v>
+        <v>54567686.23948942</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>59834859.82321822</v>
+        <v>59834859.82321823</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>66366095.55613157</v>
+        <v>66366095.55613159</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>75327072.67030132</v>
+        <v>75327072.67030126</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>1559.512140047485</v>
+        <v>1559.715640518627</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.286013274053</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>1741.357253135671</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>1815.92150058184</v>
+        <v>1815.921500581839</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>1911.879093764572</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="CI265" s="396" t="n">
-        <v>0.9999999999999949</v>
+        <v>0.9999999999999953</v>
       </c>
       <c r="CJ265" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CK265" s="397" t="n">
         <v>1.000000000000005</v>
       </c>
       <c r="CL265" s="397" t="n">
-        <v>0.9999999999999983</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CM265" s="398" t="n">
         <v>1.000000000000006</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999998904</v>
+        <v>0.9999999999998912</v>
       </c>
       <c r="CO265" s="103" t="n">
         <v>1.00000000000004</v>
@@ -52333,28 +52333,28 @@
         <v>1.000000000000254</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.999999999999917</v>
+        <v>0.9999999999999167</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>1.000000000000211</v>
+        <v>1.000000000000212</v>
       </c>
       <c r="CT265" s="396" t="n">
-        <v>0.9999999999999949</v>
+        <v>0.9999999999999953</v>
       </c>
       <c r="CU265" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CV265" s="397" t="n">
         <v>1.000000000000005</v>
       </c>
       <c r="CW265" s="397" t="n">
-        <v>0.9999999999999983</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CX265" s="398" t="n">
         <v>1.000000000000006</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.010821595180418</v>
+        <v>1.010821595180419</v>
       </c>
       <c r="CZ265" s="103" t="n">
         <v>1.011287059486804</v>
@@ -52363,10 +52363,10 @@
         <v>1.011865406606377</v>
       </c>
       <c r="DB265" s="103" t="n">
-        <v>1.012224134246556</v>
+        <v>1.012224134246555</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>1.012461354756916</v>
+        <v>1.012461354756917</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,16 +52384,16 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>34750578.12387209</v>
+        <v>34757061.96015742</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>39059424.72251657</v>
       </c>
       <c r="DM265" s="375" t="n">
-        <v>43435991.2510025</v>
+        <v>43435991.25100249</v>
       </c>
       <c r="DN265" s="375" t="n">
-        <v>48299721.45664501</v>
+        <v>48299721.45664503</v>
       </c>
       <c r="DO265" s="392" t="n">
         <v>55445858.27453821</v>
@@ -52406,7 +52406,7 @@
         </is>
       </c>
       <c r="C266" s="369" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="D266" s="368" t="n">
         <v>30609035.168748</v>
@@ -52421,7 +52421,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="H266" s="371" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="I266" s="372" t="n">
         <v>2485.680463849397</v>
@@ -52441,7 +52441,7 @@
         </is>
       </c>
       <c r="T266" s="374" t="n">
-        <v>27454849.664673</v>
+        <v>27457656.608241</v>
       </c>
       <c r="U266" s="375" t="n">
         <v>30609035.168748</v>
@@ -52456,7 +52456,7 @@
         <v>43774095.21109</v>
       </c>
       <c r="Y266" s="377" t="n">
-        <v>2349.470593410198</v>
+        <v>2349.71079983824</v>
       </c>
       <c r="Z266" s="372" t="n">
         <v>2485.680463849397</v>
@@ -52476,34 +52476,34 @@
         </is>
       </c>
       <c r="AK266" s="506" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>30609035.16874772</v>
+        <v>30609035.16874774</v>
       </c>
       <c r="AM266" s="368" t="n">
         <v>34281145.60176639</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>38563749.91945267</v>
+        <v>38563749.91945266</v>
       </c>
       <c r="AO266" s="380" t="n">
         <v>43774095.21109042</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2349.470593430893</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2485.680463852157</v>
+        <v>2485.680463852158</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2610.628996359923</v>
+        <v>2610.628996359929</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204245</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52511,34 +52511,34 @@
         </is>
       </c>
       <c r="BB266" s="391" t="n">
-        <v>27454849.66467313</v>
+        <v>27457656.60824113</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>30609035.16874772</v>
+        <v>30609035.16874774</v>
       </c>
       <c r="BD266" s="375" t="n">
         <v>34281145.60176639</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>38563749.91945267</v>
+        <v>38563749.91945266</v>
       </c>
       <c r="BF266" s="392" t="n">
         <v>43774095.21109042</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2349.470593430893</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2485.680463852157</v>
+        <v>2485.680463852158</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2610.628996359923</v>
+        <v>2610.628996359929</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204245</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52546,13 +52546,13 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>27524559.52788394</v>
+        <v>27527373.59848613</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>30832725.79709065</v>
+        <v>30832725.79709067</v>
       </c>
       <c r="BU266" s="375" t="n">
-        <v>34674878.53744321</v>
+        <v>34674878.53744323</v>
       </c>
       <c r="BV266" s="375" t="n">
         <v>39141702.84725135</v>
@@ -52561,22 +52561,22 @@
         <v>44556567.68142486</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2349.470593430893</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2485.680463852157</v>
+        <v>2485.680463852158</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2610.628996359923</v>
+        <v>2610.628996359929</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204245</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="CI266" s="396" t="n">
-        <v>0.9999999999999923</v>
+        <v>0.9999999999999928</v>
       </c>
       <c r="CJ266" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52585,28 +52585,28 @@
         <v>1.00000000000002</v>
       </c>
       <c r="CL266" s="397" t="n">
-        <v>0.9999999999999705</v>
+        <v>0.9999999999999706</v>
       </c>
       <c r="CM266" s="398" t="n">
-        <v>0.9999999999999597</v>
+        <v>0.9999999999999599</v>
       </c>
       <c r="CN266" s="102" t="n">
-        <v>0.9999999999999944</v>
+        <v>0.999999999999994</v>
       </c>
       <c r="CO266" s="103" t="n">
-        <v>1.000000000000006</v>
+        <v>1.000000000000005</v>
       </c>
       <c r="CP266" s="103" t="n">
         <v>1.000000000000113</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999997714</v>
+        <v>0.9999999999997716</v>
       </c>
       <c r="CR266" s="104" t="n">
-        <v>0.9999999999997512</v>
+        <v>0.999999999999751</v>
       </c>
       <c r="CT266" s="396" t="n">
-        <v>0.9999999999999923</v>
+        <v>0.9999999999999928</v>
       </c>
       <c r="CU266" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52615,16 +52615,16 @@
         <v>1.00000000000002</v>
       </c>
       <c r="CW266" s="397" t="n">
-        <v>0.9999999999999705</v>
+        <v>0.9999999999999706</v>
       </c>
       <c r="CX266" s="398" t="n">
-        <v>0.9999999999999597</v>
+        <v>0.9999999999999599</v>
       </c>
       <c r="CY266" s="102" t="n">
-        <v>1.011153716208353</v>
+        <v>1.011153716208352</v>
       </c>
       <c r="CZ266" s="103" t="n">
-        <v>1.011529745696788</v>
+        <v>1.011529745696787</v>
       </c>
       <c r="DA266" s="103" t="n">
         <v>1.011878771076148</v>
@@ -52651,19 +52651,19 @@
         <v>0</v>
       </c>
       <c r="DK266" s="391" t="n">
-        <v>18936636.2269968</v>
+        <v>18939430.84554336</v>
       </c>
       <c r="DL266" s="375" t="n">
         <v>21655757.83449421</v>
       </c>
       <c r="DM266" s="375" t="n">
-        <v>24654357.08209224</v>
+        <v>24654357.08209226</v>
       </c>
       <c r="DN266" s="375" t="n">
-        <v>28165319.75429519</v>
+        <v>28165319.7542952</v>
       </c>
       <c r="DO266" s="392" t="n">
-        <v>32487496.48842778</v>
+        <v>32487496.48842777</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1" thickBot="1">
@@ -52743,34 +52743,34 @@
         </is>
       </c>
       <c r="AK267" s="435" t="n">
-        <v>277449060.8194634</v>
+        <v>277449060.8194629</v>
       </c>
       <c r="AL267" s="408" t="n">
-        <v>313016581.3406088</v>
+        <v>313016581.3406091</v>
       </c>
       <c r="AM267" s="408" t="n">
-        <v>353845923.7850231</v>
+        <v>353845923.7850234</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>400144174.7224731</v>
+        <v>400144174.7224728</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647978</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>12521.3294952065</v>
+        <v>12521.32949520649</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>12813.16039477738</v>
+        <v>12813.16039477741</v>
       </c>
       <c r="AR267" s="411" t="n">
-        <v>13089.8288465903</v>
+        <v>13089.82884659033</v>
       </c>
       <c r="AS267" s="411" t="n">
         <v>13374.3106451707</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>13705.78892367379</v>
+        <v>13705.78892367376</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52778,34 +52778,34 @@
         </is>
       </c>
       <c r="BB267" s="419" t="n">
-        <v>277449060.8194634</v>
+        <v>277449060.8194629</v>
       </c>
       <c r="BC267" s="420" t="n">
-        <v>313016581.3406088</v>
+        <v>313016581.3406091</v>
       </c>
       <c r="BD267" s="420" t="n">
-        <v>353845923.7850231</v>
+        <v>353845923.7850234</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>400144174.7224731</v>
+        <v>400144174.7224728</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>458182076.6647986</v>
+        <v>458182076.6647978</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>12521.3294952065</v>
+        <v>12521.32949520649</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>12813.16039477738</v>
+        <v>12813.16039477741</v>
       </c>
       <c r="BI267" s="417" t="n">
-        <v>13089.8288465903</v>
+        <v>13089.82884659033</v>
       </c>
       <c r="BJ267" s="417" t="n">
         <v>13374.3106451707</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>13705.78892367379</v>
+        <v>13705.78892367376</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52813,43 +52813,43 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>269873908.338268</v>
+        <v>269873908.3382675</v>
       </c>
       <c r="BT267" s="420" t="n">
-        <v>304550625.5079275</v>
+        <v>304550625.5079278</v>
       </c>
       <c r="BU267" s="420" t="n">
-        <v>344413772.2410912</v>
+        <v>344413772.2410915</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>389867207.5569912</v>
+        <v>389867207.556991</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>446500063.8135937</v>
+        <v>446500063.813593</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>12521.3294952065</v>
+        <v>12521.32949520649</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>12813.16039477738</v>
+        <v>12813.16039477741</v>
       </c>
       <c r="BZ267" s="417" t="n">
-        <v>13089.8288465903</v>
+        <v>13089.82884659033</v>
       </c>
       <c r="CA267" s="417" t="n">
         <v>13374.3106451707</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>13705.78892367379</v>
+        <v>13705.78892367376</v>
       </c>
       <c r="CI267" s="422" t="n">
-        <v>0.9999999999997758</v>
+        <v>0.9999999999997755</v>
       </c>
       <c r="CJ267" s="423" t="n">
         <v>1.000000000000281</v>
       </c>
       <c r="CK267" s="423" t="n">
-        <v>0.9999999999997822</v>
+        <v>0.9999999999997825</v>
       </c>
       <c r="CL267" s="423" t="n">
         <v>1.000000000000173</v>
@@ -52858,28 +52858,28 @@
         <v>1.000000000000534</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>1.000000000000435</v>
+        <v>1.000000000000437</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>0.9999999999995581</v>
+        <v>0.9999999999995572</v>
       </c>
       <c r="CP267" s="133" t="n">
-        <v>1.000000000000195</v>
+        <v>1.000000000000194</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>0.9999999999997891</v>
+        <v>0.9999999999997896</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>0.9999999999996199</v>
+        <v>0.9999999999996215</v>
       </c>
       <c r="CT267" s="422" t="n">
-        <v>0.9999999999997758</v>
+        <v>0.9999999999997755</v>
       </c>
       <c r="CU267" s="423" t="n">
         <v>1.000000000000281</v>
       </c>
       <c r="CV267" s="423" t="n">
-        <v>0.9999999999997822</v>
+        <v>0.9999999999997825</v>
       </c>
       <c r="CW267" s="423" t="n">
         <v>1.000000000000173</v>
@@ -52888,19 +52888,19 @@
         <v>1.000000000000534</v>
       </c>
       <c r="CY267" s="132" t="n">
-        <v>1.030804461102172</v>
+        <v>1.030804461102173</v>
       </c>
       <c r="CZ267" s="133" t="n">
-        <v>1.031706490389905</v>
+        <v>1.031706490389904</v>
       </c>
       <c r="DA267" s="133" t="n">
-        <v>1.032463657793182</v>
+        <v>1.032463657793181</v>
       </c>
       <c r="DB267" s="133" t="n">
         <v>1.032608668003572</v>
       </c>
       <c r="DC267" s="134" t="n">
-        <v>1.033561506215621</v>
+        <v>1.033561506215622</v>
       </c>
       <c r="DE267" s="419" t="n">
         <v>0</v>
@@ -52918,16 +52918,16 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>163797061.6705368</v>
+        <v>163797061.6705367</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>188089957.4893983</v>
+        <v>188089957.4893982</v>
       </c>
       <c r="DM267" s="420" t="n">
         <v>215978942.3423747</v>
       </c>
       <c r="DN267" s="420" t="n">
-        <v>246346883.7616722</v>
+        <v>246346883.7616721</v>
       </c>
       <c r="DO267" s="421" t="n">
         <v>286688358.6587306</v>
@@ -52940,7 +52940,7 @@
         </is>
       </c>
       <c r="C268" s="425" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="D268" s="425" t="n">
         <v>538493761.125447</v>
@@ -52955,7 +52955,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="H268" s="427" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="I268" s="427" t="n">
         <v>2306.219676493023</v>
@@ -52975,7 +52975,7 @@
         </is>
       </c>
       <c r="T268" s="429" t="n">
-        <v>481175033.23343</v>
+        <v>481207249.29029</v>
       </c>
       <c r="U268" s="430" t="n">
         <v>538493761.125447</v>
@@ -52990,7 +52990,7 @@
         <v>769480271.159713</v>
       </c>
       <c r="Y268" s="432" t="n">
-        <v>2163.721440416514</v>
+        <v>2163.866307810164</v>
       </c>
       <c r="Z268" s="433" t="n">
         <v>2306.219676493023</v>
@@ -53010,34 +53010,34 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>481161614.8533117</v>
+        <v>481193830.9101709</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>538476579.7954477</v>
+        <v>538476579.7954482</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017829</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>675861979.5778959</v>
+        <v>675861979.5778958</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916769</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>2163.756050837527</v>
+        <v>2163.900924588497</v>
       </c>
       <c r="AQ268" s="437" t="n">
-        <v>2306.266576502184</v>
+        <v>2306.266576502192</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>2446.296897853598</v>
+        <v>2446.296897853596</v>
       </c>
       <c r="AS268" s="437" t="n">
-        <v>2570.842398787373</v>
+        <v>2570.842398787378</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2709.041941852846</v>
+        <v>2709.041941852845</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53045,34 +53045,34 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>481161614.8533117</v>
+        <v>481193830.9101709</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>538476579.7954477</v>
+        <v>538476579.7954482</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017829</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>675861979.5778959</v>
+        <v>675861979.5778958</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916769</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>2163.756050837527</v>
+        <v>2163.900924588497</v>
       </c>
       <c r="BH268" s="443" t="n">
-        <v>2306.266576502184</v>
+        <v>2306.266576502192</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>2446.296897853598</v>
+        <v>2446.296897853596</v>
       </c>
       <c r="BJ268" s="443" t="n">
-        <v>2570.842398787373</v>
+        <v>2570.842398787378</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2709.041941852846</v>
+        <v>2709.041941852845</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,34 +53080,34 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>474951381.2752879</v>
+        <v>474983814.1090366</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>533029484.8638858</v>
+        <v>533029484.8638863</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>598231970.5695922</v>
+        <v>598231970.5695925</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>672371281.2532208</v>
+        <v>672371281.2532206</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>766783160.6297805</v>
+        <v>766783160.6297803</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>2128.802545631964</v>
+        <v>2128.94791440395</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>2262.185456546922</v>
+        <v>2262.185456546929</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>2393.088848784539</v>
+        <v>2393.088848784537</v>
       </c>
       <c r="CA268" s="443" t="n">
-        <v>2509.778431754754</v>
+        <v>2509.778431754758</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2639.54117137533</v>
+        <v>2639.541171375329</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,19 +53125,19 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>308699048.2713142</v>
+        <v>308731196.5387801</v>
       </c>
       <c r="DL268" s="440" t="n">
-        <v>353793145.220949</v>
+        <v>353793145.2209489</v>
       </c>
       <c r="DM268" s="440" t="n">
         <v>402085870.8963985</v>
       </c>
       <c r="DN268" s="440" t="n">
-        <v>454436840.577256</v>
+        <v>454436840.5772561</v>
       </c>
       <c r="DO268" s="441" t="n">
-        <v>525288975.6667448</v>
+        <v>525288975.6667446</v>
       </c>
     </row>
     <row r="269">
@@ -58406,34 +58406,34 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178443</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>2163.155319482305</v>
+        <v>2163.155319482293</v>
       </c>
       <c r="BZ294" s="190" t="n">
-        <v>2378.866087308497</v>
+        <v>2378.866087308485</v>
       </c>
       <c r="CA294" s="190" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173779</v>
       </c>
       <c r="CB294" s="198" t="n">
-        <v>2879.554573332819</v>
+        <v>2879.554573332804</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178443</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>2163.155319482305</v>
+        <v>2163.155319482293</v>
       </c>
       <c r="CE294" s="200" t="n">
-        <v>2378.866087308497</v>
+        <v>2378.866087308485</v>
       </c>
       <c r="CF294" s="200" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173779</v>
       </c>
       <c r="CG294" s="201" t="n">
-        <v>2879.554573332819</v>
+        <v>2879.554573332804</v>
       </c>
       <c r="CI294" s="199" t="n">
         <v>0</v>
@@ -58463,19 +58463,19 @@
         <v>0</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>1964.875071784439</v>
+        <v>1964.87507178443</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>2163.155319482305</v>
+        <v>2163.155319482293</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>2378.866087308497</v>
+        <v>2378.866087308485</v>
       </c>
       <c r="CZ294" s="200" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173779</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>2879.554573332819</v>
+        <v>2879.554573332804</v>
       </c>
     </row>
     <row r="295">
@@ -58701,34 +58701,34 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031423</v>
       </c>
       <c r="BY295" s="190" t="n">
-        <v>372.0859813342884</v>
+        <v>372.0859813342864</v>
       </c>
       <c r="BZ295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314235</v>
       </c>
       <c r="CA295" s="190" t="n">
-        <v>446.7528256294974</v>
+        <v>446.752825629495</v>
       </c>
       <c r="CB295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467678</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031423</v>
       </c>
       <c r="CD295" s="190" t="n">
-        <v>372.0859813342884</v>
+        <v>372.0859813342864</v>
       </c>
       <c r="CE295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314235</v>
       </c>
       <c r="CF295" s="190" t="n">
-        <v>446.7528256294974</v>
+        <v>446.752825629495</v>
       </c>
       <c r="CG295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467678</v>
       </c>
       <c r="CI295" s="197" t="n">
         <v>0</v>
@@ -58758,19 +58758,19 @@
         <v>0</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031423</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>372.0859813342884</v>
+        <v>372.0859813342864</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>407.7078036314258</v>
+        <v>407.7078036314235</v>
       </c>
       <c r="CZ295" s="190" t="n">
-        <v>446.7528256294974</v>
+        <v>446.752825629495</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467678</v>
       </c>
     </row>
     <row r="296">
@@ -58996,34 +58996,34 @@
         <v>0</v>
       </c>
       <c r="BX296" s="197" t="n">
-        <v>130.6682137649147</v>
+        <v>130.6682137649139</v>
       </c>
       <c r="BY296" s="190" t="n">
-        <v>143.0165673943987</v>
+        <v>143.0165673943978</v>
       </c>
       <c r="BZ296" s="190" t="n">
-        <v>157.7761316534094</v>
+        <v>157.7761316534084</v>
       </c>
       <c r="CA296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323896</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.91484786594</v>
       </c>
       <c r="CC296" s="197" t="n">
-        <v>130.6682137649147</v>
+        <v>130.6682137649139</v>
       </c>
       <c r="CD296" s="190" t="n">
-        <v>143.0165673943987</v>
+        <v>143.0165673943978</v>
       </c>
       <c r="CE296" s="190" t="n">
-        <v>157.7761316534094</v>
+        <v>157.7761316534084</v>
       </c>
       <c r="CF296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323896</v>
       </c>
       <c r="CG296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.91484786594</v>
       </c>
       <c r="CI296" s="197" t="n">
         <v>0</v>
@@ -59053,19 +59053,19 @@
         <v>0</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>130.6682137649147</v>
+        <v>130.6682137649139</v>
       </c>
       <c r="CX296" s="190" t="n">
-        <v>143.0165673943987</v>
+        <v>143.0165673943978</v>
       </c>
       <c r="CY296" s="190" t="n">
-        <v>157.7761316534094</v>
+        <v>157.7761316534084</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323896</v>
       </c>
       <c r="DA296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.91484786594</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" thickBot="1">
@@ -59291,31 +59291,31 @@
         <v>0</v>
       </c>
       <c r="BX297" s="211" t="n">
-        <v>663.932716975579</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>753.618247441934</v>
+        <v>753.6182474419337</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CA297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398271</v>
       </c>
       <c r="CB297" s="213" t="n">
         <v>1093.349295717359</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>663.932716975579</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CD297" s="212" t="n">
-        <v>753.618247441934</v>
+        <v>753.6182474419337</v>
       </c>
       <c r="CE297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CF297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398271</v>
       </c>
       <c r="CG297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59348,16 +59348,16 @@
         <v>0</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>663.932716975579</v>
+        <v>663.9327169755792</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>753.618247441934</v>
+        <v>753.6182474419337</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245002</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398271</v>
       </c>
       <c r="DA297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59586,34 +59586,34 @@
         <v>0</v>
       </c>
       <c r="BX298" s="221" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028065</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652911</v>
       </c>
       <c r="BZ298" s="222" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217817</v>
       </c>
       <c r="CA298" s="222" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875491</v>
       </c>
       <c r="CB298" s="214" t="n">
-        <v>4656.78981356289</v>
+        <v>4656.78981356287</v>
       </c>
       <c r="CC298" s="222" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028065</v>
       </c>
       <c r="CD298" s="222" t="n">
-        <v>3431.876115652926</v>
+        <v>3431.876115652911</v>
       </c>
       <c r="CE298" s="222" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217817</v>
       </c>
       <c r="CF298" s="222" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875491</v>
       </c>
       <c r="CG298" s="214" t="n">
-        <v>4656.78981356289</v>
+        <v>4656.78981356287</v>
       </c>
       <c r="CI298" s="349" t="n">
         <v>0</v>
@@ -59643,19 +59643,19 @@
         <v>0</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>3107.351651028077</v>
+        <v>3107.351651028065</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>3431.876115652927</v>
+        <v>3431.876115652911</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217817</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875491</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>4656.78981356289</v>
+        <v>4656.78981356287</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -71183,49 +71183,49 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>1587676.557723576</v>
+        <v>1587964.100370663</v>
       </c>
       <c r="BT368" s="375" t="n">
         <v>1859004.224119248</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>2152911.242958716</v>
+        <v>2152911.2429587</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>2465352.406804799</v>
+        <v>2465352.406804793</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>2848333.99196268</v>
+        <v>2848333.991962671</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>808.0292638054065</v>
+        <v>808.1756052452386</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>859.3947033651531</v>
+        <v>859.3947033651579</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>905.0157360453055</v>
+        <v>905.0157360453039</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>942.7199139126466</v>
+        <v>942.719913912649</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875787</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>1587676.557723576</v>
+        <v>1587964.100370663</v>
       </c>
       <c r="CX368" s="512" t="n">
         <v>1859004.224119248</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>2152911.242958716</v>
+        <v>2152911.2429587</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>2465352.406804799</v>
+        <v>2465352.406804793</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>2848333.99196268</v>
+        <v>2848333.991962671</v>
       </c>
     </row>
     <row r="369">
@@ -71375,49 +71375,49 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>542516.2970675451</v>
+        <v>542587.0899259115</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>615908.7206380003</v>
+        <v>615908.7206379945</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>709964.9410135973</v>
+        <v>709964.9410135936</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>811268.0615062943</v>
+        <v>811268.0615062892</v>
       </c>
       <c r="BW369" s="392" t="n">
-        <v>938677.3753216262</v>
+        <v>938677.3753216201</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1559.512140047484</v>
+        <v>1559.715640518627</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>1655.286013274059</v>
+        <v>1655.286013274053</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1741.357253135671</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="CA369" s="372" t="n">
-        <v>1815.921500581841</v>
+        <v>1815.921500581839</v>
       </c>
       <c r="CB369" s="387" t="n">
-        <v>1911.879093764572</v>
+        <v>1911.879093764571</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>542516.2970675451</v>
+        <v>542587.0899259115</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>615908.7206380003</v>
+        <v>615908.7206379945</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>709964.9410135973</v>
+        <v>709964.9410135936</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>811268.0615062943</v>
+        <v>811268.0615062892</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>938677.3753216262</v>
+        <v>938677.3753216201</v>
       </c>
     </row>
     <row r="370">
@@ -71567,49 +71567,49 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>307001.1257368089</v>
+        <v>307032.5130816945</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>355493.4875794522</v>
+        <v>355493.48757945</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>411894.9442278915</v>
+        <v>411894.9442278896</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>471930.3932272117</v>
+        <v>471930.393227209</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195705</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>2349.470593430893</v>
+        <v>2349.710799858938</v>
       </c>
       <c r="BY370" s="372" t="n">
-        <v>2485.680463852157</v>
+        <v>2485.680463852158</v>
       </c>
       <c r="BZ370" s="372" t="n">
-        <v>2610.628996359924</v>
+        <v>2610.628996359929</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>2708.250053204244</v>
+        <v>2708.250053204245</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840876</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>307001.1257368089</v>
+        <v>307032.5130816945</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>355493.4875794522</v>
+        <v>355493.48757945</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>411894.9442278915</v>
+        <v>411894.9442278896</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>471930.3932272117</v>
+        <v>471930.393227209</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195705</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71759,49 +71759,49 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>8313320.311898909</v>
+        <v>8313320.311898901</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>9656231.480904527</v>
+        <v>9656231.480904544</v>
       </c>
       <c r="BU371" s="420" t="n">
-        <v>11180930.84129481</v>
+        <v>11180930.84129483</v>
       </c>
       <c r="BV371" s="420" t="n">
         <v>12713050.33670373</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694949</v>
       </c>
       <c r="BX371" s="416" t="n">
-        <v>12521.3294952065</v>
+        <v>12521.32949520649</v>
       </c>
       <c r="BY371" s="417" t="n">
-        <v>12813.16039477738</v>
+        <v>12813.16039477741</v>
       </c>
       <c r="BZ371" s="417" t="n">
-        <v>13089.8288465903</v>
+        <v>13089.82884659033</v>
       </c>
       <c r="CA371" s="417" t="n">
         <v>13374.3106451707</v>
       </c>
       <c r="CB371" s="418" t="n">
-        <v>13705.7889236738</v>
+        <v>13705.78892367376</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>8313320.311898909</v>
+        <v>8313320.311898901</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>9656231.480904527</v>
+        <v>9656231.480904544</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>11180930.84129481</v>
+        <v>11180930.84129483</v>
       </c>
       <c r="CZ371" s="420" t="n">
         <v>12713050.33670373</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694949</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71951,49 +71951,49 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>10750514.29242684</v>
+        <v>10750904.01527717</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>12486637.91324123</v>
+        <v>12486637.91324124</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>14455701.96949502</v>
+        <v>14455701.96949501</v>
       </c>
       <c r="BV372" s="440" t="n">
-        <v>16461601.19824203</v>
+        <v>16461601.19824202</v>
       </c>
       <c r="BW372" s="441" t="n">
-        <v>19311960.7534534</v>
+        <v>19311960.75345335</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3459.70314910126</v>
+        <v>3459.828568717107</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>3638.429096053079</v>
+        <v>3638.429096053098</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>3805.6148937706</v>
+        <v>3805.614893770615</v>
       </c>
       <c r="CA372" s="443" t="n">
-        <v>3931.865569506746</v>
+        <v>3931.865569506758</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>4147.054414439613</v>
+        <v>4147.054414439619</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>10750514.29242684</v>
+        <v>10750904.01527717</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>12486637.91324123</v>
+        <v>12486637.91324124</v>
       </c>
       <c r="CY372" s="420" t="n">
         <v>14455701.96949501</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>16461601.19824203</v>
+        <v>16461601.19824202</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>19311960.7534534</v>
+        <v>19311960.75345335</v>
       </c>
     </row>
     <row r="375">
